--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D1245B-7C3E-415B-9788-DD8961F93586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531C2F8E-FFF6-432E-983F-FF4C39799191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Constructor_ID</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>Constructor’s total championship points from the prior season divided by the total constructor points awarded across all teams in that season.</t>
+  </si>
+  <si>
+    <t>Has_Defending_Driver_Champ</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the constructor employs the reigning Drivers’ World Champion entering the current season (1 = one driver on the constructor’s roster won the Drivers’ Championship in the previous season, 0 = no defending Drivers’ Champion on the team).</t>
   </si>
 </sst>
 </file>
@@ -979,12 +985,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1086,6 +1092,17 @@
         <v>21</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531C2F8E-FFF6-432E-983F-FF4C39799191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27104173-F5B1-4904-A9E1-C822977D41B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
-  <si>
-    <t>Constructor_ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
   <si>
     <t>Season</t>
   </si>
@@ -34,39 +31,21 @@
     <t>Team_Name</t>
   </si>
   <si>
-    <t>New_Team</t>
-  </si>
-  <si>
     <t>New_Identity</t>
   </si>
   <si>
     <t>Constructor_Champion</t>
   </si>
   <si>
-    <t>Unique numeric identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant despite team name, branding, or ownership changes and reflects underlying organizational continuity. (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes would share the same Constructor_ID).</t>
-  </si>
-  <si>
-    <t>Official constructor name used for championship entry in a given season. This may vary across seasons for the same Constructor_ID due to sponsorship, branding, or ownership changes.</t>
-  </si>
-  <si>
     <t>Target variable indicating whether a constructor won the Formula One World Championship (1 = won championship, 0 = did not win championship).</t>
   </si>
   <si>
-    <t>Binary variable indicating whether a constructor competed under a new team name compared to the previous season while maintaining the same Constructor_ID (1 = Team_Name differs from the previous season for the same Constructor_ID, 0 = no name change).</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether a constructor represents a genuinely new organizational entry into the Formula One World Championship, meaning the team has never previously competed in Formula One under any ownership lineage (1 = first ever appearance in F1 history, 0 = constructor lineage has competed in F1 at any point in history).</t>
-  </si>
-  <si>
     <t>Binary variable indicating whether a season introduced a major technical or sporting regulation overhaul that materially altered car design, power units, aerodynamics, or competitive structure (1 = season includes significant regulatory reset, 0 = no major regulation overhaul)</t>
   </si>
   <si>
     <t>Reg_Change_Year</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>Target</t>
   </si>
   <si>
@@ -76,29 +55,107 @@
     <t>Column</t>
   </si>
   <si>
-    <t>Column Type</t>
-  </si>
-  <si>
-    <t>Data Description</t>
-  </si>
-  <si>
     <t>Prior_Season_Points_Share</t>
   </si>
   <si>
-    <t>Constructor’s total championship points from the prior season divided by the total constructor points awarded across all teams in that season.</t>
-  </si>
-  <si>
-    <t>Has_Defending_Driver_Champ</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether the constructor employs the reigning Drivers’ World Champion entering the current season (1 = one driver on the constructor’s roster won the Drivers’ Championship in the previous season, 0 = no defending Drivers’ Champion on the team).</t>
+    <t>Works_Team</t>
+  </si>
+  <si>
+    <t>Defending_Driver_Champ</t>
+  </si>
+  <si>
+    <t>Prior_Season_Win_Prop</t>
+  </si>
+  <si>
+    <t>Prior_Season_Constructor_Points</t>
+  </si>
+  <si>
+    <t>Prior_Season_Points_Total</t>
+  </si>
+  <si>
+    <t>The amount of points scored by a single team in the previous season.</t>
+  </si>
+  <si>
+    <t>The amount of points scored by all teams in the previous season.</t>
+  </si>
+  <si>
+    <t>Prior_Season_Grand_Prix_Wins</t>
+  </si>
+  <si>
+    <t>Prior_Season_Grand_Prix_Count</t>
+  </si>
+  <si>
+    <t>The number of races won by a constructor in the previous season (this does not include sprint Race wins).</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Test|Train.csv</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>Unique numeric identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve organizational continuity (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a constructor is new to the sport, meaning the team has never previously competed in Formula One under any ownership lineage (1 = first ever appearance in F1 history, 0 = constructor lineage has competed in F1 at any point in history).</t>
+  </si>
+  <si>
+    <t>Constructor_Lineage_ID</t>
+  </si>
+  <si>
+    <t>Composite unique identifier formed by concatenating Constructor_Lineage_ID, Season, and Team_Name. Used as the primary row-level key.</t>
+  </si>
+  <si>
+    <t>Official constructor name used for championship entry in a given season. This may vary across seasons for the same Constructor_Lineage_ID due to sponsorship, branding, or ownership changes.</t>
+  </si>
+  <si>
+    <t>New_Name</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a returning constructor is competing under a new team name compared to the previous season (1 = `Team_Name` differs from the previous season for the same `Constructor_Lineage_ID`, 0 = no name change).</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of total points scored by all teams in the previous season (`Prior_Season_Constructor_Points` divided by `Prior_Season_Points_Total`). This normalizes performance across seasons with different numbers of teams or scoring systems.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of total races won in the previous season (`Prior_Season_Grand_Prix_Wins` divided by `Prior_Season_Grand_Prix_Count`). This normalizes performance across seasons with different numbers of races.</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the constructor operates as a full works manufacturer team in a given season (1 = manufacturer owned and builds both chassis and power unit in-house, 0 = customer team).</t>
+  </si>
+  <si>
+    <t>Use For Modeling</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the reigning Drivers’ World Champion is competing for a team in the current season (1 = one driver on the constructor’s roster won the Drivers’ Championship in the previous season, 0 = no reigning Drivers’ Champion on the team).</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix held in the previous season (this does not include sprint races).</t>
+  </si>
+  <si>
+    <t>Excluded</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>All prior season performance variables reflect results from the immediately preceding season and are used to simulate preseason championship prediction without incorporating in season outcomes.</t>
+  </si>
+  <si>
+    <t>Engineered feature</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,8 +290,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333D42"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,13 +499,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,12 +676,24 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -985,125 +1074,276 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="255.77734375" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="255.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27104173-F5B1-4904-A9E1-C822977D41B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB94DEDB-3212-436C-BE3E-61E3EAD9C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>Season</t>
   </si>
@@ -149,13 +149,19 @@
   </si>
   <si>
     <t>Engineered feature</t>
+  </si>
+  <si>
+    <t>Engine_Provider</t>
+  </si>
+  <si>
+    <t>Categorical variable indicating which company created the engine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +306,12 @@
       <i/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -676,7 +688,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
@@ -689,11 +701,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1074,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
@@ -1083,12 +1096,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -1111,13 +1124,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1125,13 +1138,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1139,13 +1152,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1180,23 +1193,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
+      <c r="D9" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>24</v>
@@ -1205,12 +1218,12 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -1219,110 +1232,110 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>15</v>
+      <c r="A12" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>39</v>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>16</v>
+      <c r="A13" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>24</v>
@@ -1331,19 +1344,34 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -1,37 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB94DEDB-3212-436C-BE3E-61E3EAD9C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF65E74F-A0C0-46E8-9416-D748BF035C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>Season</t>
   </si>
   <si>
-    <t>Championship year in which the constructor competed in the Formula One World Championship.</t>
-  </si>
-  <si>
     <t>Team_Name</t>
-  </si>
-  <si>
-    <t>New_Identity</t>
   </si>
   <si>
     <t>Constructor_Champion</t>
@@ -40,16 +47,7 @@
     <t>Target variable indicating whether a constructor won the Formula One World Championship (1 = won championship, 0 = did not win championship).</t>
   </si>
   <si>
-    <t>Binary variable indicating whether a season introduced a major technical or sporting regulation overhaul that materially altered car design, power units, aerodynamics, or competitive structure (1 = season includes significant regulatory reset, 0 = no major regulation overhaul)</t>
-  </si>
-  <si>
     <t>Reg_Change_Year</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Predictor</t>
   </si>
   <si>
     <t>Column</t>
@@ -58,34 +56,19 @@
     <t>Prior_Season_Points_Share</t>
   </si>
   <si>
-    <t>Works_Team</t>
-  </si>
-  <si>
     <t>Defending_Driver_Champ</t>
   </si>
   <si>
     <t>Prior_Season_Win_Prop</t>
   </si>
   <si>
-    <t>Prior_Season_Constructor_Points</t>
-  </si>
-  <si>
     <t>Prior_Season_Points_Total</t>
-  </si>
-  <si>
-    <t>The amount of points scored by a single team in the previous season.</t>
-  </si>
-  <si>
-    <t>The amount of points scored by all teams in the previous season.</t>
   </si>
   <si>
     <t>Prior_Season_Grand_Prix_Wins</t>
   </si>
   <si>
     <t>Prior_Season_Grand_Prix_Count</t>
-  </si>
-  <si>
-    <t>The number of races won by a constructor in the previous season (this does not include sprint Race wins).</t>
   </si>
   <si>
     <t>Description</t>
@@ -100,37 +83,13 @@
     <t>Origin</t>
   </si>
   <si>
-    <t>Unique numeric identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve organizational continuity (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether a constructor is new to the sport, meaning the team has never previously competed in Formula One under any ownership lineage (1 = first ever appearance in F1 history, 0 = constructor lineage has competed in F1 at any point in history).</t>
-  </si>
-  <si>
     <t>Constructor_Lineage_ID</t>
   </si>
   <si>
     <t>Composite unique identifier formed by concatenating Constructor_Lineage_ID, Season, and Team_Name. Used as the primary row-level key.</t>
   </si>
   <si>
-    <t>Official constructor name used for championship entry in a given season. This may vary across seasons for the same Constructor_Lineage_ID due to sponsorship, branding, or ownership changes.</t>
-  </si>
-  <si>
     <t>New_Name</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether a returning constructor is competing under a new team name compared to the previous season (1 = `Team_Name` differs from the previous season for the same `Constructor_Lineage_ID`, 0 = no name change).</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of total points scored by all teams in the previous season (`Prior_Season_Constructor_Points` divided by `Prior_Season_Points_Total`). This normalizes performance across seasons with different numbers of teams or scoring systems.</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of total races won in the previous season (`Prior_Season_Grand_Prix_Wins` divided by `Prior_Season_Grand_Prix_Count`). This normalizes performance across seasons with different numbers of races.</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether the constructor operates as a full works manufacturer team in a given season (1 = manufacturer owned and builds both chassis and power unit in-house, 0 = customer team).</t>
-  </si>
-  <si>
-    <t>Use For Modeling</t>
   </si>
   <si>
     <t>Binary variable indicating whether the reigning Drivers’ World Champion is competing for a team in the current season (1 = one driver on the constructor’s roster won the Drivers’ Championship in the previous season, 0 = no reigning Drivers’ Champion on the team).</t>
@@ -139,29 +98,217 @@
     <t>The number of Grand Prix held in the previous season (this does not include sprint races).</t>
   </si>
   <si>
-    <t>Excluded</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
     <t>All prior season performance variables reflect results from the immediately preceding season and are used to simulate preseason championship prediction without incorporating in season outcomes.</t>
   </si>
   <si>
     <t>Engineered feature</t>
   </si>
   <si>
-    <t>Engine_Provider</t>
+    <t>Engine_Branding</t>
   </si>
   <si>
-    <t>Categorical variable indicating which company created the engine</t>
+    <t>Categorical variable indicating the engine manufacturer or brand that powered the constructor during the given season.</t>
+  </si>
+  <si>
+    <t>New_Team</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the team is the reigning Constructors World Champion (1 if the constructor won the championship the prior season, 0 otherwise).</t>
+  </si>
+  <si>
+    <t>Defending_Constructor_Champ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of DNF or DNS results during the previous season (this does not include sprint race results). </t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the season included a major technical or sporting regulation change (1 = yes, 0 = no).</t>
+  </si>
+  <si>
+    <t>Numerical identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve organizational continuity (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
+  </si>
+  <si>
+    <t>Year in which the constructor competed in the Formula One World Championship.</t>
+  </si>
+  <si>
+    <t>Constructor name used for championship entry in a given season. This may vary across seasons for the same `Constructor_Lineage_ID` due to sponsorship, branding, or ownership changes.</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a returning constructor is competing under a new team name compared to the previous season (1 = `Team_Name` differs from the previous season, 0 = no name change).</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a constructor is new to the F1 championship (1 = first ever appearance in F1 history, 0 = constructor has previously competed in Formula 1 under any name).</t>
+  </si>
+  <si>
+    <t>Prior_Season_NonFinishes</t>
+  </si>
+  <si>
+    <t>Prior_Season_NonFinish_Rate</t>
+  </si>
+  <si>
+    <t>The amount of points scored by a single team in the previous season (including points earned from fastest lap or sprint races).</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the previous season (this does not include sprint Race wins).</t>
+  </si>
+  <si>
+    <t>Prior_Season_Points_Earned</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of total points scored by all teams in the previous season (`Prior_Season_Points_Earned` divided by `Prior_Season_Points_Total`). This normalizes performance across seasons with different numbers of teams or scoring systems.</t>
+  </si>
+  <si>
+    <r>
+      <t>Constructor’s proportion of races won in the previous season (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_Grand_Prix_Wins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_Grand_Prix_Count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Constructor’s proportion of DNF or DNS results (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_NonFinishes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ÷ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_Grand_Prix_Count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> × 2)), accounting for 2 cars per race.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Underlined</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> variables  are used solely for feature engineering and are dropped from the dataset after derived features are created.</t>
+    </r>
+  </si>
+  <si>
+    <t>Total points scored by all constructors in the previous season, including fastest lap and sprint points. This total reflects the full prior-season grid, including teams that did not compete in the current season.</t>
+  </si>
+  <si>
+    <t>Prior_Season_Grand_Prix_Wins_First5GP</t>
+  </si>
+  <si>
+    <t>Prior_Season_Win_Prop_First5GP</t>
+  </si>
+  <si>
+    <t>Prior_Season_Grand_Prix_Wins_Last5GP</t>
+  </si>
+  <si>
+    <t>Prior_Season_Win_Prop_Last5GP</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the previous season's first 5 rounds (this does not include sprint Race wins).</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the previous season's last 5 rounds (this does not include sprint Race wins).</t>
+  </si>
+  <si>
+    <t>`Prior_Season_Grand_Prix_Wins_First5GP` ÷ 5</t>
+  </si>
+  <si>
+    <t>`Prior_Season_Grand_Prix_Wins_Last5GP` ÷ 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,12 +444,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF333D42"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="0"/>
@@ -316,8 +457,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,13 +689,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,23 +856,21 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1087,289 +1251,8491 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:XFB27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="255.77734375" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="10" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>25</v>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>36</v>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
       </c>
-      <c r="D3" s="7" t="s">
+    </row>
+    <row r="18" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>28</v>
+    <row r="20" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
+      <c r="B20" s="1" t="s">
+        <v>14</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>39</v>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="21" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>0</v>
+    <row r="22" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A22" s="8" t="s">
+        <v>45</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
+      <c r="B22" s="1" t="s">
+        <v>14</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>2</v>
+    <row r="23" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
+      <c r="C23" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>23</v>
+    <row r="24" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A24" s="8" t="s">
+        <v>47</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AB26" s="5"/>
+      <c r="AD26" s="5"/>
+      <c r="AF26" s="5"/>
+      <c r="AH26" s="5"/>
+      <c r="AJ26" s="5"/>
+      <c r="AL26" s="5"/>
+      <c r="AN26" s="5"/>
+      <c r="AP26" s="5"/>
+      <c r="AR26" s="5"/>
+      <c r="AT26" s="5"/>
+      <c r="AV26" s="5"/>
+      <c r="AX26" s="5"/>
+      <c r="AZ26" s="5"/>
+      <c r="BB26" s="5"/>
+      <c r="BD26" s="5"/>
+      <c r="BF26" s="5"/>
+      <c r="BH26" s="5"/>
+      <c r="BJ26" s="5"/>
+      <c r="BL26" s="5"/>
+      <c r="BN26" s="5"/>
+      <c r="BP26" s="5"/>
+      <c r="BR26" s="5"/>
+      <c r="BT26" s="5"/>
+      <c r="BV26" s="5"/>
+      <c r="BX26" s="5"/>
+      <c r="BZ26" s="5"/>
+      <c r="CB26" s="5"/>
+      <c r="CD26" s="5"/>
+      <c r="CF26" s="5"/>
+      <c r="CH26" s="5"/>
+      <c r="CJ26" s="5"/>
+      <c r="CL26" s="5"/>
+      <c r="CN26" s="5"/>
+      <c r="CP26" s="5"/>
+      <c r="CR26" s="5"/>
+      <c r="CT26" s="5"/>
+      <c r="CV26" s="5"/>
+      <c r="CX26" s="5"/>
+      <c r="CZ26" s="5"/>
+      <c r="DB26" s="5"/>
+      <c r="DD26" s="5"/>
+      <c r="DF26" s="5"/>
+      <c r="DH26" s="5"/>
+      <c r="DJ26" s="5"/>
+      <c r="DL26" s="5"/>
+      <c r="DN26" s="5"/>
+      <c r="DP26" s="5"/>
+      <c r="DR26" s="5"/>
+      <c r="DT26" s="5"/>
+      <c r="DV26" s="5"/>
+      <c r="DX26" s="5"/>
+      <c r="DZ26" s="5"/>
+      <c r="EB26" s="5"/>
+      <c r="ED26" s="5"/>
+      <c r="EF26" s="5"/>
+      <c r="EH26" s="5"/>
+      <c r="EJ26" s="5"/>
+      <c r="EL26" s="5"/>
+      <c r="EN26" s="5"/>
+      <c r="EP26" s="5"/>
+      <c r="ER26" s="5"/>
+      <c r="ET26" s="5"/>
+      <c r="EV26" s="5"/>
+      <c r="EX26" s="5"/>
+      <c r="EZ26" s="5"/>
+      <c r="FB26" s="5"/>
+      <c r="FD26" s="5"/>
+      <c r="FF26" s="5"/>
+      <c r="FH26" s="5"/>
+      <c r="FJ26" s="5"/>
+      <c r="FL26" s="5"/>
+      <c r="FN26" s="5"/>
+      <c r="FP26" s="5"/>
+      <c r="FR26" s="5"/>
+      <c r="FT26" s="5"/>
+      <c r="FV26" s="5"/>
+      <c r="FX26" s="5"/>
+      <c r="FZ26" s="5"/>
+      <c r="GB26" s="5"/>
+      <c r="GD26" s="5"/>
+      <c r="GF26" s="5"/>
+      <c r="GH26" s="5"/>
+      <c r="GJ26" s="5"/>
+      <c r="GL26" s="5"/>
+      <c r="GN26" s="5"/>
+      <c r="GP26" s="5"/>
+      <c r="GR26" s="5"/>
+      <c r="GT26" s="5"/>
+      <c r="GV26" s="5"/>
+      <c r="GX26" s="5"/>
+      <c r="GZ26" s="5"/>
+      <c r="HB26" s="5"/>
+      <c r="HD26" s="5"/>
+      <c r="HF26" s="5"/>
+      <c r="HH26" s="5"/>
+      <c r="HJ26" s="5"/>
+      <c r="HL26" s="5"/>
+      <c r="HN26" s="5"/>
+      <c r="HP26" s="5"/>
+      <c r="HR26" s="5"/>
+      <c r="HT26" s="5"/>
+      <c r="HV26" s="5"/>
+      <c r="HX26" s="5"/>
+      <c r="HZ26" s="5"/>
+      <c r="IB26" s="5"/>
+      <c r="ID26" s="5"/>
+      <c r="IF26" s="5"/>
+      <c r="IH26" s="5"/>
+      <c r="IJ26" s="5"/>
+      <c r="IL26" s="5"/>
+      <c r="IN26" s="5"/>
+      <c r="IP26" s="5"/>
+      <c r="IR26" s="5"/>
+      <c r="IT26" s="5"/>
+      <c r="IV26" s="5"/>
+      <c r="IX26" s="5"/>
+      <c r="IZ26" s="5"/>
+      <c r="JB26" s="5"/>
+      <c r="JD26" s="5"/>
+      <c r="JF26" s="5"/>
+      <c r="JH26" s="5"/>
+      <c r="JJ26" s="5"/>
+      <c r="JL26" s="5"/>
+      <c r="JN26" s="5"/>
+      <c r="JP26" s="5"/>
+      <c r="JR26" s="5"/>
+      <c r="JT26" s="5"/>
+      <c r="JV26" s="5"/>
+      <c r="JX26" s="5"/>
+      <c r="JZ26" s="5"/>
+      <c r="KB26" s="5"/>
+      <c r="KD26" s="5"/>
+      <c r="KF26" s="5"/>
+      <c r="KH26" s="5"/>
+      <c r="KJ26" s="5"/>
+      <c r="KL26" s="5"/>
+      <c r="KN26" s="5"/>
+      <c r="KP26" s="5"/>
+      <c r="KR26" s="5"/>
+      <c r="KT26" s="5"/>
+      <c r="KV26" s="5"/>
+      <c r="KX26" s="5"/>
+      <c r="KZ26" s="5"/>
+      <c r="LB26" s="5"/>
+      <c r="LD26" s="5"/>
+      <c r="LF26" s="5"/>
+      <c r="LH26" s="5"/>
+      <c r="LJ26" s="5"/>
+      <c r="LL26" s="5"/>
+      <c r="LN26" s="5"/>
+      <c r="LP26" s="5"/>
+      <c r="LR26" s="5"/>
+      <c r="LT26" s="5"/>
+      <c r="LV26" s="5"/>
+      <c r="LX26" s="5"/>
+      <c r="LZ26" s="5"/>
+      <c r="MB26" s="5"/>
+      <c r="MD26" s="5"/>
+      <c r="MF26" s="5"/>
+      <c r="MH26" s="5"/>
+      <c r="MJ26" s="5"/>
+      <c r="ML26" s="5"/>
+      <c r="MN26" s="5"/>
+      <c r="MP26" s="5"/>
+      <c r="MR26" s="5"/>
+      <c r="MT26" s="5"/>
+      <c r="MV26" s="5"/>
+      <c r="MX26" s="5"/>
+      <c r="MZ26" s="5"/>
+      <c r="NB26" s="5"/>
+      <c r="ND26" s="5"/>
+      <c r="NF26" s="5"/>
+      <c r="NH26" s="5"/>
+      <c r="NJ26" s="5"/>
+      <c r="NL26" s="5"/>
+      <c r="NN26" s="5"/>
+      <c r="NP26" s="5"/>
+      <c r="NR26" s="5"/>
+      <c r="NT26" s="5"/>
+      <c r="NV26" s="5"/>
+      <c r="NX26" s="5"/>
+      <c r="NZ26" s="5"/>
+      <c r="OB26" s="5"/>
+      <c r="OD26" s="5"/>
+      <c r="OF26" s="5"/>
+      <c r="OH26" s="5"/>
+      <c r="OJ26" s="5"/>
+      <c r="OL26" s="5"/>
+      <c r="ON26" s="5"/>
+      <c r="OP26" s="5"/>
+      <c r="OR26" s="5"/>
+      <c r="OT26" s="5"/>
+      <c r="OV26" s="5"/>
+      <c r="OX26" s="5"/>
+      <c r="OZ26" s="5"/>
+      <c r="PB26" s="5"/>
+      <c r="PD26" s="5"/>
+      <c r="PF26" s="5"/>
+      <c r="PH26" s="5"/>
+      <c r="PJ26" s="5"/>
+      <c r="PL26" s="5"/>
+      <c r="PN26" s="5"/>
+      <c r="PP26" s="5"/>
+      <c r="PR26" s="5"/>
+      <c r="PT26" s="5"/>
+      <c r="PV26" s="5"/>
+      <c r="PX26" s="5"/>
+      <c r="PZ26" s="5"/>
+      <c r="QB26" s="5"/>
+      <c r="QD26" s="5"/>
+      <c r="QF26" s="5"/>
+      <c r="QH26" s="5"/>
+      <c r="QJ26" s="5"/>
+      <c r="QL26" s="5"/>
+      <c r="QN26" s="5"/>
+      <c r="QP26" s="5"/>
+      <c r="QR26" s="5"/>
+      <c r="QT26" s="5"/>
+      <c r="QV26" s="5"/>
+      <c r="QX26" s="5"/>
+      <c r="QZ26" s="5"/>
+      <c r="RB26" s="5"/>
+      <c r="RD26" s="5"/>
+      <c r="RF26" s="5"/>
+      <c r="RH26" s="5"/>
+      <c r="RJ26" s="5"/>
+      <c r="RL26" s="5"/>
+      <c r="RN26" s="5"/>
+      <c r="RP26" s="5"/>
+      <c r="RR26" s="5"/>
+      <c r="RT26" s="5"/>
+      <c r="RV26" s="5"/>
+      <c r="RX26" s="5"/>
+      <c r="RZ26" s="5"/>
+      <c r="SB26" s="5"/>
+      <c r="SD26" s="5"/>
+      <c r="SF26" s="5"/>
+      <c r="SH26" s="5"/>
+      <c r="SJ26" s="5"/>
+      <c r="SL26" s="5"/>
+      <c r="SN26" s="5"/>
+      <c r="SP26" s="5"/>
+      <c r="SR26" s="5"/>
+      <c r="ST26" s="5"/>
+      <c r="SV26" s="5"/>
+      <c r="SX26" s="5"/>
+      <c r="SZ26" s="5"/>
+      <c r="TB26" s="5"/>
+      <c r="TD26" s="5"/>
+      <c r="TF26" s="5"/>
+      <c r="TH26" s="5"/>
+      <c r="TJ26" s="5"/>
+      <c r="TL26" s="5"/>
+      <c r="TN26" s="5"/>
+      <c r="TP26" s="5"/>
+      <c r="TR26" s="5"/>
+      <c r="TT26" s="5"/>
+      <c r="TV26" s="5"/>
+      <c r="TX26" s="5"/>
+      <c r="TZ26" s="5"/>
+      <c r="UB26" s="5"/>
+      <c r="UD26" s="5"/>
+      <c r="UF26" s="5"/>
+      <c r="UH26" s="5"/>
+      <c r="UJ26" s="5"/>
+      <c r="UL26" s="5"/>
+      <c r="UN26" s="5"/>
+      <c r="UP26" s="5"/>
+      <c r="UR26" s="5"/>
+      <c r="UT26" s="5"/>
+      <c r="UV26" s="5"/>
+      <c r="UX26" s="5"/>
+      <c r="UZ26" s="5"/>
+      <c r="VB26" s="5"/>
+      <c r="VD26" s="5"/>
+      <c r="VF26" s="5"/>
+      <c r="VH26" s="5"/>
+      <c r="VJ26" s="5"/>
+      <c r="VL26" s="5"/>
+      <c r="VN26" s="5"/>
+      <c r="VP26" s="5"/>
+      <c r="VR26" s="5"/>
+      <c r="VT26" s="5"/>
+      <c r="VV26" s="5"/>
+      <c r="VX26" s="5"/>
+      <c r="VZ26" s="5"/>
+      <c r="WB26" s="5"/>
+      <c r="WD26" s="5"/>
+      <c r="WF26" s="5"/>
+      <c r="WH26" s="5"/>
+      <c r="WJ26" s="5"/>
+      <c r="WL26" s="5"/>
+      <c r="WN26" s="5"/>
+      <c r="WP26" s="5"/>
+      <c r="WR26" s="5"/>
+      <c r="WT26" s="5"/>
+      <c r="WV26" s="5"/>
+      <c r="WX26" s="5"/>
+      <c r="WZ26" s="5"/>
+      <c r="XB26" s="5"/>
+      <c r="XD26" s="5"/>
+      <c r="XF26" s="5"/>
+      <c r="XH26" s="5"/>
+      <c r="XJ26" s="5"/>
+      <c r="XL26" s="5"/>
+      <c r="XN26" s="5"/>
+      <c r="XP26" s="5"/>
+      <c r="XR26" s="5"/>
+      <c r="XT26" s="5"/>
+      <c r="XV26" s="5"/>
+      <c r="XX26" s="5"/>
+      <c r="XZ26" s="5"/>
+      <c r="YB26" s="5"/>
+      <c r="YD26" s="5"/>
+      <c r="YF26" s="5"/>
+      <c r="YH26" s="5"/>
+      <c r="YJ26" s="5"/>
+      <c r="YL26" s="5"/>
+      <c r="YN26" s="5"/>
+      <c r="YP26" s="5"/>
+      <c r="YR26" s="5"/>
+      <c r="YT26" s="5"/>
+      <c r="YV26" s="5"/>
+      <c r="YX26" s="5"/>
+      <c r="YZ26" s="5"/>
+      <c r="ZB26" s="5"/>
+      <c r="ZD26" s="5"/>
+      <c r="ZF26" s="5"/>
+      <c r="ZH26" s="5"/>
+      <c r="ZJ26" s="5"/>
+      <c r="ZL26" s="5"/>
+      <c r="ZN26" s="5"/>
+      <c r="ZP26" s="5"/>
+      <c r="ZR26" s="5"/>
+      <c r="ZT26" s="5"/>
+      <c r="ZV26" s="5"/>
+      <c r="ZX26" s="5"/>
+      <c r="ZZ26" s="5"/>
+      <c r="AAB26" s="5"/>
+      <c r="AAD26" s="5"/>
+      <c r="AAF26" s="5"/>
+      <c r="AAH26" s="5"/>
+      <c r="AAJ26" s="5"/>
+      <c r="AAL26" s="5"/>
+      <c r="AAN26" s="5"/>
+      <c r="AAP26" s="5"/>
+      <c r="AAR26" s="5"/>
+      <c r="AAT26" s="5"/>
+      <c r="AAV26" s="5"/>
+      <c r="AAX26" s="5"/>
+      <c r="AAZ26" s="5"/>
+      <c r="ABB26" s="5"/>
+      <c r="ABD26" s="5"/>
+      <c r="ABF26" s="5"/>
+      <c r="ABH26" s="5"/>
+      <c r="ABJ26" s="5"/>
+      <c r="ABL26" s="5"/>
+      <c r="ABN26" s="5"/>
+      <c r="ABP26" s="5"/>
+      <c r="ABR26" s="5"/>
+      <c r="ABT26" s="5"/>
+      <c r="ABV26" s="5"/>
+      <c r="ABX26" s="5"/>
+      <c r="ABZ26" s="5"/>
+      <c r="ACB26" s="5"/>
+      <c r="ACD26" s="5"/>
+      <c r="ACF26" s="5"/>
+      <c r="ACH26" s="5"/>
+      <c r="ACJ26" s="5"/>
+      <c r="ACL26" s="5"/>
+      <c r="ACN26" s="5"/>
+      <c r="ACP26" s="5"/>
+      <c r="ACR26" s="5"/>
+      <c r="ACT26" s="5"/>
+      <c r="ACV26" s="5"/>
+      <c r="ACX26" s="5"/>
+      <c r="ACZ26" s="5"/>
+      <c r="ADB26" s="5"/>
+      <c r="ADD26" s="5"/>
+      <c r="ADF26" s="5"/>
+      <c r="ADH26" s="5"/>
+      <c r="ADJ26" s="5"/>
+      <c r="ADL26" s="5"/>
+      <c r="ADN26" s="5"/>
+      <c r="ADP26" s="5"/>
+      <c r="ADR26" s="5"/>
+      <c r="ADT26" s="5"/>
+      <c r="ADV26" s="5"/>
+      <c r="ADX26" s="5"/>
+      <c r="ADZ26" s="5"/>
+      <c r="AEB26" s="5"/>
+      <c r="AED26" s="5"/>
+      <c r="AEF26" s="5"/>
+      <c r="AEH26" s="5"/>
+      <c r="AEJ26" s="5"/>
+      <c r="AEL26" s="5"/>
+      <c r="AEN26" s="5"/>
+      <c r="AEP26" s="5"/>
+      <c r="AER26" s="5"/>
+      <c r="AET26" s="5"/>
+      <c r="AEV26" s="5"/>
+      <c r="AEX26" s="5"/>
+      <c r="AEZ26" s="5"/>
+      <c r="AFB26" s="5"/>
+      <c r="AFD26" s="5"/>
+      <c r="AFF26" s="5"/>
+      <c r="AFH26" s="5"/>
+      <c r="AFJ26" s="5"/>
+      <c r="AFL26" s="5"/>
+      <c r="AFN26" s="5"/>
+      <c r="AFP26" s="5"/>
+      <c r="AFR26" s="5"/>
+      <c r="AFT26" s="5"/>
+      <c r="AFV26" s="5"/>
+      <c r="AFX26" s="5"/>
+      <c r="AFZ26" s="5"/>
+      <c r="AGB26" s="5"/>
+      <c r="AGD26" s="5"/>
+      <c r="AGF26" s="5"/>
+      <c r="AGH26" s="5"/>
+      <c r="AGJ26" s="5"/>
+      <c r="AGL26" s="5"/>
+      <c r="AGN26" s="5"/>
+      <c r="AGP26" s="5"/>
+      <c r="AGR26" s="5"/>
+      <c r="AGT26" s="5"/>
+      <c r="AGV26" s="5"/>
+      <c r="AGX26" s="5"/>
+      <c r="AGZ26" s="5"/>
+      <c r="AHB26" s="5"/>
+      <c r="AHD26" s="5"/>
+      <c r="AHF26" s="5"/>
+      <c r="AHH26" s="5"/>
+      <c r="AHJ26" s="5"/>
+      <c r="AHL26" s="5"/>
+      <c r="AHN26" s="5"/>
+      <c r="AHP26" s="5"/>
+      <c r="AHR26" s="5"/>
+      <c r="AHT26" s="5"/>
+      <c r="AHV26" s="5"/>
+      <c r="AHX26" s="5"/>
+      <c r="AHZ26" s="5"/>
+      <c r="AIB26" s="5"/>
+      <c r="AID26" s="5"/>
+      <c r="AIF26" s="5"/>
+      <c r="AIH26" s="5"/>
+      <c r="AIJ26" s="5"/>
+      <c r="AIL26" s="5"/>
+      <c r="AIN26" s="5"/>
+      <c r="AIP26" s="5"/>
+      <c r="AIR26" s="5"/>
+      <c r="AIT26" s="5"/>
+      <c r="AIV26" s="5"/>
+      <c r="AIX26" s="5"/>
+      <c r="AIZ26" s="5"/>
+      <c r="AJB26" s="5"/>
+      <c r="AJD26" s="5"/>
+      <c r="AJF26" s="5"/>
+      <c r="AJH26" s="5"/>
+      <c r="AJJ26" s="5"/>
+      <c r="AJL26" s="5"/>
+      <c r="AJN26" s="5"/>
+      <c r="AJP26" s="5"/>
+      <c r="AJR26" s="5"/>
+      <c r="AJT26" s="5"/>
+      <c r="AJV26" s="5"/>
+      <c r="AJX26" s="5"/>
+      <c r="AJZ26" s="5"/>
+      <c r="AKB26" s="5"/>
+      <c r="AKD26" s="5"/>
+      <c r="AKF26" s="5"/>
+      <c r="AKH26" s="5"/>
+      <c r="AKJ26" s="5"/>
+      <c r="AKL26" s="5"/>
+      <c r="AKN26" s="5"/>
+      <c r="AKP26" s="5"/>
+      <c r="AKR26" s="5"/>
+      <c r="AKT26" s="5"/>
+      <c r="AKV26" s="5"/>
+      <c r="AKX26" s="5"/>
+      <c r="AKZ26" s="5"/>
+      <c r="ALB26" s="5"/>
+      <c r="ALD26" s="5"/>
+      <c r="ALF26" s="5"/>
+      <c r="ALH26" s="5"/>
+      <c r="ALJ26" s="5"/>
+      <c r="ALL26" s="5"/>
+      <c r="ALN26" s="5"/>
+      <c r="ALP26" s="5"/>
+      <c r="ALR26" s="5"/>
+      <c r="ALT26" s="5"/>
+      <c r="ALV26" s="5"/>
+      <c r="ALX26" s="5"/>
+      <c r="ALZ26" s="5"/>
+      <c r="AMB26" s="5"/>
+      <c r="AMD26" s="5"/>
+      <c r="AMF26" s="5"/>
+      <c r="AMH26" s="5"/>
+      <c r="AMJ26" s="5"/>
+      <c r="AML26" s="5"/>
+      <c r="AMN26" s="5"/>
+      <c r="AMP26" s="5"/>
+      <c r="AMR26" s="5"/>
+      <c r="AMT26" s="5"/>
+      <c r="AMV26" s="5"/>
+      <c r="AMX26" s="5"/>
+      <c r="AMZ26" s="5"/>
+      <c r="ANB26" s="5"/>
+      <c r="AND26" s="5"/>
+      <c r="ANF26" s="5"/>
+      <c r="ANH26" s="5"/>
+      <c r="ANJ26" s="5"/>
+      <c r="ANL26" s="5"/>
+      <c r="ANN26" s="5"/>
+      <c r="ANP26" s="5"/>
+      <c r="ANR26" s="5"/>
+      <c r="ANT26" s="5"/>
+      <c r="ANV26" s="5"/>
+      <c r="ANX26" s="5"/>
+      <c r="ANZ26" s="5"/>
+      <c r="AOB26" s="5"/>
+      <c r="AOD26" s="5"/>
+      <c r="AOF26" s="5"/>
+      <c r="AOH26" s="5"/>
+      <c r="AOJ26" s="5"/>
+      <c r="AOL26" s="5"/>
+      <c r="AON26" s="5"/>
+      <c r="AOP26" s="5"/>
+      <c r="AOR26" s="5"/>
+      <c r="AOT26" s="5"/>
+      <c r="AOV26" s="5"/>
+      <c r="AOX26" s="5"/>
+      <c r="AOZ26" s="5"/>
+      <c r="APB26" s="5"/>
+      <c r="APD26" s="5"/>
+      <c r="APF26" s="5"/>
+      <c r="APH26" s="5"/>
+      <c r="APJ26" s="5"/>
+      <c r="APL26" s="5"/>
+      <c r="APN26" s="5"/>
+      <c r="APP26" s="5"/>
+      <c r="APR26" s="5"/>
+      <c r="APT26" s="5"/>
+      <c r="APV26" s="5"/>
+      <c r="APX26" s="5"/>
+      <c r="APZ26" s="5"/>
+      <c r="AQB26" s="5"/>
+      <c r="AQD26" s="5"/>
+      <c r="AQF26" s="5"/>
+      <c r="AQH26" s="5"/>
+      <c r="AQJ26" s="5"/>
+      <c r="AQL26" s="5"/>
+      <c r="AQN26" s="5"/>
+      <c r="AQP26" s="5"/>
+      <c r="AQR26" s="5"/>
+      <c r="AQT26" s="5"/>
+      <c r="AQV26" s="5"/>
+      <c r="AQX26" s="5"/>
+      <c r="AQZ26" s="5"/>
+      <c r="ARB26" s="5"/>
+      <c r="ARD26" s="5"/>
+      <c r="ARF26" s="5"/>
+      <c r="ARH26" s="5"/>
+      <c r="ARJ26" s="5"/>
+      <c r="ARL26" s="5"/>
+      <c r="ARN26" s="5"/>
+      <c r="ARP26" s="5"/>
+      <c r="ARR26" s="5"/>
+      <c r="ART26" s="5"/>
+      <c r="ARV26" s="5"/>
+      <c r="ARX26" s="5"/>
+      <c r="ARZ26" s="5"/>
+      <c r="ASB26" s="5"/>
+      <c r="ASD26" s="5"/>
+      <c r="ASF26" s="5"/>
+      <c r="ASH26" s="5"/>
+      <c r="ASJ26" s="5"/>
+      <c r="ASL26" s="5"/>
+      <c r="ASN26" s="5"/>
+      <c r="ASP26" s="5"/>
+      <c r="ASR26" s="5"/>
+      <c r="AST26" s="5"/>
+      <c r="ASV26" s="5"/>
+      <c r="ASX26" s="5"/>
+      <c r="ASZ26" s="5"/>
+      <c r="ATB26" s="5"/>
+      <c r="ATD26" s="5"/>
+      <c r="ATF26" s="5"/>
+      <c r="ATH26" s="5"/>
+      <c r="ATJ26" s="5"/>
+      <c r="ATL26" s="5"/>
+      <c r="ATN26" s="5"/>
+      <c r="ATP26" s="5"/>
+      <c r="ATR26" s="5"/>
+      <c r="ATT26" s="5"/>
+      <c r="ATV26" s="5"/>
+      <c r="ATX26" s="5"/>
+      <c r="ATZ26" s="5"/>
+      <c r="AUB26" s="5"/>
+      <c r="AUD26" s="5"/>
+      <c r="AUF26" s="5"/>
+      <c r="AUH26" s="5"/>
+      <c r="AUJ26" s="5"/>
+      <c r="AUL26" s="5"/>
+      <c r="AUN26" s="5"/>
+      <c r="AUP26" s="5"/>
+      <c r="AUR26" s="5"/>
+      <c r="AUT26" s="5"/>
+      <c r="AUV26" s="5"/>
+      <c r="AUX26" s="5"/>
+      <c r="AUZ26" s="5"/>
+      <c r="AVB26" s="5"/>
+      <c r="AVD26" s="5"/>
+      <c r="AVF26" s="5"/>
+      <c r="AVH26" s="5"/>
+      <c r="AVJ26" s="5"/>
+      <c r="AVL26" s="5"/>
+      <c r="AVN26" s="5"/>
+      <c r="AVP26" s="5"/>
+      <c r="AVR26" s="5"/>
+      <c r="AVT26" s="5"/>
+      <c r="AVV26" s="5"/>
+      <c r="AVX26" s="5"/>
+      <c r="AVZ26" s="5"/>
+      <c r="AWB26" s="5"/>
+      <c r="AWD26" s="5"/>
+      <c r="AWF26" s="5"/>
+      <c r="AWH26" s="5"/>
+      <c r="AWJ26" s="5"/>
+      <c r="AWL26" s="5"/>
+      <c r="AWN26" s="5"/>
+      <c r="AWP26" s="5"/>
+      <c r="AWR26" s="5"/>
+      <c r="AWT26" s="5"/>
+      <c r="AWV26" s="5"/>
+      <c r="AWX26" s="5"/>
+      <c r="AWZ26" s="5"/>
+      <c r="AXB26" s="5"/>
+      <c r="AXD26" s="5"/>
+      <c r="AXF26" s="5"/>
+      <c r="AXH26" s="5"/>
+      <c r="AXJ26" s="5"/>
+      <c r="AXL26" s="5"/>
+      <c r="AXN26" s="5"/>
+      <c r="AXP26" s="5"/>
+      <c r="AXR26" s="5"/>
+      <c r="AXT26" s="5"/>
+      <c r="AXV26" s="5"/>
+      <c r="AXX26" s="5"/>
+      <c r="AXZ26" s="5"/>
+      <c r="AYB26" s="5"/>
+      <c r="AYD26" s="5"/>
+      <c r="AYF26" s="5"/>
+      <c r="AYH26" s="5"/>
+      <c r="AYJ26" s="5"/>
+      <c r="AYL26" s="5"/>
+      <c r="AYN26" s="5"/>
+      <c r="AYP26" s="5"/>
+      <c r="AYR26" s="5"/>
+      <c r="AYT26" s="5"/>
+      <c r="AYV26" s="5"/>
+      <c r="AYX26" s="5"/>
+      <c r="AYZ26" s="5"/>
+      <c r="AZB26" s="5"/>
+      <c r="AZD26" s="5"/>
+      <c r="AZF26" s="5"/>
+      <c r="AZH26" s="5"/>
+      <c r="AZJ26" s="5"/>
+      <c r="AZL26" s="5"/>
+      <c r="AZN26" s="5"/>
+      <c r="AZP26" s="5"/>
+      <c r="AZR26" s="5"/>
+      <c r="AZT26" s="5"/>
+      <c r="AZV26" s="5"/>
+      <c r="AZX26" s="5"/>
+      <c r="AZZ26" s="5"/>
+      <c r="BAB26" s="5"/>
+      <c r="BAD26" s="5"/>
+      <c r="BAF26" s="5"/>
+      <c r="BAH26" s="5"/>
+      <c r="BAJ26" s="5"/>
+      <c r="BAL26" s="5"/>
+      <c r="BAN26" s="5"/>
+      <c r="BAP26" s="5"/>
+      <c r="BAR26" s="5"/>
+      <c r="BAT26" s="5"/>
+      <c r="BAV26" s="5"/>
+      <c r="BAX26" s="5"/>
+      <c r="BAZ26" s="5"/>
+      <c r="BBB26" s="5"/>
+      <c r="BBD26" s="5"/>
+      <c r="BBF26" s="5"/>
+      <c r="BBH26" s="5"/>
+      <c r="BBJ26" s="5"/>
+      <c r="BBL26" s="5"/>
+      <c r="BBN26" s="5"/>
+      <c r="BBP26" s="5"/>
+      <c r="BBR26" s="5"/>
+      <c r="BBT26" s="5"/>
+      <c r="BBV26" s="5"/>
+      <c r="BBX26" s="5"/>
+      <c r="BBZ26" s="5"/>
+      <c r="BCB26" s="5"/>
+      <c r="BCD26" s="5"/>
+      <c r="BCF26" s="5"/>
+      <c r="BCH26" s="5"/>
+      <c r="BCJ26" s="5"/>
+      <c r="BCL26" s="5"/>
+      <c r="BCN26" s="5"/>
+      <c r="BCP26" s="5"/>
+      <c r="BCR26" s="5"/>
+      <c r="BCT26" s="5"/>
+      <c r="BCV26" s="5"/>
+      <c r="BCX26" s="5"/>
+      <c r="BCZ26" s="5"/>
+      <c r="BDB26" s="5"/>
+      <c r="BDD26" s="5"/>
+      <c r="BDF26" s="5"/>
+      <c r="BDH26" s="5"/>
+      <c r="BDJ26" s="5"/>
+      <c r="BDL26" s="5"/>
+      <c r="BDN26" s="5"/>
+      <c r="BDP26" s="5"/>
+      <c r="BDR26" s="5"/>
+      <c r="BDT26" s="5"/>
+      <c r="BDV26" s="5"/>
+      <c r="BDX26" s="5"/>
+      <c r="BDZ26" s="5"/>
+      <c r="BEB26" s="5"/>
+      <c r="BED26" s="5"/>
+      <c r="BEF26" s="5"/>
+      <c r="BEH26" s="5"/>
+      <c r="BEJ26" s="5"/>
+      <c r="BEL26" s="5"/>
+      <c r="BEN26" s="5"/>
+      <c r="BEP26" s="5"/>
+      <c r="BER26" s="5"/>
+      <c r="BET26" s="5"/>
+      <c r="BEV26" s="5"/>
+      <c r="BEX26" s="5"/>
+      <c r="BEZ26" s="5"/>
+      <c r="BFB26" s="5"/>
+      <c r="BFD26" s="5"/>
+      <c r="BFF26" s="5"/>
+      <c r="BFH26" s="5"/>
+      <c r="BFJ26" s="5"/>
+      <c r="BFL26" s="5"/>
+      <c r="BFN26" s="5"/>
+      <c r="BFP26" s="5"/>
+      <c r="BFR26" s="5"/>
+      <c r="BFT26" s="5"/>
+      <c r="BFV26" s="5"/>
+      <c r="BFX26" s="5"/>
+      <c r="BFZ26" s="5"/>
+      <c r="BGB26" s="5"/>
+      <c r="BGD26" s="5"/>
+      <c r="BGF26" s="5"/>
+      <c r="BGH26" s="5"/>
+      <c r="BGJ26" s="5"/>
+      <c r="BGL26" s="5"/>
+      <c r="BGN26" s="5"/>
+      <c r="BGP26" s="5"/>
+      <c r="BGR26" s="5"/>
+      <c r="BGT26" s="5"/>
+      <c r="BGV26" s="5"/>
+      <c r="BGX26" s="5"/>
+      <c r="BGZ26" s="5"/>
+      <c r="BHB26" s="5"/>
+      <c r="BHD26" s="5"/>
+      <c r="BHF26" s="5"/>
+      <c r="BHH26" s="5"/>
+      <c r="BHJ26" s="5"/>
+      <c r="BHL26" s="5"/>
+      <c r="BHN26" s="5"/>
+      <c r="BHP26" s="5"/>
+      <c r="BHR26" s="5"/>
+      <c r="BHT26" s="5"/>
+      <c r="BHV26" s="5"/>
+      <c r="BHX26" s="5"/>
+      <c r="BHZ26" s="5"/>
+      <c r="BIB26" s="5"/>
+      <c r="BID26" s="5"/>
+      <c r="BIF26" s="5"/>
+      <c r="BIH26" s="5"/>
+      <c r="BIJ26" s="5"/>
+      <c r="BIL26" s="5"/>
+      <c r="BIN26" s="5"/>
+      <c r="BIP26" s="5"/>
+      <c r="BIR26" s="5"/>
+      <c r="BIT26" s="5"/>
+      <c r="BIV26" s="5"/>
+      <c r="BIX26" s="5"/>
+      <c r="BIZ26" s="5"/>
+      <c r="BJB26" s="5"/>
+      <c r="BJD26" s="5"/>
+      <c r="BJF26" s="5"/>
+      <c r="BJH26" s="5"/>
+      <c r="BJJ26" s="5"/>
+      <c r="BJL26" s="5"/>
+      <c r="BJN26" s="5"/>
+      <c r="BJP26" s="5"/>
+      <c r="BJR26" s="5"/>
+      <c r="BJT26" s="5"/>
+      <c r="BJV26" s="5"/>
+      <c r="BJX26" s="5"/>
+      <c r="BJZ26" s="5"/>
+      <c r="BKB26" s="5"/>
+      <c r="BKD26" s="5"/>
+      <c r="BKF26" s="5"/>
+      <c r="BKH26" s="5"/>
+      <c r="BKJ26" s="5"/>
+      <c r="BKL26" s="5"/>
+      <c r="BKN26" s="5"/>
+      <c r="BKP26" s="5"/>
+      <c r="BKR26" s="5"/>
+      <c r="BKT26" s="5"/>
+      <c r="BKV26" s="5"/>
+      <c r="BKX26" s="5"/>
+      <c r="BKZ26" s="5"/>
+      <c r="BLB26" s="5"/>
+      <c r="BLD26" s="5"/>
+      <c r="BLF26" s="5"/>
+      <c r="BLH26" s="5"/>
+      <c r="BLJ26" s="5"/>
+      <c r="BLL26" s="5"/>
+      <c r="BLN26" s="5"/>
+      <c r="BLP26" s="5"/>
+      <c r="BLR26" s="5"/>
+      <c r="BLT26" s="5"/>
+      <c r="BLV26" s="5"/>
+      <c r="BLX26" s="5"/>
+      <c r="BLZ26" s="5"/>
+      <c r="BMB26" s="5"/>
+      <c r="BMD26" s="5"/>
+      <c r="BMF26" s="5"/>
+      <c r="BMH26" s="5"/>
+      <c r="BMJ26" s="5"/>
+      <c r="BML26" s="5"/>
+      <c r="BMN26" s="5"/>
+      <c r="BMP26" s="5"/>
+      <c r="BMR26" s="5"/>
+      <c r="BMT26" s="5"/>
+      <c r="BMV26" s="5"/>
+      <c r="BMX26" s="5"/>
+      <c r="BMZ26" s="5"/>
+      <c r="BNB26" s="5"/>
+      <c r="BND26" s="5"/>
+      <c r="BNF26" s="5"/>
+      <c r="BNH26" s="5"/>
+      <c r="BNJ26" s="5"/>
+      <c r="BNL26" s="5"/>
+      <c r="BNN26" s="5"/>
+      <c r="BNP26" s="5"/>
+      <c r="BNR26" s="5"/>
+      <c r="BNT26" s="5"/>
+      <c r="BNV26" s="5"/>
+      <c r="BNX26" s="5"/>
+      <c r="BNZ26" s="5"/>
+      <c r="BOB26" s="5"/>
+      <c r="BOD26" s="5"/>
+      <c r="BOF26" s="5"/>
+      <c r="BOH26" s="5"/>
+      <c r="BOJ26" s="5"/>
+      <c r="BOL26" s="5"/>
+      <c r="BON26" s="5"/>
+      <c r="BOP26" s="5"/>
+      <c r="BOR26" s="5"/>
+      <c r="BOT26" s="5"/>
+      <c r="BOV26" s="5"/>
+      <c r="BOX26" s="5"/>
+      <c r="BOZ26" s="5"/>
+      <c r="BPB26" s="5"/>
+      <c r="BPD26" s="5"/>
+      <c r="BPF26" s="5"/>
+      <c r="BPH26" s="5"/>
+      <c r="BPJ26" s="5"/>
+      <c r="BPL26" s="5"/>
+      <c r="BPN26" s="5"/>
+      <c r="BPP26" s="5"/>
+      <c r="BPR26" s="5"/>
+      <c r="BPT26" s="5"/>
+      <c r="BPV26" s="5"/>
+      <c r="BPX26" s="5"/>
+      <c r="BPZ26" s="5"/>
+      <c r="BQB26" s="5"/>
+      <c r="BQD26" s="5"/>
+      <c r="BQF26" s="5"/>
+      <c r="BQH26" s="5"/>
+      <c r="BQJ26" s="5"/>
+      <c r="BQL26" s="5"/>
+      <c r="BQN26" s="5"/>
+      <c r="BQP26" s="5"/>
+      <c r="BQR26" s="5"/>
+      <c r="BQT26" s="5"/>
+      <c r="BQV26" s="5"/>
+      <c r="BQX26" s="5"/>
+      <c r="BQZ26" s="5"/>
+      <c r="BRB26" s="5"/>
+      <c r="BRD26" s="5"/>
+      <c r="BRF26" s="5"/>
+      <c r="BRH26" s="5"/>
+      <c r="BRJ26" s="5"/>
+      <c r="BRL26" s="5"/>
+      <c r="BRN26" s="5"/>
+      <c r="BRP26" s="5"/>
+      <c r="BRR26" s="5"/>
+      <c r="BRT26" s="5"/>
+      <c r="BRV26" s="5"/>
+      <c r="BRX26" s="5"/>
+      <c r="BRZ26" s="5"/>
+      <c r="BSB26" s="5"/>
+      <c r="BSD26" s="5"/>
+      <c r="BSF26" s="5"/>
+      <c r="BSH26" s="5"/>
+      <c r="BSJ26" s="5"/>
+      <c r="BSL26" s="5"/>
+      <c r="BSN26" s="5"/>
+      <c r="BSP26" s="5"/>
+      <c r="BSR26" s="5"/>
+      <c r="BST26" s="5"/>
+      <c r="BSV26" s="5"/>
+      <c r="BSX26" s="5"/>
+      <c r="BSZ26" s="5"/>
+      <c r="BTB26" s="5"/>
+      <c r="BTD26" s="5"/>
+      <c r="BTF26" s="5"/>
+      <c r="BTH26" s="5"/>
+      <c r="BTJ26" s="5"/>
+      <c r="BTL26" s="5"/>
+      <c r="BTN26" s="5"/>
+      <c r="BTP26" s="5"/>
+      <c r="BTR26" s="5"/>
+      <c r="BTT26" s="5"/>
+      <c r="BTV26" s="5"/>
+      <c r="BTX26" s="5"/>
+      <c r="BTZ26" s="5"/>
+      <c r="BUB26" s="5"/>
+      <c r="BUD26" s="5"/>
+      <c r="BUF26" s="5"/>
+      <c r="BUH26" s="5"/>
+      <c r="BUJ26" s="5"/>
+      <c r="BUL26" s="5"/>
+      <c r="BUN26" s="5"/>
+      <c r="BUP26" s="5"/>
+      <c r="BUR26" s="5"/>
+      <c r="BUT26" s="5"/>
+      <c r="BUV26" s="5"/>
+      <c r="BUX26" s="5"/>
+      <c r="BUZ26" s="5"/>
+      <c r="BVB26" s="5"/>
+      <c r="BVD26" s="5"/>
+      <c r="BVF26" s="5"/>
+      <c r="BVH26" s="5"/>
+      <c r="BVJ26" s="5"/>
+      <c r="BVL26" s="5"/>
+      <c r="BVN26" s="5"/>
+      <c r="BVP26" s="5"/>
+      <c r="BVR26" s="5"/>
+      <c r="BVT26" s="5"/>
+      <c r="BVV26" s="5"/>
+      <c r="BVX26" s="5"/>
+      <c r="BVZ26" s="5"/>
+      <c r="BWB26" s="5"/>
+      <c r="BWD26" s="5"/>
+      <c r="BWF26" s="5"/>
+      <c r="BWH26" s="5"/>
+      <c r="BWJ26" s="5"/>
+      <c r="BWL26" s="5"/>
+      <c r="BWN26" s="5"/>
+      <c r="BWP26" s="5"/>
+      <c r="BWR26" s="5"/>
+      <c r="BWT26" s="5"/>
+      <c r="BWV26" s="5"/>
+      <c r="BWX26" s="5"/>
+      <c r="BWZ26" s="5"/>
+      <c r="BXB26" s="5"/>
+      <c r="BXD26" s="5"/>
+      <c r="BXF26" s="5"/>
+      <c r="BXH26" s="5"/>
+      <c r="BXJ26" s="5"/>
+      <c r="BXL26" s="5"/>
+      <c r="BXN26" s="5"/>
+      <c r="BXP26" s="5"/>
+      <c r="BXR26" s="5"/>
+      <c r="BXT26" s="5"/>
+      <c r="BXV26" s="5"/>
+      <c r="BXX26" s="5"/>
+      <c r="BXZ26" s="5"/>
+      <c r="BYB26" s="5"/>
+      <c r="BYD26" s="5"/>
+      <c r="BYF26" s="5"/>
+      <c r="BYH26" s="5"/>
+      <c r="BYJ26" s="5"/>
+      <c r="BYL26" s="5"/>
+      <c r="BYN26" s="5"/>
+      <c r="BYP26" s="5"/>
+      <c r="BYR26" s="5"/>
+      <c r="BYT26" s="5"/>
+      <c r="BYV26" s="5"/>
+      <c r="BYX26" s="5"/>
+      <c r="BYZ26" s="5"/>
+      <c r="BZB26" s="5"/>
+      <c r="BZD26" s="5"/>
+      <c r="BZF26" s="5"/>
+      <c r="BZH26" s="5"/>
+      <c r="BZJ26" s="5"/>
+      <c r="BZL26" s="5"/>
+      <c r="BZN26" s="5"/>
+      <c r="BZP26" s="5"/>
+      <c r="BZR26" s="5"/>
+      <c r="BZT26" s="5"/>
+      <c r="BZV26" s="5"/>
+      <c r="BZX26" s="5"/>
+      <c r="BZZ26" s="5"/>
+      <c r="CAB26" s="5"/>
+      <c r="CAD26" s="5"/>
+      <c r="CAF26" s="5"/>
+      <c r="CAH26" s="5"/>
+      <c r="CAJ26" s="5"/>
+      <c r="CAL26" s="5"/>
+      <c r="CAN26" s="5"/>
+      <c r="CAP26" s="5"/>
+      <c r="CAR26" s="5"/>
+      <c r="CAT26" s="5"/>
+      <c r="CAV26" s="5"/>
+      <c r="CAX26" s="5"/>
+      <c r="CAZ26" s="5"/>
+      <c r="CBB26" s="5"/>
+      <c r="CBD26" s="5"/>
+      <c r="CBF26" s="5"/>
+      <c r="CBH26" s="5"/>
+      <c r="CBJ26" s="5"/>
+      <c r="CBL26" s="5"/>
+      <c r="CBN26" s="5"/>
+      <c r="CBP26" s="5"/>
+      <c r="CBR26" s="5"/>
+      <c r="CBT26" s="5"/>
+      <c r="CBV26" s="5"/>
+      <c r="CBX26" s="5"/>
+      <c r="CBZ26" s="5"/>
+      <c r="CCB26" s="5"/>
+      <c r="CCD26" s="5"/>
+      <c r="CCF26" s="5"/>
+      <c r="CCH26" s="5"/>
+      <c r="CCJ26" s="5"/>
+      <c r="CCL26" s="5"/>
+      <c r="CCN26" s="5"/>
+      <c r="CCP26" s="5"/>
+      <c r="CCR26" s="5"/>
+      <c r="CCT26" s="5"/>
+      <c r="CCV26" s="5"/>
+      <c r="CCX26" s="5"/>
+      <c r="CCZ26" s="5"/>
+      <c r="CDB26" s="5"/>
+      <c r="CDD26" s="5"/>
+      <c r="CDF26" s="5"/>
+      <c r="CDH26" s="5"/>
+      <c r="CDJ26" s="5"/>
+      <c r="CDL26" s="5"/>
+      <c r="CDN26" s="5"/>
+      <c r="CDP26" s="5"/>
+      <c r="CDR26" s="5"/>
+      <c r="CDT26" s="5"/>
+      <c r="CDV26" s="5"/>
+      <c r="CDX26" s="5"/>
+      <c r="CDZ26" s="5"/>
+      <c r="CEB26" s="5"/>
+      <c r="CED26" s="5"/>
+      <c r="CEF26" s="5"/>
+      <c r="CEH26" s="5"/>
+      <c r="CEJ26" s="5"/>
+      <c r="CEL26" s="5"/>
+      <c r="CEN26" s="5"/>
+      <c r="CEP26" s="5"/>
+      <c r="CER26" s="5"/>
+      <c r="CET26" s="5"/>
+      <c r="CEV26" s="5"/>
+      <c r="CEX26" s="5"/>
+      <c r="CEZ26" s="5"/>
+      <c r="CFB26" s="5"/>
+      <c r="CFD26" s="5"/>
+      <c r="CFF26" s="5"/>
+      <c r="CFH26" s="5"/>
+      <c r="CFJ26" s="5"/>
+      <c r="CFL26" s="5"/>
+      <c r="CFN26" s="5"/>
+      <c r="CFP26" s="5"/>
+      <c r="CFR26" s="5"/>
+      <c r="CFT26" s="5"/>
+      <c r="CFV26" s="5"/>
+      <c r="CFX26" s="5"/>
+      <c r="CFZ26" s="5"/>
+      <c r="CGB26" s="5"/>
+      <c r="CGD26" s="5"/>
+      <c r="CGF26" s="5"/>
+      <c r="CGH26" s="5"/>
+      <c r="CGJ26" s="5"/>
+      <c r="CGL26" s="5"/>
+      <c r="CGN26" s="5"/>
+      <c r="CGP26" s="5"/>
+      <c r="CGR26" s="5"/>
+      <c r="CGT26" s="5"/>
+      <c r="CGV26" s="5"/>
+      <c r="CGX26" s="5"/>
+      <c r="CGZ26" s="5"/>
+      <c r="CHB26" s="5"/>
+      <c r="CHD26" s="5"/>
+      <c r="CHF26" s="5"/>
+      <c r="CHH26" s="5"/>
+      <c r="CHJ26" s="5"/>
+      <c r="CHL26" s="5"/>
+      <c r="CHN26" s="5"/>
+      <c r="CHP26" s="5"/>
+      <c r="CHR26" s="5"/>
+      <c r="CHT26" s="5"/>
+      <c r="CHV26" s="5"/>
+      <c r="CHX26" s="5"/>
+      <c r="CHZ26" s="5"/>
+      <c r="CIB26" s="5"/>
+      <c r="CID26" s="5"/>
+      <c r="CIF26" s="5"/>
+      <c r="CIH26" s="5"/>
+      <c r="CIJ26" s="5"/>
+      <c r="CIL26" s="5"/>
+      <c r="CIN26" s="5"/>
+      <c r="CIP26" s="5"/>
+      <c r="CIR26" s="5"/>
+      <c r="CIT26" s="5"/>
+      <c r="CIV26" s="5"/>
+      <c r="CIX26" s="5"/>
+      <c r="CIZ26" s="5"/>
+      <c r="CJB26" s="5"/>
+      <c r="CJD26" s="5"/>
+      <c r="CJF26" s="5"/>
+      <c r="CJH26" s="5"/>
+      <c r="CJJ26" s="5"/>
+      <c r="CJL26" s="5"/>
+      <c r="CJN26" s="5"/>
+      <c r="CJP26" s="5"/>
+      <c r="CJR26" s="5"/>
+      <c r="CJT26" s="5"/>
+      <c r="CJV26" s="5"/>
+      <c r="CJX26" s="5"/>
+      <c r="CJZ26" s="5"/>
+      <c r="CKB26" s="5"/>
+      <c r="CKD26" s="5"/>
+      <c r="CKF26" s="5"/>
+      <c r="CKH26" s="5"/>
+      <c r="CKJ26" s="5"/>
+      <c r="CKL26" s="5"/>
+      <c r="CKN26" s="5"/>
+      <c r="CKP26" s="5"/>
+      <c r="CKR26" s="5"/>
+      <c r="CKT26" s="5"/>
+      <c r="CKV26" s="5"/>
+      <c r="CKX26" s="5"/>
+      <c r="CKZ26" s="5"/>
+      <c r="CLB26" s="5"/>
+      <c r="CLD26" s="5"/>
+      <c r="CLF26" s="5"/>
+      <c r="CLH26" s="5"/>
+      <c r="CLJ26" s="5"/>
+      <c r="CLL26" s="5"/>
+      <c r="CLN26" s="5"/>
+      <c r="CLP26" s="5"/>
+      <c r="CLR26" s="5"/>
+      <c r="CLT26" s="5"/>
+      <c r="CLV26" s="5"/>
+      <c r="CLX26" s="5"/>
+      <c r="CLZ26" s="5"/>
+      <c r="CMB26" s="5"/>
+      <c r="CMD26" s="5"/>
+      <c r="CMF26" s="5"/>
+      <c r="CMH26" s="5"/>
+      <c r="CMJ26" s="5"/>
+      <c r="CML26" s="5"/>
+      <c r="CMN26" s="5"/>
+      <c r="CMP26" s="5"/>
+      <c r="CMR26" s="5"/>
+      <c r="CMT26" s="5"/>
+      <c r="CMV26" s="5"/>
+      <c r="CMX26" s="5"/>
+      <c r="CMZ26" s="5"/>
+      <c r="CNB26" s="5"/>
+      <c r="CND26" s="5"/>
+      <c r="CNF26" s="5"/>
+      <c r="CNH26" s="5"/>
+      <c r="CNJ26" s="5"/>
+      <c r="CNL26" s="5"/>
+      <c r="CNN26" s="5"/>
+      <c r="CNP26" s="5"/>
+      <c r="CNR26" s="5"/>
+      <c r="CNT26" s="5"/>
+      <c r="CNV26" s="5"/>
+      <c r="CNX26" s="5"/>
+      <c r="CNZ26" s="5"/>
+      <c r="COB26" s="5"/>
+      <c r="COD26" s="5"/>
+      <c r="COF26" s="5"/>
+      <c r="COH26" s="5"/>
+      <c r="COJ26" s="5"/>
+      <c r="COL26" s="5"/>
+      <c r="CON26" s="5"/>
+      <c r="COP26" s="5"/>
+      <c r="COR26" s="5"/>
+      <c r="COT26" s="5"/>
+      <c r="COV26" s="5"/>
+      <c r="COX26" s="5"/>
+      <c r="COZ26" s="5"/>
+      <c r="CPB26" s="5"/>
+      <c r="CPD26" s="5"/>
+      <c r="CPF26" s="5"/>
+      <c r="CPH26" s="5"/>
+      <c r="CPJ26" s="5"/>
+      <c r="CPL26" s="5"/>
+      <c r="CPN26" s="5"/>
+      <c r="CPP26" s="5"/>
+      <c r="CPR26" s="5"/>
+      <c r="CPT26" s="5"/>
+      <c r="CPV26" s="5"/>
+      <c r="CPX26" s="5"/>
+      <c r="CPZ26" s="5"/>
+      <c r="CQB26" s="5"/>
+      <c r="CQD26" s="5"/>
+      <c r="CQF26" s="5"/>
+      <c r="CQH26" s="5"/>
+      <c r="CQJ26" s="5"/>
+      <c r="CQL26" s="5"/>
+      <c r="CQN26" s="5"/>
+      <c r="CQP26" s="5"/>
+      <c r="CQR26" s="5"/>
+      <c r="CQT26" s="5"/>
+      <c r="CQV26" s="5"/>
+      <c r="CQX26" s="5"/>
+      <c r="CQZ26" s="5"/>
+      <c r="CRB26" s="5"/>
+      <c r="CRD26" s="5"/>
+      <c r="CRF26" s="5"/>
+      <c r="CRH26" s="5"/>
+      <c r="CRJ26" s="5"/>
+      <c r="CRL26" s="5"/>
+      <c r="CRN26" s="5"/>
+      <c r="CRP26" s="5"/>
+      <c r="CRR26" s="5"/>
+      <c r="CRT26" s="5"/>
+      <c r="CRV26" s="5"/>
+      <c r="CRX26" s="5"/>
+      <c r="CRZ26" s="5"/>
+      <c r="CSB26" s="5"/>
+      <c r="CSD26" s="5"/>
+      <c r="CSF26" s="5"/>
+      <c r="CSH26" s="5"/>
+      <c r="CSJ26" s="5"/>
+      <c r="CSL26" s="5"/>
+      <c r="CSN26" s="5"/>
+      <c r="CSP26" s="5"/>
+      <c r="CSR26" s="5"/>
+      <c r="CST26" s="5"/>
+      <c r="CSV26" s="5"/>
+      <c r="CSX26" s="5"/>
+      <c r="CSZ26" s="5"/>
+      <c r="CTB26" s="5"/>
+      <c r="CTD26" s="5"/>
+      <c r="CTF26" s="5"/>
+      <c r="CTH26" s="5"/>
+      <c r="CTJ26" s="5"/>
+      <c r="CTL26" s="5"/>
+      <c r="CTN26" s="5"/>
+      <c r="CTP26" s="5"/>
+      <c r="CTR26" s="5"/>
+      <c r="CTT26" s="5"/>
+      <c r="CTV26" s="5"/>
+      <c r="CTX26" s="5"/>
+      <c r="CTZ26" s="5"/>
+      <c r="CUB26" s="5"/>
+      <c r="CUD26" s="5"/>
+      <c r="CUF26" s="5"/>
+      <c r="CUH26" s="5"/>
+      <c r="CUJ26" s="5"/>
+      <c r="CUL26" s="5"/>
+      <c r="CUN26" s="5"/>
+      <c r="CUP26" s="5"/>
+      <c r="CUR26" s="5"/>
+      <c r="CUT26" s="5"/>
+      <c r="CUV26" s="5"/>
+      <c r="CUX26" s="5"/>
+      <c r="CUZ26" s="5"/>
+      <c r="CVB26" s="5"/>
+      <c r="CVD26" s="5"/>
+      <c r="CVF26" s="5"/>
+      <c r="CVH26" s="5"/>
+      <c r="CVJ26" s="5"/>
+      <c r="CVL26" s="5"/>
+      <c r="CVN26" s="5"/>
+      <c r="CVP26" s="5"/>
+      <c r="CVR26" s="5"/>
+      <c r="CVT26" s="5"/>
+      <c r="CVV26" s="5"/>
+      <c r="CVX26" s="5"/>
+      <c r="CVZ26" s="5"/>
+      <c r="CWB26" s="5"/>
+      <c r="CWD26" s="5"/>
+      <c r="CWF26" s="5"/>
+      <c r="CWH26" s="5"/>
+      <c r="CWJ26" s="5"/>
+      <c r="CWL26" s="5"/>
+      <c r="CWN26" s="5"/>
+      <c r="CWP26" s="5"/>
+      <c r="CWR26" s="5"/>
+      <c r="CWT26" s="5"/>
+      <c r="CWV26" s="5"/>
+      <c r="CWX26" s="5"/>
+      <c r="CWZ26" s="5"/>
+      <c r="CXB26" s="5"/>
+      <c r="CXD26" s="5"/>
+      <c r="CXF26" s="5"/>
+      <c r="CXH26" s="5"/>
+      <c r="CXJ26" s="5"/>
+      <c r="CXL26" s="5"/>
+      <c r="CXN26" s="5"/>
+      <c r="CXP26" s="5"/>
+      <c r="CXR26" s="5"/>
+      <c r="CXT26" s="5"/>
+      <c r="CXV26" s="5"/>
+      <c r="CXX26" s="5"/>
+      <c r="CXZ26" s="5"/>
+      <c r="CYB26" s="5"/>
+      <c r="CYD26" s="5"/>
+      <c r="CYF26" s="5"/>
+      <c r="CYH26" s="5"/>
+      <c r="CYJ26" s="5"/>
+      <c r="CYL26" s="5"/>
+      <c r="CYN26" s="5"/>
+      <c r="CYP26" s="5"/>
+      <c r="CYR26" s="5"/>
+      <c r="CYT26" s="5"/>
+      <c r="CYV26" s="5"/>
+      <c r="CYX26" s="5"/>
+      <c r="CYZ26" s="5"/>
+      <c r="CZB26" s="5"/>
+      <c r="CZD26" s="5"/>
+      <c r="CZF26" s="5"/>
+      <c r="CZH26" s="5"/>
+      <c r="CZJ26" s="5"/>
+      <c r="CZL26" s="5"/>
+      <c r="CZN26" s="5"/>
+      <c r="CZP26" s="5"/>
+      <c r="CZR26" s="5"/>
+      <c r="CZT26" s="5"/>
+      <c r="CZV26" s="5"/>
+      <c r="CZX26" s="5"/>
+      <c r="CZZ26" s="5"/>
+      <c r="DAB26" s="5"/>
+      <c r="DAD26" s="5"/>
+      <c r="DAF26" s="5"/>
+      <c r="DAH26" s="5"/>
+      <c r="DAJ26" s="5"/>
+      <c r="DAL26" s="5"/>
+      <c r="DAN26" s="5"/>
+      <c r="DAP26" s="5"/>
+      <c r="DAR26" s="5"/>
+      <c r="DAT26" s="5"/>
+      <c r="DAV26" s="5"/>
+      <c r="DAX26" s="5"/>
+      <c r="DAZ26" s="5"/>
+      <c r="DBB26" s="5"/>
+      <c r="DBD26" s="5"/>
+      <c r="DBF26" s="5"/>
+      <c r="DBH26" s="5"/>
+      <c r="DBJ26" s="5"/>
+      <c r="DBL26" s="5"/>
+      <c r="DBN26" s="5"/>
+      <c r="DBP26" s="5"/>
+      <c r="DBR26" s="5"/>
+      <c r="DBT26" s="5"/>
+      <c r="DBV26" s="5"/>
+      <c r="DBX26" s="5"/>
+      <c r="DBZ26" s="5"/>
+      <c r="DCB26" s="5"/>
+      <c r="DCD26" s="5"/>
+      <c r="DCF26" s="5"/>
+      <c r="DCH26" s="5"/>
+      <c r="DCJ26" s="5"/>
+      <c r="DCL26" s="5"/>
+      <c r="DCN26" s="5"/>
+      <c r="DCP26" s="5"/>
+      <c r="DCR26" s="5"/>
+      <c r="DCT26" s="5"/>
+      <c r="DCV26" s="5"/>
+      <c r="DCX26" s="5"/>
+      <c r="DCZ26" s="5"/>
+      <c r="DDB26" s="5"/>
+      <c r="DDD26" s="5"/>
+      <c r="DDF26" s="5"/>
+      <c r="DDH26" s="5"/>
+      <c r="DDJ26" s="5"/>
+      <c r="DDL26" s="5"/>
+      <c r="DDN26" s="5"/>
+      <c r="DDP26" s="5"/>
+      <c r="DDR26" s="5"/>
+      <c r="DDT26" s="5"/>
+      <c r="DDV26" s="5"/>
+      <c r="DDX26" s="5"/>
+      <c r="DDZ26" s="5"/>
+      <c r="DEB26" s="5"/>
+      <c r="DED26" s="5"/>
+      <c r="DEF26" s="5"/>
+      <c r="DEH26" s="5"/>
+      <c r="DEJ26" s="5"/>
+      <c r="DEL26" s="5"/>
+      <c r="DEN26" s="5"/>
+      <c r="DEP26" s="5"/>
+      <c r="DER26" s="5"/>
+      <c r="DET26" s="5"/>
+      <c r="DEV26" s="5"/>
+      <c r="DEX26" s="5"/>
+      <c r="DEZ26" s="5"/>
+      <c r="DFB26" s="5"/>
+      <c r="DFD26" s="5"/>
+      <c r="DFF26" s="5"/>
+      <c r="DFH26" s="5"/>
+      <c r="DFJ26" s="5"/>
+      <c r="DFL26" s="5"/>
+      <c r="DFN26" s="5"/>
+      <c r="DFP26" s="5"/>
+      <c r="DFR26" s="5"/>
+      <c r="DFT26" s="5"/>
+      <c r="DFV26" s="5"/>
+      <c r="DFX26" s="5"/>
+      <c r="DFZ26" s="5"/>
+      <c r="DGB26" s="5"/>
+      <c r="DGD26" s="5"/>
+      <c r="DGF26" s="5"/>
+      <c r="DGH26" s="5"/>
+      <c r="DGJ26" s="5"/>
+      <c r="DGL26" s="5"/>
+      <c r="DGN26" s="5"/>
+      <c r="DGP26" s="5"/>
+      <c r="DGR26" s="5"/>
+      <c r="DGT26" s="5"/>
+      <c r="DGV26" s="5"/>
+      <c r="DGX26" s="5"/>
+      <c r="DGZ26" s="5"/>
+      <c r="DHB26" s="5"/>
+      <c r="DHD26" s="5"/>
+      <c r="DHF26" s="5"/>
+      <c r="DHH26" s="5"/>
+      <c r="DHJ26" s="5"/>
+      <c r="DHL26" s="5"/>
+      <c r="DHN26" s="5"/>
+      <c r="DHP26" s="5"/>
+      <c r="DHR26" s="5"/>
+      <c r="DHT26" s="5"/>
+      <c r="DHV26" s="5"/>
+      <c r="DHX26" s="5"/>
+      <c r="DHZ26" s="5"/>
+      <c r="DIB26" s="5"/>
+      <c r="DID26" s="5"/>
+      <c r="DIF26" s="5"/>
+      <c r="DIH26" s="5"/>
+      <c r="DIJ26" s="5"/>
+      <c r="DIL26" s="5"/>
+      <c r="DIN26" s="5"/>
+      <c r="DIP26" s="5"/>
+      <c r="DIR26" s="5"/>
+      <c r="DIT26" s="5"/>
+      <c r="DIV26" s="5"/>
+      <c r="DIX26" s="5"/>
+      <c r="DIZ26" s="5"/>
+      <c r="DJB26" s="5"/>
+      <c r="DJD26" s="5"/>
+      <c r="DJF26" s="5"/>
+      <c r="DJH26" s="5"/>
+      <c r="DJJ26" s="5"/>
+      <c r="DJL26" s="5"/>
+      <c r="DJN26" s="5"/>
+      <c r="DJP26" s="5"/>
+      <c r="DJR26" s="5"/>
+      <c r="DJT26" s="5"/>
+      <c r="DJV26" s="5"/>
+      <c r="DJX26" s="5"/>
+      <c r="DJZ26" s="5"/>
+      <c r="DKB26" s="5"/>
+      <c r="DKD26" s="5"/>
+      <c r="DKF26" s="5"/>
+      <c r="DKH26" s="5"/>
+      <c r="DKJ26" s="5"/>
+      <c r="DKL26" s="5"/>
+      <c r="DKN26" s="5"/>
+      <c r="DKP26" s="5"/>
+      <c r="DKR26" s="5"/>
+      <c r="DKT26" s="5"/>
+      <c r="DKV26" s="5"/>
+      <c r="DKX26" s="5"/>
+      <c r="DKZ26" s="5"/>
+      <c r="DLB26" s="5"/>
+      <c r="DLD26" s="5"/>
+      <c r="DLF26" s="5"/>
+      <c r="DLH26" s="5"/>
+      <c r="DLJ26" s="5"/>
+      <c r="DLL26" s="5"/>
+      <c r="DLN26" s="5"/>
+      <c r="DLP26" s="5"/>
+      <c r="DLR26" s="5"/>
+      <c r="DLT26" s="5"/>
+      <c r="DLV26" s="5"/>
+      <c r="DLX26" s="5"/>
+      <c r="DLZ26" s="5"/>
+      <c r="DMB26" s="5"/>
+      <c r="DMD26" s="5"/>
+      <c r="DMF26" s="5"/>
+      <c r="DMH26" s="5"/>
+      <c r="DMJ26" s="5"/>
+      <c r="DML26" s="5"/>
+      <c r="DMN26" s="5"/>
+      <c r="DMP26" s="5"/>
+      <c r="DMR26" s="5"/>
+      <c r="DMT26" s="5"/>
+      <c r="DMV26" s="5"/>
+      <c r="DMX26" s="5"/>
+      <c r="DMZ26" s="5"/>
+      <c r="DNB26" s="5"/>
+      <c r="DND26" s="5"/>
+      <c r="DNF26" s="5"/>
+      <c r="DNH26" s="5"/>
+      <c r="DNJ26" s="5"/>
+      <c r="DNL26" s="5"/>
+      <c r="DNN26" s="5"/>
+      <c r="DNP26" s="5"/>
+      <c r="DNR26" s="5"/>
+      <c r="DNT26" s="5"/>
+      <c r="DNV26" s="5"/>
+      <c r="DNX26" s="5"/>
+      <c r="DNZ26" s="5"/>
+      <c r="DOB26" s="5"/>
+      <c r="DOD26" s="5"/>
+      <c r="DOF26" s="5"/>
+      <c r="DOH26" s="5"/>
+      <c r="DOJ26" s="5"/>
+      <c r="DOL26" s="5"/>
+      <c r="DON26" s="5"/>
+      <c r="DOP26" s="5"/>
+      <c r="DOR26" s="5"/>
+      <c r="DOT26" s="5"/>
+      <c r="DOV26" s="5"/>
+      <c r="DOX26" s="5"/>
+      <c r="DOZ26" s="5"/>
+      <c r="DPB26" s="5"/>
+      <c r="DPD26" s="5"/>
+      <c r="DPF26" s="5"/>
+      <c r="DPH26" s="5"/>
+      <c r="DPJ26" s="5"/>
+      <c r="DPL26" s="5"/>
+      <c r="DPN26" s="5"/>
+      <c r="DPP26" s="5"/>
+      <c r="DPR26" s="5"/>
+      <c r="DPT26" s="5"/>
+      <c r="DPV26" s="5"/>
+      <c r="DPX26" s="5"/>
+      <c r="DPZ26" s="5"/>
+      <c r="DQB26" s="5"/>
+      <c r="DQD26" s="5"/>
+      <c r="DQF26" s="5"/>
+      <c r="DQH26" s="5"/>
+      <c r="DQJ26" s="5"/>
+      <c r="DQL26" s="5"/>
+      <c r="DQN26" s="5"/>
+      <c r="DQP26" s="5"/>
+      <c r="DQR26" s="5"/>
+      <c r="DQT26" s="5"/>
+      <c r="DQV26" s="5"/>
+      <c r="DQX26" s="5"/>
+      <c r="DQZ26" s="5"/>
+      <c r="DRB26" s="5"/>
+      <c r="DRD26" s="5"/>
+      <c r="DRF26" s="5"/>
+      <c r="DRH26" s="5"/>
+      <c r="DRJ26" s="5"/>
+      <c r="DRL26" s="5"/>
+      <c r="DRN26" s="5"/>
+      <c r="DRP26" s="5"/>
+      <c r="DRR26" s="5"/>
+      <c r="DRT26" s="5"/>
+      <c r="DRV26" s="5"/>
+      <c r="DRX26" s="5"/>
+      <c r="DRZ26" s="5"/>
+      <c r="DSB26" s="5"/>
+      <c r="DSD26" s="5"/>
+      <c r="DSF26" s="5"/>
+      <c r="DSH26" s="5"/>
+      <c r="DSJ26" s="5"/>
+      <c r="DSL26" s="5"/>
+      <c r="DSN26" s="5"/>
+      <c r="DSP26" s="5"/>
+      <c r="DSR26" s="5"/>
+      <c r="DST26" s="5"/>
+      <c r="DSV26" s="5"/>
+      <c r="DSX26" s="5"/>
+      <c r="DSZ26" s="5"/>
+      <c r="DTB26" s="5"/>
+      <c r="DTD26" s="5"/>
+      <c r="DTF26" s="5"/>
+      <c r="DTH26" s="5"/>
+      <c r="DTJ26" s="5"/>
+      <c r="DTL26" s="5"/>
+      <c r="DTN26" s="5"/>
+      <c r="DTP26" s="5"/>
+      <c r="DTR26" s="5"/>
+      <c r="DTT26" s="5"/>
+      <c r="DTV26" s="5"/>
+      <c r="DTX26" s="5"/>
+      <c r="DTZ26" s="5"/>
+      <c r="DUB26" s="5"/>
+      <c r="DUD26" s="5"/>
+      <c r="DUF26" s="5"/>
+      <c r="DUH26" s="5"/>
+      <c r="DUJ26" s="5"/>
+      <c r="DUL26" s="5"/>
+      <c r="DUN26" s="5"/>
+      <c r="DUP26" s="5"/>
+      <c r="DUR26" s="5"/>
+      <c r="DUT26" s="5"/>
+      <c r="DUV26" s="5"/>
+      <c r="DUX26" s="5"/>
+      <c r="DUZ26" s="5"/>
+      <c r="DVB26" s="5"/>
+      <c r="DVD26" s="5"/>
+      <c r="DVF26" s="5"/>
+      <c r="DVH26" s="5"/>
+      <c r="DVJ26" s="5"/>
+      <c r="DVL26" s="5"/>
+      <c r="DVN26" s="5"/>
+      <c r="DVP26" s="5"/>
+      <c r="DVR26" s="5"/>
+      <c r="DVT26" s="5"/>
+      <c r="DVV26" s="5"/>
+      <c r="DVX26" s="5"/>
+      <c r="DVZ26" s="5"/>
+      <c r="DWB26" s="5"/>
+      <c r="DWD26" s="5"/>
+      <c r="DWF26" s="5"/>
+      <c r="DWH26" s="5"/>
+      <c r="DWJ26" s="5"/>
+      <c r="DWL26" s="5"/>
+      <c r="DWN26" s="5"/>
+      <c r="DWP26" s="5"/>
+      <c r="DWR26" s="5"/>
+      <c r="DWT26" s="5"/>
+      <c r="DWV26" s="5"/>
+      <c r="DWX26" s="5"/>
+      <c r="DWZ26" s="5"/>
+      <c r="DXB26" s="5"/>
+      <c r="DXD26" s="5"/>
+      <c r="DXF26" s="5"/>
+      <c r="DXH26" s="5"/>
+      <c r="DXJ26" s="5"/>
+      <c r="DXL26" s="5"/>
+      <c r="DXN26" s="5"/>
+      <c r="DXP26" s="5"/>
+      <c r="DXR26" s="5"/>
+      <c r="DXT26" s="5"/>
+      <c r="DXV26" s="5"/>
+      <c r="DXX26" s="5"/>
+      <c r="DXZ26" s="5"/>
+      <c r="DYB26" s="5"/>
+      <c r="DYD26" s="5"/>
+      <c r="DYF26" s="5"/>
+      <c r="DYH26" s="5"/>
+      <c r="DYJ26" s="5"/>
+      <c r="DYL26" s="5"/>
+      <c r="DYN26" s="5"/>
+      <c r="DYP26" s="5"/>
+      <c r="DYR26" s="5"/>
+      <c r="DYT26" s="5"/>
+      <c r="DYV26" s="5"/>
+      <c r="DYX26" s="5"/>
+      <c r="DYZ26" s="5"/>
+      <c r="DZB26" s="5"/>
+      <c r="DZD26" s="5"/>
+      <c r="DZF26" s="5"/>
+      <c r="DZH26" s="5"/>
+      <c r="DZJ26" s="5"/>
+      <c r="DZL26" s="5"/>
+      <c r="DZN26" s="5"/>
+      <c r="DZP26" s="5"/>
+      <c r="DZR26" s="5"/>
+      <c r="DZT26" s="5"/>
+      <c r="DZV26" s="5"/>
+      <c r="DZX26" s="5"/>
+      <c r="DZZ26" s="5"/>
+      <c r="EAB26" s="5"/>
+      <c r="EAD26" s="5"/>
+      <c r="EAF26" s="5"/>
+      <c r="EAH26" s="5"/>
+      <c r="EAJ26" s="5"/>
+      <c r="EAL26" s="5"/>
+      <c r="EAN26" s="5"/>
+      <c r="EAP26" s="5"/>
+      <c r="EAR26" s="5"/>
+      <c r="EAT26" s="5"/>
+      <c r="EAV26" s="5"/>
+      <c r="EAX26" s="5"/>
+      <c r="EAZ26" s="5"/>
+      <c r="EBB26" s="5"/>
+      <c r="EBD26" s="5"/>
+      <c r="EBF26" s="5"/>
+      <c r="EBH26" s="5"/>
+      <c r="EBJ26" s="5"/>
+      <c r="EBL26" s="5"/>
+      <c r="EBN26" s="5"/>
+      <c r="EBP26" s="5"/>
+      <c r="EBR26" s="5"/>
+      <c r="EBT26" s="5"/>
+      <c r="EBV26" s="5"/>
+      <c r="EBX26" s="5"/>
+      <c r="EBZ26" s="5"/>
+      <c r="ECB26" s="5"/>
+      <c r="ECD26" s="5"/>
+      <c r="ECF26" s="5"/>
+      <c r="ECH26" s="5"/>
+      <c r="ECJ26" s="5"/>
+      <c r="ECL26" s="5"/>
+      <c r="ECN26" s="5"/>
+      <c r="ECP26" s="5"/>
+      <c r="ECR26" s="5"/>
+      <c r="ECT26" s="5"/>
+      <c r="ECV26" s="5"/>
+      <c r="ECX26" s="5"/>
+      <c r="ECZ26" s="5"/>
+      <c r="EDB26" s="5"/>
+      <c r="EDD26" s="5"/>
+      <c r="EDF26" s="5"/>
+      <c r="EDH26" s="5"/>
+      <c r="EDJ26" s="5"/>
+      <c r="EDL26" s="5"/>
+      <c r="EDN26" s="5"/>
+      <c r="EDP26" s="5"/>
+      <c r="EDR26" s="5"/>
+      <c r="EDT26" s="5"/>
+      <c r="EDV26" s="5"/>
+      <c r="EDX26" s="5"/>
+      <c r="EDZ26" s="5"/>
+      <c r="EEB26" s="5"/>
+      <c r="EED26" s="5"/>
+      <c r="EEF26" s="5"/>
+      <c r="EEH26" s="5"/>
+      <c r="EEJ26" s="5"/>
+      <c r="EEL26" s="5"/>
+      <c r="EEN26" s="5"/>
+      <c r="EEP26" s="5"/>
+      <c r="EER26" s="5"/>
+      <c r="EET26" s="5"/>
+      <c r="EEV26" s="5"/>
+      <c r="EEX26" s="5"/>
+      <c r="EEZ26" s="5"/>
+      <c r="EFB26" s="5"/>
+      <c r="EFD26" s="5"/>
+      <c r="EFF26" s="5"/>
+      <c r="EFH26" s="5"/>
+      <c r="EFJ26" s="5"/>
+      <c r="EFL26" s="5"/>
+      <c r="EFN26" s="5"/>
+      <c r="EFP26" s="5"/>
+      <c r="EFR26" s="5"/>
+      <c r="EFT26" s="5"/>
+      <c r="EFV26" s="5"/>
+      <c r="EFX26" s="5"/>
+      <c r="EFZ26" s="5"/>
+      <c r="EGB26" s="5"/>
+      <c r="EGD26" s="5"/>
+      <c r="EGF26" s="5"/>
+      <c r="EGH26" s="5"/>
+      <c r="EGJ26" s="5"/>
+      <c r="EGL26" s="5"/>
+      <c r="EGN26" s="5"/>
+      <c r="EGP26" s="5"/>
+      <c r="EGR26" s="5"/>
+      <c r="EGT26" s="5"/>
+      <c r="EGV26" s="5"/>
+      <c r="EGX26" s="5"/>
+      <c r="EGZ26" s="5"/>
+      <c r="EHB26" s="5"/>
+      <c r="EHD26" s="5"/>
+      <c r="EHF26" s="5"/>
+      <c r="EHH26" s="5"/>
+      <c r="EHJ26" s="5"/>
+      <c r="EHL26" s="5"/>
+      <c r="EHN26" s="5"/>
+      <c r="EHP26" s="5"/>
+      <c r="EHR26" s="5"/>
+      <c r="EHT26" s="5"/>
+      <c r="EHV26" s="5"/>
+      <c r="EHX26" s="5"/>
+      <c r="EHZ26" s="5"/>
+      <c r="EIB26" s="5"/>
+      <c r="EID26" s="5"/>
+      <c r="EIF26" s="5"/>
+      <c r="EIH26" s="5"/>
+      <c r="EIJ26" s="5"/>
+      <c r="EIL26" s="5"/>
+      <c r="EIN26" s="5"/>
+      <c r="EIP26" s="5"/>
+      <c r="EIR26" s="5"/>
+      <c r="EIT26" s="5"/>
+      <c r="EIV26" s="5"/>
+      <c r="EIX26" s="5"/>
+      <c r="EIZ26" s="5"/>
+      <c r="EJB26" s="5"/>
+      <c r="EJD26" s="5"/>
+      <c r="EJF26" s="5"/>
+      <c r="EJH26" s="5"/>
+      <c r="EJJ26" s="5"/>
+      <c r="EJL26" s="5"/>
+      <c r="EJN26" s="5"/>
+      <c r="EJP26" s="5"/>
+      <c r="EJR26" s="5"/>
+      <c r="EJT26" s="5"/>
+      <c r="EJV26" s="5"/>
+      <c r="EJX26" s="5"/>
+      <c r="EJZ26" s="5"/>
+      <c r="EKB26" s="5"/>
+      <c r="EKD26" s="5"/>
+      <c r="EKF26" s="5"/>
+      <c r="EKH26" s="5"/>
+      <c r="EKJ26" s="5"/>
+      <c r="EKL26" s="5"/>
+      <c r="EKN26" s="5"/>
+      <c r="EKP26" s="5"/>
+      <c r="EKR26" s="5"/>
+      <c r="EKT26" s="5"/>
+      <c r="EKV26" s="5"/>
+      <c r="EKX26" s="5"/>
+      <c r="EKZ26" s="5"/>
+      <c r="ELB26" s="5"/>
+      <c r="ELD26" s="5"/>
+      <c r="ELF26" s="5"/>
+      <c r="ELH26" s="5"/>
+      <c r="ELJ26" s="5"/>
+      <c r="ELL26" s="5"/>
+      <c r="ELN26" s="5"/>
+      <c r="ELP26" s="5"/>
+      <c r="ELR26" s="5"/>
+      <c r="ELT26" s="5"/>
+      <c r="ELV26" s="5"/>
+      <c r="ELX26" s="5"/>
+      <c r="ELZ26" s="5"/>
+      <c r="EMB26" s="5"/>
+      <c r="EMD26" s="5"/>
+      <c r="EMF26" s="5"/>
+      <c r="EMH26" s="5"/>
+      <c r="EMJ26" s="5"/>
+      <c r="EML26" s="5"/>
+      <c r="EMN26" s="5"/>
+      <c r="EMP26" s="5"/>
+      <c r="EMR26" s="5"/>
+      <c r="EMT26" s="5"/>
+      <c r="EMV26" s="5"/>
+      <c r="EMX26" s="5"/>
+      <c r="EMZ26" s="5"/>
+      <c r="ENB26" s="5"/>
+      <c r="END26" s="5"/>
+      <c r="ENF26" s="5"/>
+      <c r="ENH26" s="5"/>
+      <c r="ENJ26" s="5"/>
+      <c r="ENL26" s="5"/>
+      <c r="ENN26" s="5"/>
+      <c r="ENP26" s="5"/>
+      <c r="ENR26" s="5"/>
+      <c r="ENT26" s="5"/>
+      <c r="ENV26" s="5"/>
+      <c r="ENX26" s="5"/>
+      <c r="ENZ26" s="5"/>
+      <c r="EOB26" s="5"/>
+      <c r="EOD26" s="5"/>
+      <c r="EOF26" s="5"/>
+      <c r="EOH26" s="5"/>
+      <c r="EOJ26" s="5"/>
+      <c r="EOL26" s="5"/>
+      <c r="EON26" s="5"/>
+      <c r="EOP26" s="5"/>
+      <c r="EOR26" s="5"/>
+      <c r="EOT26" s="5"/>
+      <c r="EOV26" s="5"/>
+      <c r="EOX26" s="5"/>
+      <c r="EOZ26" s="5"/>
+      <c r="EPB26" s="5"/>
+      <c r="EPD26" s="5"/>
+      <c r="EPF26" s="5"/>
+      <c r="EPH26" s="5"/>
+      <c r="EPJ26" s="5"/>
+      <c r="EPL26" s="5"/>
+      <c r="EPN26" s="5"/>
+      <c r="EPP26" s="5"/>
+      <c r="EPR26" s="5"/>
+      <c r="EPT26" s="5"/>
+      <c r="EPV26" s="5"/>
+      <c r="EPX26" s="5"/>
+      <c r="EPZ26" s="5"/>
+      <c r="EQB26" s="5"/>
+      <c r="EQD26" s="5"/>
+      <c r="EQF26" s="5"/>
+      <c r="EQH26" s="5"/>
+      <c r="EQJ26" s="5"/>
+      <c r="EQL26" s="5"/>
+      <c r="EQN26" s="5"/>
+      <c r="EQP26" s="5"/>
+      <c r="EQR26" s="5"/>
+      <c r="EQT26" s="5"/>
+      <c r="EQV26" s="5"/>
+      <c r="EQX26" s="5"/>
+      <c r="EQZ26" s="5"/>
+      <c r="ERB26" s="5"/>
+      <c r="ERD26" s="5"/>
+      <c r="ERF26" s="5"/>
+      <c r="ERH26" s="5"/>
+      <c r="ERJ26" s="5"/>
+      <c r="ERL26" s="5"/>
+      <c r="ERN26" s="5"/>
+      <c r="ERP26" s="5"/>
+      <c r="ERR26" s="5"/>
+      <c r="ERT26" s="5"/>
+      <c r="ERV26" s="5"/>
+      <c r="ERX26" s="5"/>
+      <c r="ERZ26" s="5"/>
+      <c r="ESB26" s="5"/>
+      <c r="ESD26" s="5"/>
+      <c r="ESF26" s="5"/>
+      <c r="ESH26" s="5"/>
+      <c r="ESJ26" s="5"/>
+      <c r="ESL26" s="5"/>
+      <c r="ESN26" s="5"/>
+      <c r="ESP26" s="5"/>
+      <c r="ESR26" s="5"/>
+      <c r="EST26" s="5"/>
+      <c r="ESV26" s="5"/>
+      <c r="ESX26" s="5"/>
+      <c r="ESZ26" s="5"/>
+      <c r="ETB26" s="5"/>
+      <c r="ETD26" s="5"/>
+      <c r="ETF26" s="5"/>
+      <c r="ETH26" s="5"/>
+      <c r="ETJ26" s="5"/>
+      <c r="ETL26" s="5"/>
+      <c r="ETN26" s="5"/>
+      <c r="ETP26" s="5"/>
+      <c r="ETR26" s="5"/>
+      <c r="ETT26" s="5"/>
+      <c r="ETV26" s="5"/>
+      <c r="ETX26" s="5"/>
+      <c r="ETZ26" s="5"/>
+      <c r="EUB26" s="5"/>
+      <c r="EUD26" s="5"/>
+      <c r="EUF26" s="5"/>
+      <c r="EUH26" s="5"/>
+      <c r="EUJ26" s="5"/>
+      <c r="EUL26" s="5"/>
+      <c r="EUN26" s="5"/>
+      <c r="EUP26" s="5"/>
+      <c r="EUR26" s="5"/>
+      <c r="EUT26" s="5"/>
+      <c r="EUV26" s="5"/>
+      <c r="EUX26" s="5"/>
+      <c r="EUZ26" s="5"/>
+      <c r="EVB26" s="5"/>
+      <c r="EVD26" s="5"/>
+      <c r="EVF26" s="5"/>
+      <c r="EVH26" s="5"/>
+      <c r="EVJ26" s="5"/>
+      <c r="EVL26" s="5"/>
+      <c r="EVN26" s="5"/>
+      <c r="EVP26" s="5"/>
+      <c r="EVR26" s="5"/>
+      <c r="EVT26" s="5"/>
+      <c r="EVV26" s="5"/>
+      <c r="EVX26" s="5"/>
+      <c r="EVZ26" s="5"/>
+      <c r="EWB26" s="5"/>
+      <c r="EWD26" s="5"/>
+      <c r="EWF26" s="5"/>
+      <c r="EWH26" s="5"/>
+      <c r="EWJ26" s="5"/>
+      <c r="EWL26" s="5"/>
+      <c r="EWN26" s="5"/>
+      <c r="EWP26" s="5"/>
+      <c r="EWR26" s="5"/>
+      <c r="EWT26" s="5"/>
+      <c r="EWV26" s="5"/>
+      <c r="EWX26" s="5"/>
+      <c r="EWZ26" s="5"/>
+      <c r="EXB26" s="5"/>
+      <c r="EXD26" s="5"/>
+      <c r="EXF26" s="5"/>
+      <c r="EXH26" s="5"/>
+      <c r="EXJ26" s="5"/>
+      <c r="EXL26" s="5"/>
+      <c r="EXN26" s="5"/>
+      <c r="EXP26" s="5"/>
+      <c r="EXR26" s="5"/>
+      <c r="EXT26" s="5"/>
+      <c r="EXV26" s="5"/>
+      <c r="EXX26" s="5"/>
+      <c r="EXZ26" s="5"/>
+      <c r="EYB26" s="5"/>
+      <c r="EYD26" s="5"/>
+      <c r="EYF26" s="5"/>
+      <c r="EYH26" s="5"/>
+      <c r="EYJ26" s="5"/>
+      <c r="EYL26" s="5"/>
+      <c r="EYN26" s="5"/>
+      <c r="EYP26" s="5"/>
+      <c r="EYR26" s="5"/>
+      <c r="EYT26" s="5"/>
+      <c r="EYV26" s="5"/>
+      <c r="EYX26" s="5"/>
+      <c r="EYZ26" s="5"/>
+      <c r="EZB26" s="5"/>
+      <c r="EZD26" s="5"/>
+      <c r="EZF26" s="5"/>
+      <c r="EZH26" s="5"/>
+      <c r="EZJ26" s="5"/>
+      <c r="EZL26" s="5"/>
+      <c r="EZN26" s="5"/>
+      <c r="EZP26" s="5"/>
+      <c r="EZR26" s="5"/>
+      <c r="EZT26" s="5"/>
+      <c r="EZV26" s="5"/>
+      <c r="EZX26" s="5"/>
+      <c r="EZZ26" s="5"/>
+      <c r="FAB26" s="5"/>
+      <c r="FAD26" s="5"/>
+      <c r="FAF26" s="5"/>
+      <c r="FAH26" s="5"/>
+      <c r="FAJ26" s="5"/>
+      <c r="FAL26" s="5"/>
+      <c r="FAN26" s="5"/>
+      <c r="FAP26" s="5"/>
+      <c r="FAR26" s="5"/>
+      <c r="FAT26" s="5"/>
+      <c r="FAV26" s="5"/>
+      <c r="FAX26" s="5"/>
+      <c r="FAZ26" s="5"/>
+      <c r="FBB26" s="5"/>
+      <c r="FBD26" s="5"/>
+      <c r="FBF26" s="5"/>
+      <c r="FBH26" s="5"/>
+      <c r="FBJ26" s="5"/>
+      <c r="FBL26" s="5"/>
+      <c r="FBN26" s="5"/>
+      <c r="FBP26" s="5"/>
+      <c r="FBR26" s="5"/>
+      <c r="FBT26" s="5"/>
+      <c r="FBV26" s="5"/>
+      <c r="FBX26" s="5"/>
+      <c r="FBZ26" s="5"/>
+      <c r="FCB26" s="5"/>
+      <c r="FCD26" s="5"/>
+      <c r="FCF26" s="5"/>
+      <c r="FCH26" s="5"/>
+      <c r="FCJ26" s="5"/>
+      <c r="FCL26" s="5"/>
+      <c r="FCN26" s="5"/>
+      <c r="FCP26" s="5"/>
+      <c r="FCR26" s="5"/>
+      <c r="FCT26" s="5"/>
+      <c r="FCV26" s="5"/>
+      <c r="FCX26" s="5"/>
+      <c r="FCZ26" s="5"/>
+      <c r="FDB26" s="5"/>
+      <c r="FDD26" s="5"/>
+      <c r="FDF26" s="5"/>
+      <c r="FDH26" s="5"/>
+      <c r="FDJ26" s="5"/>
+      <c r="FDL26" s="5"/>
+      <c r="FDN26" s="5"/>
+      <c r="FDP26" s="5"/>
+      <c r="FDR26" s="5"/>
+      <c r="FDT26" s="5"/>
+      <c r="FDV26" s="5"/>
+      <c r="FDX26" s="5"/>
+      <c r="FDZ26" s="5"/>
+      <c r="FEB26" s="5"/>
+      <c r="FED26" s="5"/>
+      <c r="FEF26" s="5"/>
+      <c r="FEH26" s="5"/>
+      <c r="FEJ26" s="5"/>
+      <c r="FEL26" s="5"/>
+      <c r="FEN26" s="5"/>
+      <c r="FEP26" s="5"/>
+      <c r="FER26" s="5"/>
+      <c r="FET26" s="5"/>
+      <c r="FEV26" s="5"/>
+      <c r="FEX26" s="5"/>
+      <c r="FEZ26" s="5"/>
+      <c r="FFB26" s="5"/>
+      <c r="FFD26" s="5"/>
+      <c r="FFF26" s="5"/>
+      <c r="FFH26" s="5"/>
+      <c r="FFJ26" s="5"/>
+      <c r="FFL26" s="5"/>
+      <c r="FFN26" s="5"/>
+      <c r="FFP26" s="5"/>
+      <c r="FFR26" s="5"/>
+      <c r="FFT26" s="5"/>
+      <c r="FFV26" s="5"/>
+      <c r="FFX26" s="5"/>
+      <c r="FFZ26" s="5"/>
+      <c r="FGB26" s="5"/>
+      <c r="FGD26" s="5"/>
+      <c r="FGF26" s="5"/>
+      <c r="FGH26" s="5"/>
+      <c r="FGJ26" s="5"/>
+      <c r="FGL26" s="5"/>
+      <c r="FGN26" s="5"/>
+      <c r="FGP26" s="5"/>
+      <c r="FGR26" s="5"/>
+      <c r="FGT26" s="5"/>
+      <c r="FGV26" s="5"/>
+      <c r="FGX26" s="5"/>
+      <c r="FGZ26" s="5"/>
+      <c r="FHB26" s="5"/>
+      <c r="FHD26" s="5"/>
+      <c r="FHF26" s="5"/>
+      <c r="FHH26" s="5"/>
+      <c r="FHJ26" s="5"/>
+      <c r="FHL26" s="5"/>
+      <c r="FHN26" s="5"/>
+      <c r="FHP26" s="5"/>
+      <c r="FHR26" s="5"/>
+      <c r="FHT26" s="5"/>
+      <c r="FHV26" s="5"/>
+      <c r="FHX26" s="5"/>
+      <c r="FHZ26" s="5"/>
+      <c r="FIB26" s="5"/>
+      <c r="FID26" s="5"/>
+      <c r="FIF26" s="5"/>
+      <c r="FIH26" s="5"/>
+      <c r="FIJ26" s="5"/>
+      <c r="FIL26" s="5"/>
+      <c r="FIN26" s="5"/>
+      <c r="FIP26" s="5"/>
+      <c r="FIR26" s="5"/>
+      <c r="FIT26" s="5"/>
+      <c r="FIV26" s="5"/>
+      <c r="FIX26" s="5"/>
+      <c r="FIZ26" s="5"/>
+      <c r="FJB26" s="5"/>
+      <c r="FJD26" s="5"/>
+      <c r="FJF26" s="5"/>
+      <c r="FJH26" s="5"/>
+      <c r="FJJ26" s="5"/>
+      <c r="FJL26" s="5"/>
+      <c r="FJN26" s="5"/>
+      <c r="FJP26" s="5"/>
+      <c r="FJR26" s="5"/>
+      <c r="FJT26" s="5"/>
+      <c r="FJV26" s="5"/>
+      <c r="FJX26" s="5"/>
+      <c r="FJZ26" s="5"/>
+      <c r="FKB26" s="5"/>
+      <c r="FKD26" s="5"/>
+      <c r="FKF26" s="5"/>
+      <c r="FKH26" s="5"/>
+      <c r="FKJ26" s="5"/>
+      <c r="FKL26" s="5"/>
+      <c r="FKN26" s="5"/>
+      <c r="FKP26" s="5"/>
+      <c r="FKR26" s="5"/>
+      <c r="FKT26" s="5"/>
+      <c r="FKV26" s="5"/>
+      <c r="FKX26" s="5"/>
+      <c r="FKZ26" s="5"/>
+      <c r="FLB26" s="5"/>
+      <c r="FLD26" s="5"/>
+      <c r="FLF26" s="5"/>
+      <c r="FLH26" s="5"/>
+      <c r="FLJ26" s="5"/>
+      <c r="FLL26" s="5"/>
+      <c r="FLN26" s="5"/>
+      <c r="FLP26" s="5"/>
+      <c r="FLR26" s="5"/>
+      <c r="FLT26" s="5"/>
+      <c r="FLV26" s="5"/>
+      <c r="FLX26" s="5"/>
+      <c r="FLZ26" s="5"/>
+      <c r="FMB26" s="5"/>
+      <c r="FMD26" s="5"/>
+      <c r="FMF26" s="5"/>
+      <c r="FMH26" s="5"/>
+      <c r="FMJ26" s="5"/>
+      <c r="FML26" s="5"/>
+      <c r="FMN26" s="5"/>
+      <c r="FMP26" s="5"/>
+      <c r="FMR26" s="5"/>
+      <c r="FMT26" s="5"/>
+      <c r="FMV26" s="5"/>
+      <c r="FMX26" s="5"/>
+      <c r="FMZ26" s="5"/>
+      <c r="FNB26" s="5"/>
+      <c r="FND26" s="5"/>
+      <c r="FNF26" s="5"/>
+      <c r="FNH26" s="5"/>
+      <c r="FNJ26" s="5"/>
+      <c r="FNL26" s="5"/>
+      <c r="FNN26" s="5"/>
+      <c r="FNP26" s="5"/>
+      <c r="FNR26" s="5"/>
+      <c r="FNT26" s="5"/>
+      <c r="FNV26" s="5"/>
+      <c r="FNX26" s="5"/>
+      <c r="FNZ26" s="5"/>
+      <c r="FOB26" s="5"/>
+      <c r="FOD26" s="5"/>
+      <c r="FOF26" s="5"/>
+      <c r="FOH26" s="5"/>
+      <c r="FOJ26" s="5"/>
+      <c r="FOL26" s="5"/>
+      <c r="FON26" s="5"/>
+      <c r="FOP26" s="5"/>
+      <c r="FOR26" s="5"/>
+      <c r="FOT26" s="5"/>
+      <c r="FOV26" s="5"/>
+      <c r="FOX26" s="5"/>
+      <c r="FOZ26" s="5"/>
+      <c r="FPB26" s="5"/>
+      <c r="FPD26" s="5"/>
+      <c r="FPF26" s="5"/>
+      <c r="FPH26" s="5"/>
+      <c r="FPJ26" s="5"/>
+      <c r="FPL26" s="5"/>
+      <c r="FPN26" s="5"/>
+      <c r="FPP26" s="5"/>
+      <c r="FPR26" s="5"/>
+      <c r="FPT26" s="5"/>
+      <c r="FPV26" s="5"/>
+      <c r="FPX26" s="5"/>
+      <c r="FPZ26" s="5"/>
+      <c r="FQB26" s="5"/>
+      <c r="FQD26" s="5"/>
+      <c r="FQF26" s="5"/>
+      <c r="FQH26" s="5"/>
+      <c r="FQJ26" s="5"/>
+      <c r="FQL26" s="5"/>
+      <c r="FQN26" s="5"/>
+      <c r="FQP26" s="5"/>
+      <c r="FQR26" s="5"/>
+      <c r="FQT26" s="5"/>
+      <c r="FQV26" s="5"/>
+      <c r="FQX26" s="5"/>
+      <c r="FQZ26" s="5"/>
+      <c r="FRB26" s="5"/>
+      <c r="FRD26" s="5"/>
+      <c r="FRF26" s="5"/>
+      <c r="FRH26" s="5"/>
+      <c r="FRJ26" s="5"/>
+      <c r="FRL26" s="5"/>
+      <c r="FRN26" s="5"/>
+      <c r="FRP26" s="5"/>
+      <c r="FRR26" s="5"/>
+      <c r="FRT26" s="5"/>
+      <c r="FRV26" s="5"/>
+      <c r="FRX26" s="5"/>
+      <c r="FRZ26" s="5"/>
+      <c r="FSB26" s="5"/>
+      <c r="FSD26" s="5"/>
+      <c r="FSF26" s="5"/>
+      <c r="FSH26" s="5"/>
+      <c r="FSJ26" s="5"/>
+      <c r="FSL26" s="5"/>
+      <c r="FSN26" s="5"/>
+      <c r="FSP26" s="5"/>
+      <c r="FSR26" s="5"/>
+      <c r="FST26" s="5"/>
+      <c r="FSV26" s="5"/>
+      <c r="FSX26" s="5"/>
+      <c r="FSZ26" s="5"/>
+      <c r="FTB26" s="5"/>
+      <c r="FTD26" s="5"/>
+      <c r="FTF26" s="5"/>
+      <c r="FTH26" s="5"/>
+      <c r="FTJ26" s="5"/>
+      <c r="FTL26" s="5"/>
+      <c r="FTN26" s="5"/>
+      <c r="FTP26" s="5"/>
+      <c r="FTR26" s="5"/>
+      <c r="FTT26" s="5"/>
+      <c r="FTV26" s="5"/>
+      <c r="FTX26" s="5"/>
+      <c r="FTZ26" s="5"/>
+      <c r="FUB26" s="5"/>
+      <c r="FUD26" s="5"/>
+      <c r="FUF26" s="5"/>
+      <c r="FUH26" s="5"/>
+      <c r="FUJ26" s="5"/>
+      <c r="FUL26" s="5"/>
+      <c r="FUN26" s="5"/>
+      <c r="FUP26" s="5"/>
+      <c r="FUR26" s="5"/>
+      <c r="FUT26" s="5"/>
+      <c r="FUV26" s="5"/>
+      <c r="FUX26" s="5"/>
+      <c r="FUZ26" s="5"/>
+      <c r="FVB26" s="5"/>
+      <c r="FVD26" s="5"/>
+      <c r="FVF26" s="5"/>
+      <c r="FVH26" s="5"/>
+      <c r="FVJ26" s="5"/>
+      <c r="FVL26" s="5"/>
+      <c r="FVN26" s="5"/>
+      <c r="FVP26" s="5"/>
+      <c r="FVR26" s="5"/>
+      <c r="FVT26" s="5"/>
+      <c r="FVV26" s="5"/>
+      <c r="FVX26" s="5"/>
+      <c r="FVZ26" s="5"/>
+      <c r="FWB26" s="5"/>
+      <c r="FWD26" s="5"/>
+      <c r="FWF26" s="5"/>
+      <c r="FWH26" s="5"/>
+      <c r="FWJ26" s="5"/>
+      <c r="FWL26" s="5"/>
+      <c r="FWN26" s="5"/>
+      <c r="FWP26" s="5"/>
+      <c r="FWR26" s="5"/>
+      <c r="FWT26" s="5"/>
+      <c r="FWV26" s="5"/>
+      <c r="FWX26" s="5"/>
+      <c r="FWZ26" s="5"/>
+      <c r="FXB26" s="5"/>
+      <c r="FXD26" s="5"/>
+      <c r="FXF26" s="5"/>
+      <c r="FXH26" s="5"/>
+      <c r="FXJ26" s="5"/>
+      <c r="FXL26" s="5"/>
+      <c r="FXN26" s="5"/>
+      <c r="FXP26" s="5"/>
+      <c r="FXR26" s="5"/>
+      <c r="FXT26" s="5"/>
+      <c r="FXV26" s="5"/>
+      <c r="FXX26" s="5"/>
+      <c r="FXZ26" s="5"/>
+      <c r="FYB26" s="5"/>
+      <c r="FYD26" s="5"/>
+      <c r="FYF26" s="5"/>
+      <c r="FYH26" s="5"/>
+      <c r="FYJ26" s="5"/>
+      <c r="FYL26" s="5"/>
+      <c r="FYN26" s="5"/>
+      <c r="FYP26" s="5"/>
+      <c r="FYR26" s="5"/>
+      <c r="FYT26" s="5"/>
+      <c r="FYV26" s="5"/>
+      <c r="FYX26" s="5"/>
+      <c r="FYZ26" s="5"/>
+      <c r="FZB26" s="5"/>
+      <c r="FZD26" s="5"/>
+      <c r="FZF26" s="5"/>
+      <c r="FZH26" s="5"/>
+      <c r="FZJ26" s="5"/>
+      <c r="FZL26" s="5"/>
+      <c r="FZN26" s="5"/>
+      <c r="FZP26" s="5"/>
+      <c r="FZR26" s="5"/>
+      <c r="FZT26" s="5"/>
+      <c r="FZV26" s="5"/>
+      <c r="FZX26" s="5"/>
+      <c r="FZZ26" s="5"/>
+      <c r="GAB26" s="5"/>
+      <c r="GAD26" s="5"/>
+      <c r="GAF26" s="5"/>
+      <c r="GAH26" s="5"/>
+      <c r="GAJ26" s="5"/>
+      <c r="GAL26" s="5"/>
+      <c r="GAN26" s="5"/>
+      <c r="GAP26" s="5"/>
+      <c r="GAR26" s="5"/>
+      <c r="GAT26" s="5"/>
+      <c r="GAV26" s="5"/>
+      <c r="GAX26" s="5"/>
+      <c r="GAZ26" s="5"/>
+      <c r="GBB26" s="5"/>
+      <c r="GBD26" s="5"/>
+      <c r="GBF26" s="5"/>
+      <c r="GBH26" s="5"/>
+      <c r="GBJ26" s="5"/>
+      <c r="GBL26" s="5"/>
+      <c r="GBN26" s="5"/>
+      <c r="GBP26" s="5"/>
+      <c r="GBR26" s="5"/>
+      <c r="GBT26" s="5"/>
+      <c r="GBV26" s="5"/>
+      <c r="GBX26" s="5"/>
+      <c r="GBZ26" s="5"/>
+      <c r="GCB26" s="5"/>
+      <c r="GCD26" s="5"/>
+      <c r="GCF26" s="5"/>
+      <c r="GCH26" s="5"/>
+      <c r="GCJ26" s="5"/>
+      <c r="GCL26" s="5"/>
+      <c r="GCN26" s="5"/>
+      <c r="GCP26" s="5"/>
+      <c r="GCR26" s="5"/>
+      <c r="GCT26" s="5"/>
+      <c r="GCV26" s="5"/>
+      <c r="GCX26" s="5"/>
+      <c r="GCZ26" s="5"/>
+      <c r="GDB26" s="5"/>
+      <c r="GDD26" s="5"/>
+      <c r="GDF26" s="5"/>
+      <c r="GDH26" s="5"/>
+      <c r="GDJ26" s="5"/>
+      <c r="GDL26" s="5"/>
+      <c r="GDN26" s="5"/>
+      <c r="GDP26" s="5"/>
+      <c r="GDR26" s="5"/>
+      <c r="GDT26" s="5"/>
+      <c r="GDV26" s="5"/>
+      <c r="GDX26" s="5"/>
+      <c r="GDZ26" s="5"/>
+      <c r="GEB26" s="5"/>
+      <c r="GED26" s="5"/>
+      <c r="GEF26" s="5"/>
+      <c r="GEH26" s="5"/>
+      <c r="GEJ26" s="5"/>
+      <c r="GEL26" s="5"/>
+      <c r="GEN26" s="5"/>
+      <c r="GEP26" s="5"/>
+      <c r="GER26" s="5"/>
+      <c r="GET26" s="5"/>
+      <c r="GEV26" s="5"/>
+      <c r="GEX26" s="5"/>
+      <c r="GEZ26" s="5"/>
+      <c r="GFB26" s="5"/>
+      <c r="GFD26" s="5"/>
+      <c r="GFF26" s="5"/>
+      <c r="GFH26" s="5"/>
+      <c r="GFJ26" s="5"/>
+      <c r="GFL26" s="5"/>
+      <c r="GFN26" s="5"/>
+      <c r="GFP26" s="5"/>
+      <c r="GFR26" s="5"/>
+      <c r="GFT26" s="5"/>
+      <c r="GFV26" s="5"/>
+      <c r="GFX26" s="5"/>
+      <c r="GFZ26" s="5"/>
+      <c r="GGB26" s="5"/>
+      <c r="GGD26" s="5"/>
+      <c r="GGF26" s="5"/>
+      <c r="GGH26" s="5"/>
+      <c r="GGJ26" s="5"/>
+      <c r="GGL26" s="5"/>
+      <c r="GGN26" s="5"/>
+      <c r="GGP26" s="5"/>
+      <c r="GGR26" s="5"/>
+      <c r="GGT26" s="5"/>
+      <c r="GGV26" s="5"/>
+      <c r="GGX26" s="5"/>
+      <c r="GGZ26" s="5"/>
+      <c r="GHB26" s="5"/>
+      <c r="GHD26" s="5"/>
+      <c r="GHF26" s="5"/>
+      <c r="GHH26" s="5"/>
+      <c r="GHJ26" s="5"/>
+      <c r="GHL26" s="5"/>
+      <c r="GHN26" s="5"/>
+      <c r="GHP26" s="5"/>
+      <c r="GHR26" s="5"/>
+      <c r="GHT26" s="5"/>
+      <c r="GHV26" s="5"/>
+      <c r="GHX26" s="5"/>
+      <c r="GHZ26" s="5"/>
+      <c r="GIB26" s="5"/>
+      <c r="GID26" s="5"/>
+      <c r="GIF26" s="5"/>
+      <c r="GIH26" s="5"/>
+      <c r="GIJ26" s="5"/>
+      <c r="GIL26" s="5"/>
+      <c r="GIN26" s="5"/>
+      <c r="GIP26" s="5"/>
+      <c r="GIR26" s="5"/>
+      <c r="GIT26" s="5"/>
+      <c r="GIV26" s="5"/>
+      <c r="GIX26" s="5"/>
+      <c r="GIZ26" s="5"/>
+      <c r="GJB26" s="5"/>
+      <c r="GJD26" s="5"/>
+      <c r="GJF26" s="5"/>
+      <c r="GJH26" s="5"/>
+      <c r="GJJ26" s="5"/>
+      <c r="GJL26" s="5"/>
+      <c r="GJN26" s="5"/>
+      <c r="GJP26" s="5"/>
+      <c r="GJR26" s="5"/>
+      <c r="GJT26" s="5"/>
+      <c r="GJV26" s="5"/>
+      <c r="GJX26" s="5"/>
+      <c r="GJZ26" s="5"/>
+      <c r="GKB26" s="5"/>
+      <c r="GKD26" s="5"/>
+      <c r="GKF26" s="5"/>
+      <c r="GKH26" s="5"/>
+      <c r="GKJ26" s="5"/>
+      <c r="GKL26" s="5"/>
+      <c r="GKN26" s="5"/>
+      <c r="GKP26" s="5"/>
+      <c r="GKR26" s="5"/>
+      <c r="GKT26" s="5"/>
+      <c r="GKV26" s="5"/>
+      <c r="GKX26" s="5"/>
+      <c r="GKZ26" s="5"/>
+      <c r="GLB26" s="5"/>
+      <c r="GLD26" s="5"/>
+      <c r="GLF26" s="5"/>
+      <c r="GLH26" s="5"/>
+      <c r="GLJ26" s="5"/>
+      <c r="GLL26" s="5"/>
+      <c r="GLN26" s="5"/>
+      <c r="GLP26" s="5"/>
+      <c r="GLR26" s="5"/>
+      <c r="GLT26" s="5"/>
+      <c r="GLV26" s="5"/>
+      <c r="GLX26" s="5"/>
+      <c r="GLZ26" s="5"/>
+      <c r="GMB26" s="5"/>
+      <c r="GMD26" s="5"/>
+      <c r="GMF26" s="5"/>
+      <c r="GMH26" s="5"/>
+      <c r="GMJ26" s="5"/>
+      <c r="GML26" s="5"/>
+      <c r="GMN26" s="5"/>
+      <c r="GMP26" s="5"/>
+      <c r="GMR26" s="5"/>
+      <c r="GMT26" s="5"/>
+      <c r="GMV26" s="5"/>
+      <c r="GMX26" s="5"/>
+      <c r="GMZ26" s="5"/>
+      <c r="GNB26" s="5"/>
+      <c r="GND26" s="5"/>
+      <c r="GNF26" s="5"/>
+      <c r="GNH26" s="5"/>
+      <c r="GNJ26" s="5"/>
+      <c r="GNL26" s="5"/>
+      <c r="GNN26" s="5"/>
+      <c r="GNP26" s="5"/>
+      <c r="GNR26" s="5"/>
+      <c r="GNT26" s="5"/>
+      <c r="GNV26" s="5"/>
+      <c r="GNX26" s="5"/>
+      <c r="GNZ26" s="5"/>
+      <c r="GOB26" s="5"/>
+      <c r="GOD26" s="5"/>
+      <c r="GOF26" s="5"/>
+      <c r="GOH26" s="5"/>
+      <c r="GOJ26" s="5"/>
+      <c r="GOL26" s="5"/>
+      <c r="GON26" s="5"/>
+      <c r="GOP26" s="5"/>
+      <c r="GOR26" s="5"/>
+      <c r="GOT26" s="5"/>
+      <c r="GOV26" s="5"/>
+      <c r="GOX26" s="5"/>
+      <c r="GOZ26" s="5"/>
+      <c r="GPB26" s="5"/>
+      <c r="GPD26" s="5"/>
+      <c r="GPF26" s="5"/>
+      <c r="GPH26" s="5"/>
+      <c r="GPJ26" s="5"/>
+      <c r="GPL26" s="5"/>
+      <c r="GPN26" s="5"/>
+      <c r="GPP26" s="5"/>
+      <c r="GPR26" s="5"/>
+      <c r="GPT26" s="5"/>
+      <c r="GPV26" s="5"/>
+      <c r="GPX26" s="5"/>
+      <c r="GPZ26" s="5"/>
+      <c r="GQB26" s="5"/>
+      <c r="GQD26" s="5"/>
+      <c r="GQF26" s="5"/>
+      <c r="GQH26" s="5"/>
+      <c r="GQJ26" s="5"/>
+      <c r="GQL26" s="5"/>
+      <c r="GQN26" s="5"/>
+      <c r="GQP26" s="5"/>
+      <c r="GQR26" s="5"/>
+      <c r="GQT26" s="5"/>
+      <c r="GQV26" s="5"/>
+      <c r="GQX26" s="5"/>
+      <c r="GQZ26" s="5"/>
+      <c r="GRB26" s="5"/>
+      <c r="GRD26" s="5"/>
+      <c r="GRF26" s="5"/>
+      <c r="GRH26" s="5"/>
+      <c r="GRJ26" s="5"/>
+      <c r="GRL26" s="5"/>
+      <c r="GRN26" s="5"/>
+      <c r="GRP26" s="5"/>
+      <c r="GRR26" s="5"/>
+      <c r="GRT26" s="5"/>
+      <c r="GRV26" s="5"/>
+      <c r="GRX26" s="5"/>
+      <c r="GRZ26" s="5"/>
+      <c r="GSB26" s="5"/>
+      <c r="GSD26" s="5"/>
+      <c r="GSF26" s="5"/>
+      <c r="GSH26" s="5"/>
+      <c r="GSJ26" s="5"/>
+      <c r="GSL26" s="5"/>
+      <c r="GSN26" s="5"/>
+      <c r="GSP26" s="5"/>
+      <c r="GSR26" s="5"/>
+      <c r="GST26" s="5"/>
+      <c r="GSV26" s="5"/>
+      <c r="GSX26" s="5"/>
+      <c r="GSZ26" s="5"/>
+      <c r="GTB26" s="5"/>
+      <c r="GTD26" s="5"/>
+      <c r="GTF26" s="5"/>
+      <c r="GTH26" s="5"/>
+      <c r="GTJ26" s="5"/>
+      <c r="GTL26" s="5"/>
+      <c r="GTN26" s="5"/>
+      <c r="GTP26" s="5"/>
+      <c r="GTR26" s="5"/>
+      <c r="GTT26" s="5"/>
+      <c r="GTV26" s="5"/>
+      <c r="GTX26" s="5"/>
+      <c r="GTZ26" s="5"/>
+      <c r="GUB26" s="5"/>
+      <c r="GUD26" s="5"/>
+      <c r="GUF26" s="5"/>
+      <c r="GUH26" s="5"/>
+      <c r="GUJ26" s="5"/>
+      <c r="GUL26" s="5"/>
+      <c r="GUN26" s="5"/>
+      <c r="GUP26" s="5"/>
+      <c r="GUR26" s="5"/>
+      <c r="GUT26" s="5"/>
+      <c r="GUV26" s="5"/>
+      <c r="GUX26" s="5"/>
+      <c r="GUZ26" s="5"/>
+      <c r="GVB26" s="5"/>
+      <c r="GVD26" s="5"/>
+      <c r="GVF26" s="5"/>
+      <c r="GVH26" s="5"/>
+      <c r="GVJ26" s="5"/>
+      <c r="GVL26" s="5"/>
+      <c r="GVN26" s="5"/>
+      <c r="GVP26" s="5"/>
+      <c r="GVR26" s="5"/>
+      <c r="GVT26" s="5"/>
+      <c r="GVV26" s="5"/>
+      <c r="GVX26" s="5"/>
+      <c r="GVZ26" s="5"/>
+      <c r="GWB26" s="5"/>
+      <c r="GWD26" s="5"/>
+      <c r="GWF26" s="5"/>
+      <c r="GWH26" s="5"/>
+      <c r="GWJ26" s="5"/>
+      <c r="GWL26" s="5"/>
+      <c r="GWN26" s="5"/>
+      <c r="GWP26" s="5"/>
+      <c r="GWR26" s="5"/>
+      <c r="GWT26" s="5"/>
+      <c r="GWV26" s="5"/>
+      <c r="GWX26" s="5"/>
+      <c r="GWZ26" s="5"/>
+      <c r="GXB26" s="5"/>
+      <c r="GXD26" s="5"/>
+      <c r="GXF26" s="5"/>
+      <c r="GXH26" s="5"/>
+      <c r="GXJ26" s="5"/>
+      <c r="GXL26" s="5"/>
+      <c r="GXN26" s="5"/>
+      <c r="GXP26" s="5"/>
+      <c r="GXR26" s="5"/>
+      <c r="GXT26" s="5"/>
+      <c r="GXV26" s="5"/>
+      <c r="GXX26" s="5"/>
+      <c r="GXZ26" s="5"/>
+      <c r="GYB26" s="5"/>
+      <c r="GYD26" s="5"/>
+      <c r="GYF26" s="5"/>
+      <c r="GYH26" s="5"/>
+      <c r="GYJ26" s="5"/>
+      <c r="GYL26" s="5"/>
+      <c r="GYN26" s="5"/>
+      <c r="GYP26" s="5"/>
+      <c r="GYR26" s="5"/>
+      <c r="GYT26" s="5"/>
+      <c r="GYV26" s="5"/>
+      <c r="GYX26" s="5"/>
+      <c r="GYZ26" s="5"/>
+      <c r="GZB26" s="5"/>
+      <c r="GZD26" s="5"/>
+      <c r="GZF26" s="5"/>
+      <c r="GZH26" s="5"/>
+      <c r="GZJ26" s="5"/>
+      <c r="GZL26" s="5"/>
+      <c r="GZN26" s="5"/>
+      <c r="GZP26" s="5"/>
+      <c r="GZR26" s="5"/>
+      <c r="GZT26" s="5"/>
+      <c r="GZV26" s="5"/>
+      <c r="GZX26" s="5"/>
+      <c r="GZZ26" s="5"/>
+      <c r="HAB26" s="5"/>
+      <c r="HAD26" s="5"/>
+      <c r="HAF26" s="5"/>
+      <c r="HAH26" s="5"/>
+      <c r="HAJ26" s="5"/>
+      <c r="HAL26" s="5"/>
+      <c r="HAN26" s="5"/>
+      <c r="HAP26" s="5"/>
+      <c r="HAR26" s="5"/>
+      <c r="HAT26" s="5"/>
+      <c r="HAV26" s="5"/>
+      <c r="HAX26" s="5"/>
+      <c r="HAZ26" s="5"/>
+      <c r="HBB26" s="5"/>
+      <c r="HBD26" s="5"/>
+      <c r="HBF26" s="5"/>
+      <c r="HBH26" s="5"/>
+      <c r="HBJ26" s="5"/>
+      <c r="HBL26" s="5"/>
+      <c r="HBN26" s="5"/>
+      <c r="HBP26" s="5"/>
+      <c r="HBR26" s="5"/>
+      <c r="HBT26" s="5"/>
+      <c r="HBV26" s="5"/>
+      <c r="HBX26" s="5"/>
+      <c r="HBZ26" s="5"/>
+      <c r="HCB26" s="5"/>
+      <c r="HCD26" s="5"/>
+      <c r="HCF26" s="5"/>
+      <c r="HCH26" s="5"/>
+      <c r="HCJ26" s="5"/>
+      <c r="HCL26" s="5"/>
+      <c r="HCN26" s="5"/>
+      <c r="HCP26" s="5"/>
+      <c r="HCR26" s="5"/>
+      <c r="HCT26" s="5"/>
+      <c r="HCV26" s="5"/>
+      <c r="HCX26" s="5"/>
+      <c r="HCZ26" s="5"/>
+      <c r="HDB26" s="5"/>
+      <c r="HDD26" s="5"/>
+      <c r="HDF26" s="5"/>
+      <c r="HDH26" s="5"/>
+      <c r="HDJ26" s="5"/>
+      <c r="HDL26" s="5"/>
+      <c r="HDN26" s="5"/>
+      <c r="HDP26" s="5"/>
+      <c r="HDR26" s="5"/>
+      <c r="HDT26" s="5"/>
+      <c r="HDV26" s="5"/>
+      <c r="HDX26" s="5"/>
+      <c r="HDZ26" s="5"/>
+      <c r="HEB26" s="5"/>
+      <c r="HED26" s="5"/>
+      <c r="HEF26" s="5"/>
+      <c r="HEH26" s="5"/>
+      <c r="HEJ26" s="5"/>
+      <c r="HEL26" s="5"/>
+      <c r="HEN26" s="5"/>
+      <c r="HEP26" s="5"/>
+      <c r="HER26" s="5"/>
+      <c r="HET26" s="5"/>
+      <c r="HEV26" s="5"/>
+      <c r="HEX26" s="5"/>
+      <c r="HEZ26" s="5"/>
+      <c r="HFB26" s="5"/>
+      <c r="HFD26" s="5"/>
+      <c r="HFF26" s="5"/>
+      <c r="HFH26" s="5"/>
+      <c r="HFJ26" s="5"/>
+      <c r="HFL26" s="5"/>
+      <c r="HFN26" s="5"/>
+      <c r="HFP26" s="5"/>
+      <c r="HFR26" s="5"/>
+      <c r="HFT26" s="5"/>
+      <c r="HFV26" s="5"/>
+      <c r="HFX26" s="5"/>
+      <c r="HFZ26" s="5"/>
+      <c r="HGB26" s="5"/>
+      <c r="HGD26" s="5"/>
+      <c r="HGF26" s="5"/>
+      <c r="HGH26" s="5"/>
+      <c r="HGJ26" s="5"/>
+      <c r="HGL26" s="5"/>
+      <c r="HGN26" s="5"/>
+      <c r="HGP26" s="5"/>
+      <c r="HGR26" s="5"/>
+      <c r="HGT26" s="5"/>
+      <c r="HGV26" s="5"/>
+      <c r="HGX26" s="5"/>
+      <c r="HGZ26" s="5"/>
+      <c r="HHB26" s="5"/>
+      <c r="HHD26" s="5"/>
+      <c r="HHF26" s="5"/>
+      <c r="HHH26" s="5"/>
+      <c r="HHJ26" s="5"/>
+      <c r="HHL26" s="5"/>
+      <c r="HHN26" s="5"/>
+      <c r="HHP26" s="5"/>
+      <c r="HHR26" s="5"/>
+      <c r="HHT26" s="5"/>
+      <c r="HHV26" s="5"/>
+      <c r="HHX26" s="5"/>
+      <c r="HHZ26" s="5"/>
+      <c r="HIB26" s="5"/>
+      <c r="HID26" s="5"/>
+      <c r="HIF26" s="5"/>
+      <c r="HIH26" s="5"/>
+      <c r="HIJ26" s="5"/>
+      <c r="HIL26" s="5"/>
+      <c r="HIN26" s="5"/>
+      <c r="HIP26" s="5"/>
+      <c r="HIR26" s="5"/>
+      <c r="HIT26" s="5"/>
+      <c r="HIV26" s="5"/>
+      <c r="HIX26" s="5"/>
+      <c r="HIZ26" s="5"/>
+      <c r="HJB26" s="5"/>
+      <c r="HJD26" s="5"/>
+      <c r="HJF26" s="5"/>
+      <c r="HJH26" s="5"/>
+      <c r="HJJ26" s="5"/>
+      <c r="HJL26" s="5"/>
+      <c r="HJN26" s="5"/>
+      <c r="HJP26" s="5"/>
+      <c r="HJR26" s="5"/>
+      <c r="HJT26" s="5"/>
+      <c r="HJV26" s="5"/>
+      <c r="HJX26" s="5"/>
+      <c r="HJZ26" s="5"/>
+      <c r="HKB26" s="5"/>
+      <c r="HKD26" s="5"/>
+      <c r="HKF26" s="5"/>
+      <c r="HKH26" s="5"/>
+      <c r="HKJ26" s="5"/>
+      <c r="HKL26" s="5"/>
+      <c r="HKN26" s="5"/>
+      <c r="HKP26" s="5"/>
+      <c r="HKR26" s="5"/>
+      <c r="HKT26" s="5"/>
+      <c r="HKV26" s="5"/>
+      <c r="HKX26" s="5"/>
+      <c r="HKZ26" s="5"/>
+      <c r="HLB26" s="5"/>
+      <c r="HLD26" s="5"/>
+      <c r="HLF26" s="5"/>
+      <c r="HLH26" s="5"/>
+      <c r="HLJ26" s="5"/>
+      <c r="HLL26" s="5"/>
+      <c r="HLN26" s="5"/>
+      <c r="HLP26" s="5"/>
+      <c r="HLR26" s="5"/>
+      <c r="HLT26" s="5"/>
+      <c r="HLV26" s="5"/>
+      <c r="HLX26" s="5"/>
+      <c r="HLZ26" s="5"/>
+      <c r="HMB26" s="5"/>
+      <c r="HMD26" s="5"/>
+      <c r="HMF26" s="5"/>
+      <c r="HMH26" s="5"/>
+      <c r="HMJ26" s="5"/>
+      <c r="HML26" s="5"/>
+      <c r="HMN26" s="5"/>
+      <c r="HMP26" s="5"/>
+      <c r="HMR26" s="5"/>
+      <c r="HMT26" s="5"/>
+      <c r="HMV26" s="5"/>
+      <c r="HMX26" s="5"/>
+      <c r="HMZ26" s="5"/>
+      <c r="HNB26" s="5"/>
+      <c r="HND26" s="5"/>
+      <c r="HNF26" s="5"/>
+      <c r="HNH26" s="5"/>
+      <c r="HNJ26" s="5"/>
+      <c r="HNL26" s="5"/>
+      <c r="HNN26" s="5"/>
+      <c r="HNP26" s="5"/>
+      <c r="HNR26" s="5"/>
+      <c r="HNT26" s="5"/>
+      <c r="HNV26" s="5"/>
+      <c r="HNX26" s="5"/>
+      <c r="HNZ26" s="5"/>
+      <c r="HOB26" s="5"/>
+      <c r="HOD26" s="5"/>
+      <c r="HOF26" s="5"/>
+      <c r="HOH26" s="5"/>
+      <c r="HOJ26" s="5"/>
+      <c r="HOL26" s="5"/>
+      <c r="HON26" s="5"/>
+      <c r="HOP26" s="5"/>
+      <c r="HOR26" s="5"/>
+      <c r="HOT26" s="5"/>
+      <c r="HOV26" s="5"/>
+      <c r="HOX26" s="5"/>
+      <c r="HOZ26" s="5"/>
+      <c r="HPB26" s="5"/>
+      <c r="HPD26" s="5"/>
+      <c r="HPF26" s="5"/>
+      <c r="HPH26" s="5"/>
+      <c r="HPJ26" s="5"/>
+      <c r="HPL26" s="5"/>
+      <c r="HPN26" s="5"/>
+      <c r="HPP26" s="5"/>
+      <c r="HPR26" s="5"/>
+      <c r="HPT26" s="5"/>
+      <c r="HPV26" s="5"/>
+      <c r="HPX26" s="5"/>
+      <c r="HPZ26" s="5"/>
+      <c r="HQB26" s="5"/>
+      <c r="HQD26" s="5"/>
+      <c r="HQF26" s="5"/>
+      <c r="HQH26" s="5"/>
+      <c r="HQJ26" s="5"/>
+      <c r="HQL26" s="5"/>
+      <c r="HQN26" s="5"/>
+      <c r="HQP26" s="5"/>
+      <c r="HQR26" s="5"/>
+      <c r="HQT26" s="5"/>
+      <c r="HQV26" s="5"/>
+      <c r="HQX26" s="5"/>
+      <c r="HQZ26" s="5"/>
+      <c r="HRB26" s="5"/>
+      <c r="HRD26" s="5"/>
+      <c r="HRF26" s="5"/>
+      <c r="HRH26" s="5"/>
+      <c r="HRJ26" s="5"/>
+      <c r="HRL26" s="5"/>
+      <c r="HRN26" s="5"/>
+      <c r="HRP26" s="5"/>
+      <c r="HRR26" s="5"/>
+      <c r="HRT26" s="5"/>
+      <c r="HRV26" s="5"/>
+      <c r="HRX26" s="5"/>
+      <c r="HRZ26" s="5"/>
+      <c r="HSB26" s="5"/>
+      <c r="HSD26" s="5"/>
+      <c r="HSF26" s="5"/>
+      <c r="HSH26" s="5"/>
+      <c r="HSJ26" s="5"/>
+      <c r="HSL26" s="5"/>
+      <c r="HSN26" s="5"/>
+      <c r="HSP26" s="5"/>
+      <c r="HSR26" s="5"/>
+      <c r="HST26" s="5"/>
+      <c r="HSV26" s="5"/>
+      <c r="HSX26" s="5"/>
+      <c r="HSZ26" s="5"/>
+      <c r="HTB26" s="5"/>
+      <c r="HTD26" s="5"/>
+      <c r="HTF26" s="5"/>
+      <c r="HTH26" s="5"/>
+      <c r="HTJ26" s="5"/>
+      <c r="HTL26" s="5"/>
+      <c r="HTN26" s="5"/>
+      <c r="HTP26" s="5"/>
+      <c r="HTR26" s="5"/>
+      <c r="HTT26" s="5"/>
+      <c r="HTV26" s="5"/>
+      <c r="HTX26" s="5"/>
+      <c r="HTZ26" s="5"/>
+      <c r="HUB26" s="5"/>
+      <c r="HUD26" s="5"/>
+      <c r="HUF26" s="5"/>
+      <c r="HUH26" s="5"/>
+      <c r="HUJ26" s="5"/>
+      <c r="HUL26" s="5"/>
+      <c r="HUN26" s="5"/>
+      <c r="HUP26" s="5"/>
+      <c r="HUR26" s="5"/>
+      <c r="HUT26" s="5"/>
+      <c r="HUV26" s="5"/>
+      <c r="HUX26" s="5"/>
+      <c r="HUZ26" s="5"/>
+      <c r="HVB26" s="5"/>
+      <c r="HVD26" s="5"/>
+      <c r="HVF26" s="5"/>
+      <c r="HVH26" s="5"/>
+      <c r="HVJ26" s="5"/>
+      <c r="HVL26" s="5"/>
+      <c r="HVN26" s="5"/>
+      <c r="HVP26" s="5"/>
+      <c r="HVR26" s="5"/>
+      <c r="HVT26" s="5"/>
+      <c r="HVV26" s="5"/>
+      <c r="HVX26" s="5"/>
+      <c r="HVZ26" s="5"/>
+      <c r="HWB26" s="5"/>
+      <c r="HWD26" s="5"/>
+      <c r="HWF26" s="5"/>
+      <c r="HWH26" s="5"/>
+      <c r="HWJ26" s="5"/>
+      <c r="HWL26" s="5"/>
+      <c r="HWN26" s="5"/>
+      <c r="HWP26" s="5"/>
+      <c r="HWR26" s="5"/>
+      <c r="HWT26" s="5"/>
+      <c r="HWV26" s="5"/>
+      <c r="HWX26" s="5"/>
+      <c r="HWZ26" s="5"/>
+      <c r="HXB26" s="5"/>
+      <c r="HXD26" s="5"/>
+      <c r="HXF26" s="5"/>
+      <c r="HXH26" s="5"/>
+      <c r="HXJ26" s="5"/>
+      <c r="HXL26" s="5"/>
+      <c r="HXN26" s="5"/>
+      <c r="HXP26" s="5"/>
+      <c r="HXR26" s="5"/>
+      <c r="HXT26" s="5"/>
+      <c r="HXV26" s="5"/>
+      <c r="HXX26" s="5"/>
+      <c r="HXZ26" s="5"/>
+      <c r="HYB26" s="5"/>
+      <c r="HYD26" s="5"/>
+      <c r="HYF26" s="5"/>
+      <c r="HYH26" s="5"/>
+      <c r="HYJ26" s="5"/>
+      <c r="HYL26" s="5"/>
+      <c r="HYN26" s="5"/>
+      <c r="HYP26" s="5"/>
+      <c r="HYR26" s="5"/>
+      <c r="HYT26" s="5"/>
+      <c r="HYV26" s="5"/>
+      <c r="HYX26" s="5"/>
+      <c r="HYZ26" s="5"/>
+      <c r="HZB26" s="5"/>
+      <c r="HZD26" s="5"/>
+      <c r="HZF26" s="5"/>
+      <c r="HZH26" s="5"/>
+      <c r="HZJ26" s="5"/>
+      <c r="HZL26" s="5"/>
+      <c r="HZN26" s="5"/>
+      <c r="HZP26" s="5"/>
+      <c r="HZR26" s="5"/>
+      <c r="HZT26" s="5"/>
+      <c r="HZV26" s="5"/>
+      <c r="HZX26" s="5"/>
+      <c r="HZZ26" s="5"/>
+      <c r="IAB26" s="5"/>
+      <c r="IAD26" s="5"/>
+      <c r="IAF26" s="5"/>
+      <c r="IAH26" s="5"/>
+      <c r="IAJ26" s="5"/>
+      <c r="IAL26" s="5"/>
+      <c r="IAN26" s="5"/>
+      <c r="IAP26" s="5"/>
+      <c r="IAR26" s="5"/>
+      <c r="IAT26" s="5"/>
+      <c r="IAV26" s="5"/>
+      <c r="IAX26" s="5"/>
+      <c r="IAZ26" s="5"/>
+      <c r="IBB26" s="5"/>
+      <c r="IBD26" s="5"/>
+      <c r="IBF26" s="5"/>
+      <c r="IBH26" s="5"/>
+      <c r="IBJ26" s="5"/>
+      <c r="IBL26" s="5"/>
+      <c r="IBN26" s="5"/>
+      <c r="IBP26" s="5"/>
+      <c r="IBR26" s="5"/>
+      <c r="IBT26" s="5"/>
+      <c r="IBV26" s="5"/>
+      <c r="IBX26" s="5"/>
+      <c r="IBZ26" s="5"/>
+      <c r="ICB26" s="5"/>
+      <c r="ICD26" s="5"/>
+      <c r="ICF26" s="5"/>
+      <c r="ICH26" s="5"/>
+      <c r="ICJ26" s="5"/>
+      <c r="ICL26" s="5"/>
+      <c r="ICN26" s="5"/>
+      <c r="ICP26" s="5"/>
+      <c r="ICR26" s="5"/>
+      <c r="ICT26" s="5"/>
+      <c r="ICV26" s="5"/>
+      <c r="ICX26" s="5"/>
+      <c r="ICZ26" s="5"/>
+      <c r="IDB26" s="5"/>
+      <c r="IDD26" s="5"/>
+      <c r="IDF26" s="5"/>
+      <c r="IDH26" s="5"/>
+      <c r="IDJ26" s="5"/>
+      <c r="IDL26" s="5"/>
+      <c r="IDN26" s="5"/>
+      <c r="IDP26" s="5"/>
+      <c r="IDR26" s="5"/>
+      <c r="IDT26" s="5"/>
+      <c r="IDV26" s="5"/>
+      <c r="IDX26" s="5"/>
+      <c r="IDZ26" s="5"/>
+      <c r="IEB26" s="5"/>
+      <c r="IED26" s="5"/>
+      <c r="IEF26" s="5"/>
+      <c r="IEH26" s="5"/>
+      <c r="IEJ26" s="5"/>
+      <c r="IEL26" s="5"/>
+      <c r="IEN26" s="5"/>
+      <c r="IEP26" s="5"/>
+      <c r="IER26" s="5"/>
+      <c r="IET26" s="5"/>
+      <c r="IEV26" s="5"/>
+      <c r="IEX26" s="5"/>
+      <c r="IEZ26" s="5"/>
+      <c r="IFB26" s="5"/>
+      <c r="IFD26" s="5"/>
+      <c r="IFF26" s="5"/>
+      <c r="IFH26" s="5"/>
+      <c r="IFJ26" s="5"/>
+      <c r="IFL26" s="5"/>
+      <c r="IFN26" s="5"/>
+      <c r="IFP26" s="5"/>
+      <c r="IFR26" s="5"/>
+      <c r="IFT26" s="5"/>
+      <c r="IFV26" s="5"/>
+      <c r="IFX26" s="5"/>
+      <c r="IFZ26" s="5"/>
+      <c r="IGB26" s="5"/>
+      <c r="IGD26" s="5"/>
+      <c r="IGF26" s="5"/>
+      <c r="IGH26" s="5"/>
+      <c r="IGJ26" s="5"/>
+      <c r="IGL26" s="5"/>
+      <c r="IGN26" s="5"/>
+      <c r="IGP26" s="5"/>
+      <c r="IGR26" s="5"/>
+      <c r="IGT26" s="5"/>
+      <c r="IGV26" s="5"/>
+      <c r="IGX26" s="5"/>
+      <c r="IGZ26" s="5"/>
+      <c r="IHB26" s="5"/>
+      <c r="IHD26" s="5"/>
+      <c r="IHF26" s="5"/>
+      <c r="IHH26" s="5"/>
+      <c r="IHJ26" s="5"/>
+      <c r="IHL26" s="5"/>
+      <c r="IHN26" s="5"/>
+      <c r="IHP26" s="5"/>
+      <c r="IHR26" s="5"/>
+      <c r="IHT26" s="5"/>
+      <c r="IHV26" s="5"/>
+      <c r="IHX26" s="5"/>
+      <c r="IHZ26" s="5"/>
+      <c r="IIB26" s="5"/>
+      <c r="IID26" s="5"/>
+      <c r="IIF26" s="5"/>
+      <c r="IIH26" s="5"/>
+      <c r="IIJ26" s="5"/>
+      <c r="IIL26" s="5"/>
+      <c r="IIN26" s="5"/>
+      <c r="IIP26" s="5"/>
+      <c r="IIR26" s="5"/>
+      <c r="IIT26" s="5"/>
+      <c r="IIV26" s="5"/>
+      <c r="IIX26" s="5"/>
+      <c r="IIZ26" s="5"/>
+      <c r="IJB26" s="5"/>
+      <c r="IJD26" s="5"/>
+      <c r="IJF26" s="5"/>
+      <c r="IJH26" s="5"/>
+      <c r="IJJ26" s="5"/>
+      <c r="IJL26" s="5"/>
+      <c r="IJN26" s="5"/>
+      <c r="IJP26" s="5"/>
+      <c r="IJR26" s="5"/>
+      <c r="IJT26" s="5"/>
+      <c r="IJV26" s="5"/>
+      <c r="IJX26" s="5"/>
+      <c r="IJZ26" s="5"/>
+      <c r="IKB26" s="5"/>
+      <c r="IKD26" s="5"/>
+      <c r="IKF26" s="5"/>
+      <c r="IKH26" s="5"/>
+      <c r="IKJ26" s="5"/>
+      <c r="IKL26" s="5"/>
+      <c r="IKN26" s="5"/>
+      <c r="IKP26" s="5"/>
+      <c r="IKR26" s="5"/>
+      <c r="IKT26" s="5"/>
+      <c r="IKV26" s="5"/>
+      <c r="IKX26" s="5"/>
+      <c r="IKZ26" s="5"/>
+      <c r="ILB26" s="5"/>
+      <c r="ILD26" s="5"/>
+      <c r="ILF26" s="5"/>
+      <c r="ILH26" s="5"/>
+      <c r="ILJ26" s="5"/>
+      <c r="ILL26" s="5"/>
+      <c r="ILN26" s="5"/>
+      <c r="ILP26" s="5"/>
+      <c r="ILR26" s="5"/>
+      <c r="ILT26" s="5"/>
+      <c r="ILV26" s="5"/>
+      <c r="ILX26" s="5"/>
+      <c r="ILZ26" s="5"/>
+      <c r="IMB26" s="5"/>
+      <c r="IMD26" s="5"/>
+      <c r="IMF26" s="5"/>
+      <c r="IMH26" s="5"/>
+      <c r="IMJ26" s="5"/>
+      <c r="IML26" s="5"/>
+      <c r="IMN26" s="5"/>
+      <c r="IMP26" s="5"/>
+      <c r="IMR26" s="5"/>
+      <c r="IMT26" s="5"/>
+      <c r="IMV26" s="5"/>
+      <c r="IMX26" s="5"/>
+      <c r="IMZ26" s="5"/>
+      <c r="INB26" s="5"/>
+      <c r="IND26" s="5"/>
+      <c r="INF26" s="5"/>
+      <c r="INH26" s="5"/>
+      <c r="INJ26" s="5"/>
+      <c r="INL26" s="5"/>
+      <c r="INN26" s="5"/>
+      <c r="INP26" s="5"/>
+      <c r="INR26" s="5"/>
+      <c r="INT26" s="5"/>
+      <c r="INV26" s="5"/>
+      <c r="INX26" s="5"/>
+      <c r="INZ26" s="5"/>
+      <c r="IOB26" s="5"/>
+      <c r="IOD26" s="5"/>
+      <c r="IOF26" s="5"/>
+      <c r="IOH26" s="5"/>
+      <c r="IOJ26" s="5"/>
+      <c r="IOL26" s="5"/>
+      <c r="ION26" s="5"/>
+      <c r="IOP26" s="5"/>
+      <c r="IOR26" s="5"/>
+      <c r="IOT26" s="5"/>
+      <c r="IOV26" s="5"/>
+      <c r="IOX26" s="5"/>
+      <c r="IOZ26" s="5"/>
+      <c r="IPB26" s="5"/>
+      <c r="IPD26" s="5"/>
+      <c r="IPF26" s="5"/>
+      <c r="IPH26" s="5"/>
+      <c r="IPJ26" s="5"/>
+      <c r="IPL26" s="5"/>
+      <c r="IPN26" s="5"/>
+      <c r="IPP26" s="5"/>
+      <c r="IPR26" s="5"/>
+      <c r="IPT26" s="5"/>
+      <c r="IPV26" s="5"/>
+      <c r="IPX26" s="5"/>
+      <c r="IPZ26" s="5"/>
+      <c r="IQB26" s="5"/>
+      <c r="IQD26" s="5"/>
+      <c r="IQF26" s="5"/>
+      <c r="IQH26" s="5"/>
+      <c r="IQJ26" s="5"/>
+      <c r="IQL26" s="5"/>
+      <c r="IQN26" s="5"/>
+      <c r="IQP26" s="5"/>
+      <c r="IQR26" s="5"/>
+      <c r="IQT26" s="5"/>
+      <c r="IQV26" s="5"/>
+      <c r="IQX26" s="5"/>
+      <c r="IQZ26" s="5"/>
+      <c r="IRB26" s="5"/>
+      <c r="IRD26" s="5"/>
+      <c r="IRF26" s="5"/>
+      <c r="IRH26" s="5"/>
+      <c r="IRJ26" s="5"/>
+      <c r="IRL26" s="5"/>
+      <c r="IRN26" s="5"/>
+      <c r="IRP26" s="5"/>
+      <c r="IRR26" s="5"/>
+      <c r="IRT26" s="5"/>
+      <c r="IRV26" s="5"/>
+      <c r="IRX26" s="5"/>
+      <c r="IRZ26" s="5"/>
+      <c r="ISB26" s="5"/>
+      <c r="ISD26" s="5"/>
+      <c r="ISF26" s="5"/>
+      <c r="ISH26" s="5"/>
+      <c r="ISJ26" s="5"/>
+      <c r="ISL26" s="5"/>
+      <c r="ISN26" s="5"/>
+      <c r="ISP26" s="5"/>
+      <c r="ISR26" s="5"/>
+      <c r="IST26" s="5"/>
+      <c r="ISV26" s="5"/>
+      <c r="ISX26" s="5"/>
+      <c r="ISZ26" s="5"/>
+      <c r="ITB26" s="5"/>
+      <c r="ITD26" s="5"/>
+      <c r="ITF26" s="5"/>
+      <c r="ITH26" s="5"/>
+      <c r="ITJ26" s="5"/>
+      <c r="ITL26" s="5"/>
+      <c r="ITN26" s="5"/>
+      <c r="ITP26" s="5"/>
+      <c r="ITR26" s="5"/>
+      <c r="ITT26" s="5"/>
+      <c r="ITV26" s="5"/>
+      <c r="ITX26" s="5"/>
+      <c r="ITZ26" s="5"/>
+      <c r="IUB26" s="5"/>
+      <c r="IUD26" s="5"/>
+      <c r="IUF26" s="5"/>
+      <c r="IUH26" s="5"/>
+      <c r="IUJ26" s="5"/>
+      <c r="IUL26" s="5"/>
+      <c r="IUN26" s="5"/>
+      <c r="IUP26" s="5"/>
+      <c r="IUR26" s="5"/>
+      <c r="IUT26" s="5"/>
+      <c r="IUV26" s="5"/>
+      <c r="IUX26" s="5"/>
+      <c r="IUZ26" s="5"/>
+      <c r="IVB26" s="5"/>
+      <c r="IVD26" s="5"/>
+      <c r="IVF26" s="5"/>
+      <c r="IVH26" s="5"/>
+      <c r="IVJ26" s="5"/>
+      <c r="IVL26" s="5"/>
+      <c r="IVN26" s="5"/>
+      <c r="IVP26" s="5"/>
+      <c r="IVR26" s="5"/>
+      <c r="IVT26" s="5"/>
+      <c r="IVV26" s="5"/>
+      <c r="IVX26" s="5"/>
+      <c r="IVZ26" s="5"/>
+      <c r="IWB26" s="5"/>
+      <c r="IWD26" s="5"/>
+      <c r="IWF26" s="5"/>
+      <c r="IWH26" s="5"/>
+      <c r="IWJ26" s="5"/>
+      <c r="IWL26" s="5"/>
+      <c r="IWN26" s="5"/>
+      <c r="IWP26" s="5"/>
+      <c r="IWR26" s="5"/>
+      <c r="IWT26" s="5"/>
+      <c r="IWV26" s="5"/>
+      <c r="IWX26" s="5"/>
+      <c r="IWZ26" s="5"/>
+      <c r="IXB26" s="5"/>
+      <c r="IXD26" s="5"/>
+      <c r="IXF26" s="5"/>
+      <c r="IXH26" s="5"/>
+      <c r="IXJ26" s="5"/>
+      <c r="IXL26" s="5"/>
+      <c r="IXN26" s="5"/>
+      <c r="IXP26" s="5"/>
+      <c r="IXR26" s="5"/>
+      <c r="IXT26" s="5"/>
+      <c r="IXV26" s="5"/>
+      <c r="IXX26" s="5"/>
+      <c r="IXZ26" s="5"/>
+      <c r="IYB26" s="5"/>
+      <c r="IYD26" s="5"/>
+      <c r="IYF26" s="5"/>
+      <c r="IYH26" s="5"/>
+      <c r="IYJ26" s="5"/>
+      <c r="IYL26" s="5"/>
+      <c r="IYN26" s="5"/>
+      <c r="IYP26" s="5"/>
+      <c r="IYR26" s="5"/>
+      <c r="IYT26" s="5"/>
+      <c r="IYV26" s="5"/>
+      <c r="IYX26" s="5"/>
+      <c r="IYZ26" s="5"/>
+      <c r="IZB26" s="5"/>
+      <c r="IZD26" s="5"/>
+      <c r="IZF26" s="5"/>
+      <c r="IZH26" s="5"/>
+      <c r="IZJ26" s="5"/>
+      <c r="IZL26" s="5"/>
+      <c r="IZN26" s="5"/>
+      <c r="IZP26" s="5"/>
+      <c r="IZR26" s="5"/>
+      <c r="IZT26" s="5"/>
+      <c r="IZV26" s="5"/>
+      <c r="IZX26" s="5"/>
+      <c r="IZZ26" s="5"/>
+      <c r="JAB26" s="5"/>
+      <c r="JAD26" s="5"/>
+      <c r="JAF26" s="5"/>
+      <c r="JAH26" s="5"/>
+      <c r="JAJ26" s="5"/>
+      <c r="JAL26" s="5"/>
+      <c r="JAN26" s="5"/>
+      <c r="JAP26" s="5"/>
+      <c r="JAR26" s="5"/>
+      <c r="JAT26" s="5"/>
+      <c r="JAV26" s="5"/>
+      <c r="JAX26" s="5"/>
+      <c r="JAZ26" s="5"/>
+      <c r="JBB26" s="5"/>
+      <c r="JBD26" s="5"/>
+      <c r="JBF26" s="5"/>
+      <c r="JBH26" s="5"/>
+      <c r="JBJ26" s="5"/>
+      <c r="JBL26" s="5"/>
+      <c r="JBN26" s="5"/>
+      <c r="JBP26" s="5"/>
+      <c r="JBR26" s="5"/>
+      <c r="JBT26" s="5"/>
+      <c r="JBV26" s="5"/>
+      <c r="JBX26" s="5"/>
+      <c r="JBZ26" s="5"/>
+      <c r="JCB26" s="5"/>
+      <c r="JCD26" s="5"/>
+      <c r="JCF26" s="5"/>
+      <c r="JCH26" s="5"/>
+      <c r="JCJ26" s="5"/>
+      <c r="JCL26" s="5"/>
+      <c r="JCN26" s="5"/>
+      <c r="JCP26" s="5"/>
+      <c r="JCR26" s="5"/>
+      <c r="JCT26" s="5"/>
+      <c r="JCV26" s="5"/>
+      <c r="JCX26" s="5"/>
+      <c r="JCZ26" s="5"/>
+      <c r="JDB26" s="5"/>
+      <c r="JDD26" s="5"/>
+      <c r="JDF26" s="5"/>
+      <c r="JDH26" s="5"/>
+      <c r="JDJ26" s="5"/>
+      <c r="JDL26" s="5"/>
+      <c r="JDN26" s="5"/>
+      <c r="JDP26" s="5"/>
+      <c r="JDR26" s="5"/>
+      <c r="JDT26" s="5"/>
+      <c r="JDV26" s="5"/>
+      <c r="JDX26" s="5"/>
+      <c r="JDZ26" s="5"/>
+      <c r="JEB26" s="5"/>
+      <c r="JED26" s="5"/>
+      <c r="JEF26" s="5"/>
+      <c r="JEH26" s="5"/>
+      <c r="JEJ26" s="5"/>
+      <c r="JEL26" s="5"/>
+      <c r="JEN26" s="5"/>
+      <c r="JEP26" s="5"/>
+      <c r="JER26" s="5"/>
+      <c r="JET26" s="5"/>
+      <c r="JEV26" s="5"/>
+      <c r="JEX26" s="5"/>
+      <c r="JEZ26" s="5"/>
+      <c r="JFB26" s="5"/>
+      <c r="JFD26" s="5"/>
+      <c r="JFF26" s="5"/>
+      <c r="JFH26" s="5"/>
+      <c r="JFJ26" s="5"/>
+      <c r="JFL26" s="5"/>
+      <c r="JFN26" s="5"/>
+      <c r="JFP26" s="5"/>
+      <c r="JFR26" s="5"/>
+      <c r="JFT26" s="5"/>
+      <c r="JFV26" s="5"/>
+      <c r="JFX26" s="5"/>
+      <c r="JFZ26" s="5"/>
+      <c r="JGB26" s="5"/>
+      <c r="JGD26" s="5"/>
+      <c r="JGF26" s="5"/>
+      <c r="JGH26" s="5"/>
+      <c r="JGJ26" s="5"/>
+      <c r="JGL26" s="5"/>
+      <c r="JGN26" s="5"/>
+      <c r="JGP26" s="5"/>
+      <c r="JGR26" s="5"/>
+      <c r="JGT26" s="5"/>
+      <c r="JGV26" s="5"/>
+      <c r="JGX26" s="5"/>
+      <c r="JGZ26" s="5"/>
+      <c r="JHB26" s="5"/>
+      <c r="JHD26" s="5"/>
+      <c r="JHF26" s="5"/>
+      <c r="JHH26" s="5"/>
+      <c r="JHJ26" s="5"/>
+      <c r="JHL26" s="5"/>
+      <c r="JHN26" s="5"/>
+      <c r="JHP26" s="5"/>
+      <c r="JHR26" s="5"/>
+      <c r="JHT26" s="5"/>
+      <c r="JHV26" s="5"/>
+      <c r="JHX26" s="5"/>
+      <c r="JHZ26" s="5"/>
+      <c r="JIB26" s="5"/>
+      <c r="JID26" s="5"/>
+      <c r="JIF26" s="5"/>
+      <c r="JIH26" s="5"/>
+      <c r="JIJ26" s="5"/>
+      <c r="JIL26" s="5"/>
+      <c r="JIN26" s="5"/>
+      <c r="JIP26" s="5"/>
+      <c r="JIR26" s="5"/>
+      <c r="JIT26" s="5"/>
+      <c r="JIV26" s="5"/>
+      <c r="JIX26" s="5"/>
+      <c r="JIZ26" s="5"/>
+      <c r="JJB26" s="5"/>
+      <c r="JJD26" s="5"/>
+      <c r="JJF26" s="5"/>
+      <c r="JJH26" s="5"/>
+      <c r="JJJ26" s="5"/>
+      <c r="JJL26" s="5"/>
+      <c r="JJN26" s="5"/>
+      <c r="JJP26" s="5"/>
+      <c r="JJR26" s="5"/>
+      <c r="JJT26" s="5"/>
+      <c r="JJV26" s="5"/>
+      <c r="JJX26" s="5"/>
+      <c r="JJZ26" s="5"/>
+      <c r="JKB26" s="5"/>
+      <c r="JKD26" s="5"/>
+      <c r="JKF26" s="5"/>
+      <c r="JKH26" s="5"/>
+      <c r="JKJ26" s="5"/>
+      <c r="JKL26" s="5"/>
+      <c r="JKN26" s="5"/>
+      <c r="JKP26" s="5"/>
+      <c r="JKR26" s="5"/>
+      <c r="JKT26" s="5"/>
+      <c r="JKV26" s="5"/>
+      <c r="JKX26" s="5"/>
+      <c r="JKZ26" s="5"/>
+      <c r="JLB26" s="5"/>
+      <c r="JLD26" s="5"/>
+      <c r="JLF26" s="5"/>
+      <c r="JLH26" s="5"/>
+      <c r="JLJ26" s="5"/>
+      <c r="JLL26" s="5"/>
+      <c r="JLN26" s="5"/>
+      <c r="JLP26" s="5"/>
+      <c r="JLR26" s="5"/>
+      <c r="JLT26" s="5"/>
+      <c r="JLV26" s="5"/>
+      <c r="JLX26" s="5"/>
+      <c r="JLZ26" s="5"/>
+      <c r="JMB26" s="5"/>
+      <c r="JMD26" s="5"/>
+      <c r="JMF26" s="5"/>
+      <c r="JMH26" s="5"/>
+      <c r="JMJ26" s="5"/>
+      <c r="JML26" s="5"/>
+      <c r="JMN26" s="5"/>
+      <c r="JMP26" s="5"/>
+      <c r="JMR26" s="5"/>
+      <c r="JMT26" s="5"/>
+      <c r="JMV26" s="5"/>
+      <c r="JMX26" s="5"/>
+      <c r="JMZ26" s="5"/>
+      <c r="JNB26" s="5"/>
+      <c r="JND26" s="5"/>
+      <c r="JNF26" s="5"/>
+      <c r="JNH26" s="5"/>
+      <c r="JNJ26" s="5"/>
+      <c r="JNL26" s="5"/>
+      <c r="JNN26" s="5"/>
+      <c r="JNP26" s="5"/>
+      <c r="JNR26" s="5"/>
+      <c r="JNT26" s="5"/>
+      <c r="JNV26" s="5"/>
+      <c r="JNX26" s="5"/>
+      <c r="JNZ26" s="5"/>
+      <c r="JOB26" s="5"/>
+      <c r="JOD26" s="5"/>
+      <c r="JOF26" s="5"/>
+      <c r="JOH26" s="5"/>
+      <c r="JOJ26" s="5"/>
+      <c r="JOL26" s="5"/>
+      <c r="JON26" s="5"/>
+      <c r="JOP26" s="5"/>
+      <c r="JOR26" s="5"/>
+      <c r="JOT26" s="5"/>
+      <c r="JOV26" s="5"/>
+      <c r="JOX26" s="5"/>
+      <c r="JOZ26" s="5"/>
+      <c r="JPB26" s="5"/>
+      <c r="JPD26" s="5"/>
+      <c r="JPF26" s="5"/>
+      <c r="JPH26" s="5"/>
+      <c r="JPJ26" s="5"/>
+      <c r="JPL26" s="5"/>
+      <c r="JPN26" s="5"/>
+      <c r="JPP26" s="5"/>
+      <c r="JPR26" s="5"/>
+      <c r="JPT26" s="5"/>
+      <c r="JPV26" s="5"/>
+      <c r="JPX26" s="5"/>
+      <c r="JPZ26" s="5"/>
+      <c r="JQB26" s="5"/>
+      <c r="JQD26" s="5"/>
+      <c r="JQF26" s="5"/>
+      <c r="JQH26" s="5"/>
+      <c r="JQJ26" s="5"/>
+      <c r="JQL26" s="5"/>
+      <c r="JQN26" s="5"/>
+      <c r="JQP26" s="5"/>
+      <c r="JQR26" s="5"/>
+      <c r="JQT26" s="5"/>
+      <c r="JQV26" s="5"/>
+      <c r="JQX26" s="5"/>
+      <c r="JQZ26" s="5"/>
+      <c r="JRB26" s="5"/>
+      <c r="JRD26" s="5"/>
+      <c r="JRF26" s="5"/>
+      <c r="JRH26" s="5"/>
+      <c r="JRJ26" s="5"/>
+      <c r="JRL26" s="5"/>
+      <c r="JRN26" s="5"/>
+      <c r="JRP26" s="5"/>
+      <c r="JRR26" s="5"/>
+      <c r="JRT26" s="5"/>
+      <c r="JRV26" s="5"/>
+      <c r="JRX26" s="5"/>
+      <c r="JRZ26" s="5"/>
+      <c r="JSB26" s="5"/>
+      <c r="JSD26" s="5"/>
+      <c r="JSF26" s="5"/>
+      <c r="JSH26" s="5"/>
+      <c r="JSJ26" s="5"/>
+      <c r="JSL26" s="5"/>
+      <c r="JSN26" s="5"/>
+      <c r="JSP26" s="5"/>
+      <c r="JSR26" s="5"/>
+      <c r="JST26" s="5"/>
+      <c r="JSV26" s="5"/>
+      <c r="JSX26" s="5"/>
+      <c r="JSZ26" s="5"/>
+      <c r="JTB26" s="5"/>
+      <c r="JTD26" s="5"/>
+      <c r="JTF26" s="5"/>
+      <c r="JTH26" s="5"/>
+      <c r="JTJ26" s="5"/>
+      <c r="JTL26" s="5"/>
+      <c r="JTN26" s="5"/>
+      <c r="JTP26" s="5"/>
+      <c r="JTR26" s="5"/>
+      <c r="JTT26" s="5"/>
+      <c r="JTV26" s="5"/>
+      <c r="JTX26" s="5"/>
+      <c r="JTZ26" s="5"/>
+      <c r="JUB26" s="5"/>
+      <c r="JUD26" s="5"/>
+      <c r="JUF26" s="5"/>
+      <c r="JUH26" s="5"/>
+      <c r="JUJ26" s="5"/>
+      <c r="JUL26" s="5"/>
+      <c r="JUN26" s="5"/>
+      <c r="JUP26" s="5"/>
+      <c r="JUR26" s="5"/>
+      <c r="JUT26" s="5"/>
+      <c r="JUV26" s="5"/>
+      <c r="JUX26" s="5"/>
+      <c r="JUZ26" s="5"/>
+      <c r="JVB26" s="5"/>
+      <c r="JVD26" s="5"/>
+      <c r="JVF26" s="5"/>
+      <c r="JVH26" s="5"/>
+      <c r="JVJ26" s="5"/>
+      <c r="JVL26" s="5"/>
+      <c r="JVN26" s="5"/>
+      <c r="JVP26" s="5"/>
+      <c r="JVR26" s="5"/>
+      <c r="JVT26" s="5"/>
+      <c r="JVV26" s="5"/>
+      <c r="JVX26" s="5"/>
+      <c r="JVZ26" s="5"/>
+      <c r="JWB26" s="5"/>
+      <c r="JWD26" s="5"/>
+      <c r="JWF26" s="5"/>
+      <c r="JWH26" s="5"/>
+      <c r="JWJ26" s="5"/>
+      <c r="JWL26" s="5"/>
+      <c r="JWN26" s="5"/>
+      <c r="JWP26" s="5"/>
+      <c r="JWR26" s="5"/>
+      <c r="JWT26" s="5"/>
+      <c r="JWV26" s="5"/>
+      <c r="JWX26" s="5"/>
+      <c r="JWZ26" s="5"/>
+      <c r="JXB26" s="5"/>
+      <c r="JXD26" s="5"/>
+      <c r="JXF26" s="5"/>
+      <c r="JXH26" s="5"/>
+      <c r="JXJ26" s="5"/>
+      <c r="JXL26" s="5"/>
+      <c r="JXN26" s="5"/>
+      <c r="JXP26" s="5"/>
+      <c r="JXR26" s="5"/>
+      <c r="JXT26" s="5"/>
+      <c r="JXV26" s="5"/>
+      <c r="JXX26" s="5"/>
+      <c r="JXZ26" s="5"/>
+      <c r="JYB26" s="5"/>
+      <c r="JYD26" s="5"/>
+      <c r="JYF26" s="5"/>
+      <c r="JYH26" s="5"/>
+      <c r="JYJ26" s="5"/>
+      <c r="JYL26" s="5"/>
+      <c r="JYN26" s="5"/>
+      <c r="JYP26" s="5"/>
+      <c r="JYR26" s="5"/>
+      <c r="JYT26" s="5"/>
+      <c r="JYV26" s="5"/>
+      <c r="JYX26" s="5"/>
+      <c r="JYZ26" s="5"/>
+      <c r="JZB26" s="5"/>
+      <c r="JZD26" s="5"/>
+      <c r="JZF26" s="5"/>
+      <c r="JZH26" s="5"/>
+      <c r="JZJ26" s="5"/>
+      <c r="JZL26" s="5"/>
+      <c r="JZN26" s="5"/>
+      <c r="JZP26" s="5"/>
+      <c r="JZR26" s="5"/>
+      <c r="JZT26" s="5"/>
+      <c r="JZV26" s="5"/>
+      <c r="JZX26" s="5"/>
+      <c r="JZZ26" s="5"/>
+      <c r="KAB26" s="5"/>
+      <c r="KAD26" s="5"/>
+      <c r="KAF26" s="5"/>
+      <c r="KAH26" s="5"/>
+      <c r="KAJ26" s="5"/>
+      <c r="KAL26" s="5"/>
+      <c r="KAN26" s="5"/>
+      <c r="KAP26" s="5"/>
+      <c r="KAR26" s="5"/>
+      <c r="KAT26" s="5"/>
+      <c r="KAV26" s="5"/>
+      <c r="KAX26" s="5"/>
+      <c r="KAZ26" s="5"/>
+      <c r="KBB26" s="5"/>
+      <c r="KBD26" s="5"/>
+      <c r="KBF26" s="5"/>
+      <c r="KBH26" s="5"/>
+      <c r="KBJ26" s="5"/>
+      <c r="KBL26" s="5"/>
+      <c r="KBN26" s="5"/>
+      <c r="KBP26" s="5"/>
+      <c r="KBR26" s="5"/>
+      <c r="KBT26" s="5"/>
+      <c r="KBV26" s="5"/>
+      <c r="KBX26" s="5"/>
+      <c r="KBZ26" s="5"/>
+      <c r="KCB26" s="5"/>
+      <c r="KCD26" s="5"/>
+      <c r="KCF26" s="5"/>
+      <c r="KCH26" s="5"/>
+      <c r="KCJ26" s="5"/>
+      <c r="KCL26" s="5"/>
+      <c r="KCN26" s="5"/>
+      <c r="KCP26" s="5"/>
+      <c r="KCR26" s="5"/>
+      <c r="KCT26" s="5"/>
+      <c r="KCV26" s="5"/>
+      <c r="KCX26" s="5"/>
+      <c r="KCZ26" s="5"/>
+      <c r="KDB26" s="5"/>
+      <c r="KDD26" s="5"/>
+      <c r="KDF26" s="5"/>
+      <c r="KDH26" s="5"/>
+      <c r="KDJ26" s="5"/>
+      <c r="KDL26" s="5"/>
+      <c r="KDN26" s="5"/>
+      <c r="KDP26" s="5"/>
+      <c r="KDR26" s="5"/>
+      <c r="KDT26" s="5"/>
+      <c r="KDV26" s="5"/>
+      <c r="KDX26" s="5"/>
+      <c r="KDZ26" s="5"/>
+      <c r="KEB26" s="5"/>
+      <c r="KED26" s="5"/>
+      <c r="KEF26" s="5"/>
+      <c r="KEH26" s="5"/>
+      <c r="KEJ26" s="5"/>
+      <c r="KEL26" s="5"/>
+      <c r="KEN26" s="5"/>
+      <c r="KEP26" s="5"/>
+      <c r="KER26" s="5"/>
+      <c r="KET26" s="5"/>
+      <c r="KEV26" s="5"/>
+      <c r="KEX26" s="5"/>
+      <c r="KEZ26" s="5"/>
+      <c r="KFB26" s="5"/>
+      <c r="KFD26" s="5"/>
+      <c r="KFF26" s="5"/>
+      <c r="KFH26" s="5"/>
+      <c r="KFJ26" s="5"/>
+      <c r="KFL26" s="5"/>
+      <c r="KFN26" s="5"/>
+      <c r="KFP26" s="5"/>
+      <c r="KFR26" s="5"/>
+      <c r="KFT26" s="5"/>
+      <c r="KFV26" s="5"/>
+      <c r="KFX26" s="5"/>
+      <c r="KFZ26" s="5"/>
+      <c r="KGB26" s="5"/>
+      <c r="KGD26" s="5"/>
+      <c r="KGF26" s="5"/>
+      <c r="KGH26" s="5"/>
+      <c r="KGJ26" s="5"/>
+      <c r="KGL26" s="5"/>
+      <c r="KGN26" s="5"/>
+      <c r="KGP26" s="5"/>
+      <c r="KGR26" s="5"/>
+      <c r="KGT26" s="5"/>
+      <c r="KGV26" s="5"/>
+      <c r="KGX26" s="5"/>
+      <c r="KGZ26" s="5"/>
+      <c r="KHB26" s="5"/>
+      <c r="KHD26" s="5"/>
+      <c r="KHF26" s="5"/>
+      <c r="KHH26" s="5"/>
+      <c r="KHJ26" s="5"/>
+      <c r="KHL26" s="5"/>
+      <c r="KHN26" s="5"/>
+      <c r="KHP26" s="5"/>
+      <c r="KHR26" s="5"/>
+      <c r="KHT26" s="5"/>
+      <c r="KHV26" s="5"/>
+      <c r="KHX26" s="5"/>
+      <c r="KHZ26" s="5"/>
+      <c r="KIB26" s="5"/>
+      <c r="KID26" s="5"/>
+      <c r="KIF26" s="5"/>
+      <c r="KIH26" s="5"/>
+      <c r="KIJ26" s="5"/>
+      <c r="KIL26" s="5"/>
+      <c r="KIN26" s="5"/>
+      <c r="KIP26" s="5"/>
+      <c r="KIR26" s="5"/>
+      <c r="KIT26" s="5"/>
+      <c r="KIV26" s="5"/>
+      <c r="KIX26" s="5"/>
+      <c r="KIZ26" s="5"/>
+      <c r="KJB26" s="5"/>
+      <c r="KJD26" s="5"/>
+      <c r="KJF26" s="5"/>
+      <c r="KJH26" s="5"/>
+      <c r="KJJ26" s="5"/>
+      <c r="KJL26" s="5"/>
+      <c r="KJN26" s="5"/>
+      <c r="KJP26" s="5"/>
+      <c r="KJR26" s="5"/>
+      <c r="KJT26" s="5"/>
+      <c r="KJV26" s="5"/>
+      <c r="KJX26" s="5"/>
+      <c r="KJZ26" s="5"/>
+      <c r="KKB26" s="5"/>
+      <c r="KKD26" s="5"/>
+      <c r="KKF26" s="5"/>
+      <c r="KKH26" s="5"/>
+      <c r="KKJ26" s="5"/>
+      <c r="KKL26" s="5"/>
+      <c r="KKN26" s="5"/>
+      <c r="KKP26" s="5"/>
+      <c r="KKR26" s="5"/>
+      <c r="KKT26" s="5"/>
+      <c r="KKV26" s="5"/>
+      <c r="KKX26" s="5"/>
+      <c r="KKZ26" s="5"/>
+      <c r="KLB26" s="5"/>
+      <c r="KLD26" s="5"/>
+      <c r="KLF26" s="5"/>
+      <c r="KLH26" s="5"/>
+      <c r="KLJ26" s="5"/>
+      <c r="KLL26" s="5"/>
+      <c r="KLN26" s="5"/>
+      <c r="KLP26" s="5"/>
+      <c r="KLR26" s="5"/>
+      <c r="KLT26" s="5"/>
+      <c r="KLV26" s="5"/>
+      <c r="KLX26" s="5"/>
+      <c r="KLZ26" s="5"/>
+      <c r="KMB26" s="5"/>
+      <c r="KMD26" s="5"/>
+      <c r="KMF26" s="5"/>
+      <c r="KMH26" s="5"/>
+      <c r="KMJ26" s="5"/>
+      <c r="KML26" s="5"/>
+      <c r="KMN26" s="5"/>
+      <c r="KMP26" s="5"/>
+      <c r="KMR26" s="5"/>
+      <c r="KMT26" s="5"/>
+      <c r="KMV26" s="5"/>
+      <c r="KMX26" s="5"/>
+      <c r="KMZ26" s="5"/>
+      <c r="KNB26" s="5"/>
+      <c r="KND26" s="5"/>
+      <c r="KNF26" s="5"/>
+      <c r="KNH26" s="5"/>
+      <c r="KNJ26" s="5"/>
+      <c r="KNL26" s="5"/>
+      <c r="KNN26" s="5"/>
+      <c r="KNP26" s="5"/>
+      <c r="KNR26" s="5"/>
+      <c r="KNT26" s="5"/>
+      <c r="KNV26" s="5"/>
+      <c r="KNX26" s="5"/>
+      <c r="KNZ26" s="5"/>
+      <c r="KOB26" s="5"/>
+      <c r="KOD26" s="5"/>
+      <c r="KOF26" s="5"/>
+      <c r="KOH26" s="5"/>
+      <c r="KOJ26" s="5"/>
+      <c r="KOL26" s="5"/>
+      <c r="KON26" s="5"/>
+      <c r="KOP26" s="5"/>
+      <c r="KOR26" s="5"/>
+      <c r="KOT26" s="5"/>
+      <c r="KOV26" s="5"/>
+      <c r="KOX26" s="5"/>
+      <c r="KOZ26" s="5"/>
+      <c r="KPB26" s="5"/>
+      <c r="KPD26" s="5"/>
+      <c r="KPF26" s="5"/>
+      <c r="KPH26" s="5"/>
+      <c r="KPJ26" s="5"/>
+      <c r="KPL26" s="5"/>
+      <c r="KPN26" s="5"/>
+      <c r="KPP26" s="5"/>
+      <c r="KPR26" s="5"/>
+      <c r="KPT26" s="5"/>
+      <c r="KPV26" s="5"/>
+      <c r="KPX26" s="5"/>
+      <c r="KPZ26" s="5"/>
+      <c r="KQB26" s="5"/>
+      <c r="KQD26" s="5"/>
+      <c r="KQF26" s="5"/>
+      <c r="KQH26" s="5"/>
+      <c r="KQJ26" s="5"/>
+      <c r="KQL26" s="5"/>
+      <c r="KQN26" s="5"/>
+      <c r="KQP26" s="5"/>
+      <c r="KQR26" s="5"/>
+      <c r="KQT26" s="5"/>
+      <c r="KQV26" s="5"/>
+      <c r="KQX26" s="5"/>
+      <c r="KQZ26" s="5"/>
+      <c r="KRB26" s="5"/>
+      <c r="KRD26" s="5"/>
+      <c r="KRF26" s="5"/>
+      <c r="KRH26" s="5"/>
+      <c r="KRJ26" s="5"/>
+      <c r="KRL26" s="5"/>
+      <c r="KRN26" s="5"/>
+      <c r="KRP26" s="5"/>
+      <c r="KRR26" s="5"/>
+      <c r="KRT26" s="5"/>
+      <c r="KRV26" s="5"/>
+      <c r="KRX26" s="5"/>
+      <c r="KRZ26" s="5"/>
+      <c r="KSB26" s="5"/>
+      <c r="KSD26" s="5"/>
+      <c r="KSF26" s="5"/>
+      <c r="KSH26" s="5"/>
+      <c r="KSJ26" s="5"/>
+      <c r="KSL26" s="5"/>
+      <c r="KSN26" s="5"/>
+      <c r="KSP26" s="5"/>
+      <c r="KSR26" s="5"/>
+      <c r="KST26" s="5"/>
+      <c r="KSV26" s="5"/>
+      <c r="KSX26" s="5"/>
+      <c r="KSZ26" s="5"/>
+      <c r="KTB26" s="5"/>
+      <c r="KTD26" s="5"/>
+      <c r="KTF26" s="5"/>
+      <c r="KTH26" s="5"/>
+      <c r="KTJ26" s="5"/>
+      <c r="KTL26" s="5"/>
+      <c r="KTN26" s="5"/>
+      <c r="KTP26" s="5"/>
+      <c r="KTR26" s="5"/>
+      <c r="KTT26" s="5"/>
+      <c r="KTV26" s="5"/>
+      <c r="KTX26" s="5"/>
+      <c r="KTZ26" s="5"/>
+      <c r="KUB26" s="5"/>
+      <c r="KUD26" s="5"/>
+      <c r="KUF26" s="5"/>
+      <c r="KUH26" s="5"/>
+      <c r="KUJ26" s="5"/>
+      <c r="KUL26" s="5"/>
+      <c r="KUN26" s="5"/>
+      <c r="KUP26" s="5"/>
+      <c r="KUR26" s="5"/>
+      <c r="KUT26" s="5"/>
+      <c r="KUV26" s="5"/>
+      <c r="KUX26" s="5"/>
+      <c r="KUZ26" s="5"/>
+      <c r="KVB26" s="5"/>
+      <c r="KVD26" s="5"/>
+      <c r="KVF26" s="5"/>
+      <c r="KVH26" s="5"/>
+      <c r="KVJ26" s="5"/>
+      <c r="KVL26" s="5"/>
+      <c r="KVN26" s="5"/>
+      <c r="KVP26" s="5"/>
+      <c r="KVR26" s="5"/>
+      <c r="KVT26" s="5"/>
+      <c r="KVV26" s="5"/>
+      <c r="KVX26" s="5"/>
+      <c r="KVZ26" s="5"/>
+      <c r="KWB26" s="5"/>
+      <c r="KWD26" s="5"/>
+      <c r="KWF26" s="5"/>
+      <c r="KWH26" s="5"/>
+      <c r="KWJ26" s="5"/>
+      <c r="KWL26" s="5"/>
+      <c r="KWN26" s="5"/>
+      <c r="KWP26" s="5"/>
+      <c r="KWR26" s="5"/>
+      <c r="KWT26" s="5"/>
+      <c r="KWV26" s="5"/>
+      <c r="KWX26" s="5"/>
+      <c r="KWZ26" s="5"/>
+      <c r="KXB26" s="5"/>
+      <c r="KXD26" s="5"/>
+      <c r="KXF26" s="5"/>
+      <c r="KXH26" s="5"/>
+      <c r="KXJ26" s="5"/>
+      <c r="KXL26" s="5"/>
+      <c r="KXN26" s="5"/>
+      <c r="KXP26" s="5"/>
+      <c r="KXR26" s="5"/>
+      <c r="KXT26" s="5"/>
+      <c r="KXV26" s="5"/>
+      <c r="KXX26" s="5"/>
+      <c r="KXZ26" s="5"/>
+      <c r="KYB26" s="5"/>
+      <c r="KYD26" s="5"/>
+      <c r="KYF26" s="5"/>
+      <c r="KYH26" s="5"/>
+      <c r="KYJ26" s="5"/>
+      <c r="KYL26" s="5"/>
+      <c r="KYN26" s="5"/>
+      <c r="KYP26" s="5"/>
+      <c r="KYR26" s="5"/>
+      <c r="KYT26" s="5"/>
+      <c r="KYV26" s="5"/>
+      <c r="KYX26" s="5"/>
+      <c r="KYZ26" s="5"/>
+      <c r="KZB26" s="5"/>
+      <c r="KZD26" s="5"/>
+      <c r="KZF26" s="5"/>
+      <c r="KZH26" s="5"/>
+      <c r="KZJ26" s="5"/>
+      <c r="KZL26" s="5"/>
+      <c r="KZN26" s="5"/>
+      <c r="KZP26" s="5"/>
+      <c r="KZR26" s="5"/>
+      <c r="KZT26" s="5"/>
+      <c r="KZV26" s="5"/>
+      <c r="KZX26" s="5"/>
+      <c r="KZZ26" s="5"/>
+      <c r="LAB26" s="5"/>
+      <c r="LAD26" s="5"/>
+      <c r="LAF26" s="5"/>
+      <c r="LAH26" s="5"/>
+      <c r="LAJ26" s="5"/>
+      <c r="LAL26" s="5"/>
+      <c r="LAN26" s="5"/>
+      <c r="LAP26" s="5"/>
+      <c r="LAR26" s="5"/>
+      <c r="LAT26" s="5"/>
+      <c r="LAV26" s="5"/>
+      <c r="LAX26" s="5"/>
+      <c r="LAZ26" s="5"/>
+      <c r="LBB26" s="5"/>
+      <c r="LBD26" s="5"/>
+      <c r="LBF26" s="5"/>
+      <c r="LBH26" s="5"/>
+      <c r="LBJ26" s="5"/>
+      <c r="LBL26" s="5"/>
+      <c r="LBN26" s="5"/>
+      <c r="LBP26" s="5"/>
+      <c r="LBR26" s="5"/>
+      <c r="LBT26" s="5"/>
+      <c r="LBV26" s="5"/>
+      <c r="LBX26" s="5"/>
+      <c r="LBZ26" s="5"/>
+      <c r="LCB26" s="5"/>
+      <c r="LCD26" s="5"/>
+      <c r="LCF26" s="5"/>
+      <c r="LCH26" s="5"/>
+      <c r="LCJ26" s="5"/>
+      <c r="LCL26" s="5"/>
+      <c r="LCN26" s="5"/>
+      <c r="LCP26" s="5"/>
+      <c r="LCR26" s="5"/>
+      <c r="LCT26" s="5"/>
+      <c r="LCV26" s="5"/>
+      <c r="LCX26" s="5"/>
+      <c r="LCZ26" s="5"/>
+      <c r="LDB26" s="5"/>
+      <c r="LDD26" s="5"/>
+      <c r="LDF26" s="5"/>
+      <c r="LDH26" s="5"/>
+      <c r="LDJ26" s="5"/>
+      <c r="LDL26" s="5"/>
+      <c r="LDN26" s="5"/>
+      <c r="LDP26" s="5"/>
+      <c r="LDR26" s="5"/>
+      <c r="LDT26" s="5"/>
+      <c r="LDV26" s="5"/>
+      <c r="LDX26" s="5"/>
+      <c r="LDZ26" s="5"/>
+      <c r="LEB26" s="5"/>
+      <c r="LED26" s="5"/>
+      <c r="LEF26" s="5"/>
+      <c r="LEH26" s="5"/>
+      <c r="LEJ26" s="5"/>
+      <c r="LEL26" s="5"/>
+      <c r="LEN26" s="5"/>
+      <c r="LEP26" s="5"/>
+      <c r="LER26" s="5"/>
+      <c r="LET26" s="5"/>
+      <c r="LEV26" s="5"/>
+      <c r="LEX26" s="5"/>
+      <c r="LEZ26" s="5"/>
+      <c r="LFB26" s="5"/>
+      <c r="LFD26" s="5"/>
+      <c r="LFF26" s="5"/>
+      <c r="LFH26" s="5"/>
+      <c r="LFJ26" s="5"/>
+      <c r="LFL26" s="5"/>
+      <c r="LFN26" s="5"/>
+      <c r="LFP26" s="5"/>
+      <c r="LFR26" s="5"/>
+      <c r="LFT26" s="5"/>
+      <c r="LFV26" s="5"/>
+      <c r="LFX26" s="5"/>
+      <c r="LFZ26" s="5"/>
+      <c r="LGB26" s="5"/>
+      <c r="LGD26" s="5"/>
+      <c r="LGF26" s="5"/>
+      <c r="LGH26" s="5"/>
+      <c r="LGJ26" s="5"/>
+      <c r="LGL26" s="5"/>
+      <c r="LGN26" s="5"/>
+      <c r="LGP26" s="5"/>
+      <c r="LGR26" s="5"/>
+      <c r="LGT26" s="5"/>
+      <c r="LGV26" s="5"/>
+      <c r="LGX26" s="5"/>
+      <c r="LGZ26" s="5"/>
+      <c r="LHB26" s="5"/>
+      <c r="LHD26" s="5"/>
+      <c r="LHF26" s="5"/>
+      <c r="LHH26" s="5"/>
+      <c r="LHJ26" s="5"/>
+      <c r="LHL26" s="5"/>
+      <c r="LHN26" s="5"/>
+      <c r="LHP26" s="5"/>
+      <c r="LHR26" s="5"/>
+      <c r="LHT26" s="5"/>
+      <c r="LHV26" s="5"/>
+      <c r="LHX26" s="5"/>
+      <c r="LHZ26" s="5"/>
+      <c r="LIB26" s="5"/>
+      <c r="LID26" s="5"/>
+      <c r="LIF26" s="5"/>
+      <c r="LIH26" s="5"/>
+      <c r="LIJ26" s="5"/>
+      <c r="LIL26" s="5"/>
+      <c r="LIN26" s="5"/>
+      <c r="LIP26" s="5"/>
+      <c r="LIR26" s="5"/>
+      <c r="LIT26" s="5"/>
+      <c r="LIV26" s="5"/>
+      <c r="LIX26" s="5"/>
+      <c r="LIZ26" s="5"/>
+      <c r="LJB26" s="5"/>
+      <c r="LJD26" s="5"/>
+      <c r="LJF26" s="5"/>
+      <c r="LJH26" s="5"/>
+      <c r="LJJ26" s="5"/>
+      <c r="LJL26" s="5"/>
+      <c r="LJN26" s="5"/>
+      <c r="LJP26" s="5"/>
+      <c r="LJR26" s="5"/>
+      <c r="LJT26" s="5"/>
+      <c r="LJV26" s="5"/>
+      <c r="LJX26" s="5"/>
+      <c r="LJZ26" s="5"/>
+      <c r="LKB26" s="5"/>
+      <c r="LKD26" s="5"/>
+      <c r="LKF26" s="5"/>
+      <c r="LKH26" s="5"/>
+      <c r="LKJ26" s="5"/>
+      <c r="LKL26" s="5"/>
+      <c r="LKN26" s="5"/>
+      <c r="LKP26" s="5"/>
+      <c r="LKR26" s="5"/>
+      <c r="LKT26" s="5"/>
+      <c r="LKV26" s="5"/>
+      <c r="LKX26" s="5"/>
+      <c r="LKZ26" s="5"/>
+      <c r="LLB26" s="5"/>
+      <c r="LLD26" s="5"/>
+      <c r="LLF26" s="5"/>
+      <c r="LLH26" s="5"/>
+      <c r="LLJ26" s="5"/>
+      <c r="LLL26" s="5"/>
+      <c r="LLN26" s="5"/>
+      <c r="LLP26" s="5"/>
+      <c r="LLR26" s="5"/>
+      <c r="LLT26" s="5"/>
+      <c r="LLV26" s="5"/>
+      <c r="LLX26" s="5"/>
+      <c r="LLZ26" s="5"/>
+      <c r="LMB26" s="5"/>
+      <c r="LMD26" s="5"/>
+      <c r="LMF26" s="5"/>
+      <c r="LMH26" s="5"/>
+      <c r="LMJ26" s="5"/>
+      <c r="LML26" s="5"/>
+      <c r="LMN26" s="5"/>
+      <c r="LMP26" s="5"/>
+      <c r="LMR26" s="5"/>
+      <c r="LMT26" s="5"/>
+      <c r="LMV26" s="5"/>
+      <c r="LMX26" s="5"/>
+      <c r="LMZ26" s="5"/>
+      <c r="LNB26" s="5"/>
+      <c r="LND26" s="5"/>
+      <c r="LNF26" s="5"/>
+      <c r="LNH26" s="5"/>
+      <c r="LNJ26" s="5"/>
+      <c r="LNL26" s="5"/>
+      <c r="LNN26" s="5"/>
+      <c r="LNP26" s="5"/>
+      <c r="LNR26" s="5"/>
+      <c r="LNT26" s="5"/>
+      <c r="LNV26" s="5"/>
+      <c r="LNX26" s="5"/>
+      <c r="LNZ26" s="5"/>
+      <c r="LOB26" s="5"/>
+      <c r="LOD26" s="5"/>
+      <c r="LOF26" s="5"/>
+      <c r="LOH26" s="5"/>
+      <c r="LOJ26" s="5"/>
+      <c r="LOL26" s="5"/>
+      <c r="LON26" s="5"/>
+      <c r="LOP26" s="5"/>
+      <c r="LOR26" s="5"/>
+      <c r="LOT26" s="5"/>
+      <c r="LOV26" s="5"/>
+      <c r="LOX26" s="5"/>
+      <c r="LOZ26" s="5"/>
+      <c r="LPB26" s="5"/>
+      <c r="LPD26" s="5"/>
+      <c r="LPF26" s="5"/>
+      <c r="LPH26" s="5"/>
+      <c r="LPJ26" s="5"/>
+      <c r="LPL26" s="5"/>
+      <c r="LPN26" s="5"/>
+      <c r="LPP26" s="5"/>
+      <c r="LPR26" s="5"/>
+      <c r="LPT26" s="5"/>
+      <c r="LPV26" s="5"/>
+      <c r="LPX26" s="5"/>
+      <c r="LPZ26" s="5"/>
+      <c r="LQB26" s="5"/>
+      <c r="LQD26" s="5"/>
+      <c r="LQF26" s="5"/>
+      <c r="LQH26" s="5"/>
+      <c r="LQJ26" s="5"/>
+      <c r="LQL26" s="5"/>
+      <c r="LQN26" s="5"/>
+      <c r="LQP26" s="5"/>
+      <c r="LQR26" s="5"/>
+      <c r="LQT26" s="5"/>
+      <c r="LQV26" s="5"/>
+      <c r="LQX26" s="5"/>
+      <c r="LQZ26" s="5"/>
+      <c r="LRB26" s="5"/>
+      <c r="LRD26" s="5"/>
+      <c r="LRF26" s="5"/>
+      <c r="LRH26" s="5"/>
+      <c r="LRJ26" s="5"/>
+      <c r="LRL26" s="5"/>
+      <c r="LRN26" s="5"/>
+      <c r="LRP26" s="5"/>
+      <c r="LRR26" s="5"/>
+      <c r="LRT26" s="5"/>
+      <c r="LRV26" s="5"/>
+      <c r="LRX26" s="5"/>
+      <c r="LRZ26" s="5"/>
+      <c r="LSB26" s="5"/>
+      <c r="LSD26" s="5"/>
+      <c r="LSF26" s="5"/>
+      <c r="LSH26" s="5"/>
+      <c r="LSJ26" s="5"/>
+      <c r="LSL26" s="5"/>
+      <c r="LSN26" s="5"/>
+      <c r="LSP26" s="5"/>
+      <c r="LSR26" s="5"/>
+      <c r="LST26" s="5"/>
+      <c r="LSV26" s="5"/>
+      <c r="LSX26" s="5"/>
+      <c r="LSZ26" s="5"/>
+      <c r="LTB26" s="5"/>
+      <c r="LTD26" s="5"/>
+      <c r="LTF26" s="5"/>
+      <c r="LTH26" s="5"/>
+      <c r="LTJ26" s="5"/>
+      <c r="LTL26" s="5"/>
+      <c r="LTN26" s="5"/>
+      <c r="LTP26" s="5"/>
+      <c r="LTR26" s="5"/>
+      <c r="LTT26" s="5"/>
+      <c r="LTV26" s="5"/>
+      <c r="LTX26" s="5"/>
+      <c r="LTZ26" s="5"/>
+      <c r="LUB26" s="5"/>
+      <c r="LUD26" s="5"/>
+      <c r="LUF26" s="5"/>
+      <c r="LUH26" s="5"/>
+      <c r="LUJ26" s="5"/>
+      <c r="LUL26" s="5"/>
+      <c r="LUN26" s="5"/>
+      <c r="LUP26" s="5"/>
+      <c r="LUR26" s="5"/>
+      <c r="LUT26" s="5"/>
+      <c r="LUV26" s="5"/>
+      <c r="LUX26" s="5"/>
+      <c r="LUZ26" s="5"/>
+      <c r="LVB26" s="5"/>
+      <c r="LVD26" s="5"/>
+      <c r="LVF26" s="5"/>
+      <c r="LVH26" s="5"/>
+      <c r="LVJ26" s="5"/>
+      <c r="LVL26" s="5"/>
+      <c r="LVN26" s="5"/>
+      <c r="LVP26" s="5"/>
+      <c r="LVR26" s="5"/>
+      <c r="LVT26" s="5"/>
+      <c r="LVV26" s="5"/>
+      <c r="LVX26" s="5"/>
+      <c r="LVZ26" s="5"/>
+      <c r="LWB26" s="5"/>
+      <c r="LWD26" s="5"/>
+      <c r="LWF26" s="5"/>
+      <c r="LWH26" s="5"/>
+      <c r="LWJ26" s="5"/>
+      <c r="LWL26" s="5"/>
+      <c r="LWN26" s="5"/>
+      <c r="LWP26" s="5"/>
+      <c r="LWR26" s="5"/>
+      <c r="LWT26" s="5"/>
+      <c r="LWV26" s="5"/>
+      <c r="LWX26" s="5"/>
+      <c r="LWZ26" s="5"/>
+      <c r="LXB26" s="5"/>
+      <c r="LXD26" s="5"/>
+      <c r="LXF26" s="5"/>
+      <c r="LXH26" s="5"/>
+      <c r="LXJ26" s="5"/>
+      <c r="LXL26" s="5"/>
+      <c r="LXN26" s="5"/>
+      <c r="LXP26" s="5"/>
+      <c r="LXR26" s="5"/>
+      <c r="LXT26" s="5"/>
+      <c r="LXV26" s="5"/>
+      <c r="LXX26" s="5"/>
+      <c r="LXZ26" s="5"/>
+      <c r="LYB26" s="5"/>
+      <c r="LYD26" s="5"/>
+      <c r="LYF26" s="5"/>
+      <c r="LYH26" s="5"/>
+      <c r="LYJ26" s="5"/>
+      <c r="LYL26" s="5"/>
+      <c r="LYN26" s="5"/>
+      <c r="LYP26" s="5"/>
+      <c r="LYR26" s="5"/>
+      <c r="LYT26" s="5"/>
+      <c r="LYV26" s="5"/>
+      <c r="LYX26" s="5"/>
+      <c r="LYZ26" s="5"/>
+      <c r="LZB26" s="5"/>
+      <c r="LZD26" s="5"/>
+      <c r="LZF26" s="5"/>
+      <c r="LZH26" s="5"/>
+      <c r="LZJ26" s="5"/>
+      <c r="LZL26" s="5"/>
+      <c r="LZN26" s="5"/>
+      <c r="LZP26" s="5"/>
+      <c r="LZR26" s="5"/>
+      <c r="LZT26" s="5"/>
+      <c r="LZV26" s="5"/>
+      <c r="LZX26" s="5"/>
+      <c r="LZZ26" s="5"/>
+      <c r="MAB26" s="5"/>
+      <c r="MAD26" s="5"/>
+      <c r="MAF26" s="5"/>
+      <c r="MAH26" s="5"/>
+      <c r="MAJ26" s="5"/>
+      <c r="MAL26" s="5"/>
+      <c r="MAN26" s="5"/>
+      <c r="MAP26" s="5"/>
+      <c r="MAR26" s="5"/>
+      <c r="MAT26" s="5"/>
+      <c r="MAV26" s="5"/>
+      <c r="MAX26" s="5"/>
+      <c r="MAZ26" s="5"/>
+      <c r="MBB26" s="5"/>
+      <c r="MBD26" s="5"/>
+      <c r="MBF26" s="5"/>
+      <c r="MBH26" s="5"/>
+      <c r="MBJ26" s="5"/>
+      <c r="MBL26" s="5"/>
+      <c r="MBN26" s="5"/>
+      <c r="MBP26" s="5"/>
+      <c r="MBR26" s="5"/>
+      <c r="MBT26" s="5"/>
+      <c r="MBV26" s="5"/>
+      <c r="MBX26" s="5"/>
+      <c r="MBZ26" s="5"/>
+      <c r="MCB26" s="5"/>
+      <c r="MCD26" s="5"/>
+      <c r="MCF26" s="5"/>
+      <c r="MCH26" s="5"/>
+      <c r="MCJ26" s="5"/>
+      <c r="MCL26" s="5"/>
+      <c r="MCN26" s="5"/>
+      <c r="MCP26" s="5"/>
+      <c r="MCR26" s="5"/>
+      <c r="MCT26" s="5"/>
+      <c r="MCV26" s="5"/>
+      <c r="MCX26" s="5"/>
+      <c r="MCZ26" s="5"/>
+      <c r="MDB26" s="5"/>
+      <c r="MDD26" s="5"/>
+      <c r="MDF26" s="5"/>
+      <c r="MDH26" s="5"/>
+      <c r="MDJ26" s="5"/>
+      <c r="MDL26" s="5"/>
+      <c r="MDN26" s="5"/>
+      <c r="MDP26" s="5"/>
+      <c r="MDR26" s="5"/>
+      <c r="MDT26" s="5"/>
+      <c r="MDV26" s="5"/>
+      <c r="MDX26" s="5"/>
+      <c r="MDZ26" s="5"/>
+      <c r="MEB26" s="5"/>
+      <c r="MED26" s="5"/>
+      <c r="MEF26" s="5"/>
+      <c r="MEH26" s="5"/>
+      <c r="MEJ26" s="5"/>
+      <c r="MEL26" s="5"/>
+      <c r="MEN26" s="5"/>
+      <c r="MEP26" s="5"/>
+      <c r="MER26" s="5"/>
+      <c r="MET26" s="5"/>
+      <c r="MEV26" s="5"/>
+      <c r="MEX26" s="5"/>
+      <c r="MEZ26" s="5"/>
+      <c r="MFB26" s="5"/>
+      <c r="MFD26" s="5"/>
+      <c r="MFF26" s="5"/>
+      <c r="MFH26" s="5"/>
+      <c r="MFJ26" s="5"/>
+      <c r="MFL26" s="5"/>
+      <c r="MFN26" s="5"/>
+      <c r="MFP26" s="5"/>
+      <c r="MFR26" s="5"/>
+      <c r="MFT26" s="5"/>
+      <c r="MFV26" s="5"/>
+      <c r="MFX26" s="5"/>
+      <c r="MFZ26" s="5"/>
+      <c r="MGB26" s="5"/>
+      <c r="MGD26" s="5"/>
+      <c r="MGF26" s="5"/>
+      <c r="MGH26" s="5"/>
+      <c r="MGJ26" s="5"/>
+      <c r="MGL26" s="5"/>
+      <c r="MGN26" s="5"/>
+      <c r="MGP26" s="5"/>
+      <c r="MGR26" s="5"/>
+      <c r="MGT26" s="5"/>
+      <c r="MGV26" s="5"/>
+      <c r="MGX26" s="5"/>
+      <c r="MGZ26" s="5"/>
+      <c r="MHB26" s="5"/>
+      <c r="MHD26" s="5"/>
+      <c r="MHF26" s="5"/>
+      <c r="MHH26" s="5"/>
+      <c r="MHJ26" s="5"/>
+      <c r="MHL26" s="5"/>
+      <c r="MHN26" s="5"/>
+      <c r="MHP26" s="5"/>
+      <c r="MHR26" s="5"/>
+      <c r="MHT26" s="5"/>
+      <c r="MHV26" s="5"/>
+      <c r="MHX26" s="5"/>
+      <c r="MHZ26" s="5"/>
+      <c r="MIB26" s="5"/>
+      <c r="MID26" s="5"/>
+      <c r="MIF26" s="5"/>
+      <c r="MIH26" s="5"/>
+      <c r="MIJ26" s="5"/>
+      <c r="MIL26" s="5"/>
+      <c r="MIN26" s="5"/>
+      <c r="MIP26" s="5"/>
+      <c r="MIR26" s="5"/>
+      <c r="MIT26" s="5"/>
+      <c r="MIV26" s="5"/>
+      <c r="MIX26" s="5"/>
+      <c r="MIZ26" s="5"/>
+      <c r="MJB26" s="5"/>
+      <c r="MJD26" s="5"/>
+      <c r="MJF26" s="5"/>
+      <c r="MJH26" s="5"/>
+      <c r="MJJ26" s="5"/>
+      <c r="MJL26" s="5"/>
+      <c r="MJN26" s="5"/>
+      <c r="MJP26" s="5"/>
+      <c r="MJR26" s="5"/>
+      <c r="MJT26" s="5"/>
+      <c r="MJV26" s="5"/>
+      <c r="MJX26" s="5"/>
+      <c r="MJZ26" s="5"/>
+      <c r="MKB26" s="5"/>
+      <c r="MKD26" s="5"/>
+      <c r="MKF26" s="5"/>
+      <c r="MKH26" s="5"/>
+      <c r="MKJ26" s="5"/>
+      <c r="MKL26" s="5"/>
+      <c r="MKN26" s="5"/>
+      <c r="MKP26" s="5"/>
+      <c r="MKR26" s="5"/>
+      <c r="MKT26" s="5"/>
+      <c r="MKV26" s="5"/>
+      <c r="MKX26" s="5"/>
+      <c r="MKZ26" s="5"/>
+      <c r="MLB26" s="5"/>
+      <c r="MLD26" s="5"/>
+      <c r="MLF26" s="5"/>
+      <c r="MLH26" s="5"/>
+      <c r="MLJ26" s="5"/>
+      <c r="MLL26" s="5"/>
+      <c r="MLN26" s="5"/>
+      <c r="MLP26" s="5"/>
+      <c r="MLR26" s="5"/>
+      <c r="MLT26" s="5"/>
+      <c r="MLV26" s="5"/>
+      <c r="MLX26" s="5"/>
+      <c r="MLZ26" s="5"/>
+      <c r="MMB26" s="5"/>
+      <c r="MMD26" s="5"/>
+      <c r="MMF26" s="5"/>
+      <c r="MMH26" s="5"/>
+      <c r="MMJ26" s="5"/>
+      <c r="MML26" s="5"/>
+      <c r="MMN26" s="5"/>
+      <c r="MMP26" s="5"/>
+      <c r="MMR26" s="5"/>
+      <c r="MMT26" s="5"/>
+      <c r="MMV26" s="5"/>
+      <c r="MMX26" s="5"/>
+      <c r="MMZ26" s="5"/>
+      <c r="MNB26" s="5"/>
+      <c r="MND26" s="5"/>
+      <c r="MNF26" s="5"/>
+      <c r="MNH26" s="5"/>
+      <c r="MNJ26" s="5"/>
+      <c r="MNL26" s="5"/>
+      <c r="MNN26" s="5"/>
+      <c r="MNP26" s="5"/>
+      <c r="MNR26" s="5"/>
+      <c r="MNT26" s="5"/>
+      <c r="MNV26" s="5"/>
+      <c r="MNX26" s="5"/>
+      <c r="MNZ26" s="5"/>
+      <c r="MOB26" s="5"/>
+      <c r="MOD26" s="5"/>
+      <c r="MOF26" s="5"/>
+      <c r="MOH26" s="5"/>
+      <c r="MOJ26" s="5"/>
+      <c r="MOL26" s="5"/>
+      <c r="MON26" s="5"/>
+      <c r="MOP26" s="5"/>
+      <c r="MOR26" s="5"/>
+      <c r="MOT26" s="5"/>
+      <c r="MOV26" s="5"/>
+      <c r="MOX26" s="5"/>
+      <c r="MOZ26" s="5"/>
+      <c r="MPB26" s="5"/>
+      <c r="MPD26" s="5"/>
+      <c r="MPF26" s="5"/>
+      <c r="MPH26" s="5"/>
+      <c r="MPJ26" s="5"/>
+      <c r="MPL26" s="5"/>
+      <c r="MPN26" s="5"/>
+      <c r="MPP26" s="5"/>
+      <c r="MPR26" s="5"/>
+      <c r="MPT26" s="5"/>
+      <c r="MPV26" s="5"/>
+      <c r="MPX26" s="5"/>
+      <c r="MPZ26" s="5"/>
+      <c r="MQB26" s="5"/>
+      <c r="MQD26" s="5"/>
+      <c r="MQF26" s="5"/>
+      <c r="MQH26" s="5"/>
+      <c r="MQJ26" s="5"/>
+      <c r="MQL26" s="5"/>
+      <c r="MQN26" s="5"/>
+      <c r="MQP26" s="5"/>
+      <c r="MQR26" s="5"/>
+      <c r="MQT26" s="5"/>
+      <c r="MQV26" s="5"/>
+      <c r="MQX26" s="5"/>
+      <c r="MQZ26" s="5"/>
+      <c r="MRB26" s="5"/>
+      <c r="MRD26" s="5"/>
+      <c r="MRF26" s="5"/>
+      <c r="MRH26" s="5"/>
+      <c r="MRJ26" s="5"/>
+      <c r="MRL26" s="5"/>
+      <c r="MRN26" s="5"/>
+      <c r="MRP26" s="5"/>
+      <c r="MRR26" s="5"/>
+      <c r="MRT26" s="5"/>
+      <c r="MRV26" s="5"/>
+      <c r="MRX26" s="5"/>
+      <c r="MRZ26" s="5"/>
+      <c r="MSB26" s="5"/>
+      <c r="MSD26" s="5"/>
+      <c r="MSF26" s="5"/>
+      <c r="MSH26" s="5"/>
+      <c r="MSJ26" s="5"/>
+      <c r="MSL26" s="5"/>
+      <c r="MSN26" s="5"/>
+      <c r="MSP26" s="5"/>
+      <c r="MSR26" s="5"/>
+      <c r="MST26" s="5"/>
+      <c r="MSV26" s="5"/>
+      <c r="MSX26" s="5"/>
+      <c r="MSZ26" s="5"/>
+      <c r="MTB26" s="5"/>
+      <c r="MTD26" s="5"/>
+      <c r="MTF26" s="5"/>
+      <c r="MTH26" s="5"/>
+      <c r="MTJ26" s="5"/>
+      <c r="MTL26" s="5"/>
+      <c r="MTN26" s="5"/>
+      <c r="MTP26" s="5"/>
+      <c r="MTR26" s="5"/>
+      <c r="MTT26" s="5"/>
+      <c r="MTV26" s="5"/>
+      <c r="MTX26" s="5"/>
+      <c r="MTZ26" s="5"/>
+      <c r="MUB26" s="5"/>
+      <c r="MUD26" s="5"/>
+      <c r="MUF26" s="5"/>
+      <c r="MUH26" s="5"/>
+      <c r="MUJ26" s="5"/>
+      <c r="MUL26" s="5"/>
+      <c r="MUN26" s="5"/>
+      <c r="MUP26" s="5"/>
+      <c r="MUR26" s="5"/>
+      <c r="MUT26" s="5"/>
+      <c r="MUV26" s="5"/>
+      <c r="MUX26" s="5"/>
+      <c r="MUZ26" s="5"/>
+      <c r="MVB26" s="5"/>
+      <c r="MVD26" s="5"/>
+      <c r="MVF26" s="5"/>
+      <c r="MVH26" s="5"/>
+      <c r="MVJ26" s="5"/>
+      <c r="MVL26" s="5"/>
+      <c r="MVN26" s="5"/>
+      <c r="MVP26" s="5"/>
+      <c r="MVR26" s="5"/>
+      <c r="MVT26" s="5"/>
+      <c r="MVV26" s="5"/>
+      <c r="MVX26" s="5"/>
+      <c r="MVZ26" s="5"/>
+      <c r="MWB26" s="5"/>
+      <c r="MWD26" s="5"/>
+      <c r="MWF26" s="5"/>
+      <c r="MWH26" s="5"/>
+      <c r="MWJ26" s="5"/>
+      <c r="MWL26" s="5"/>
+      <c r="MWN26" s="5"/>
+      <c r="MWP26" s="5"/>
+      <c r="MWR26" s="5"/>
+      <c r="MWT26" s="5"/>
+      <c r="MWV26" s="5"/>
+      <c r="MWX26" s="5"/>
+      <c r="MWZ26" s="5"/>
+      <c r="MXB26" s="5"/>
+      <c r="MXD26" s="5"/>
+      <c r="MXF26" s="5"/>
+      <c r="MXH26" s="5"/>
+      <c r="MXJ26" s="5"/>
+      <c r="MXL26" s="5"/>
+      <c r="MXN26" s="5"/>
+      <c r="MXP26" s="5"/>
+      <c r="MXR26" s="5"/>
+      <c r="MXT26" s="5"/>
+      <c r="MXV26" s="5"/>
+      <c r="MXX26" s="5"/>
+      <c r="MXZ26" s="5"/>
+      <c r="MYB26" s="5"/>
+      <c r="MYD26" s="5"/>
+      <c r="MYF26" s="5"/>
+      <c r="MYH26" s="5"/>
+      <c r="MYJ26" s="5"/>
+      <c r="MYL26" s="5"/>
+      <c r="MYN26" s="5"/>
+      <c r="MYP26" s="5"/>
+      <c r="MYR26" s="5"/>
+      <c r="MYT26" s="5"/>
+      <c r="MYV26" s="5"/>
+      <c r="MYX26" s="5"/>
+      <c r="MYZ26" s="5"/>
+      <c r="MZB26" s="5"/>
+      <c r="MZD26" s="5"/>
+      <c r="MZF26" s="5"/>
+      <c r="MZH26" s="5"/>
+      <c r="MZJ26" s="5"/>
+      <c r="MZL26" s="5"/>
+      <c r="MZN26" s="5"/>
+      <c r="MZP26" s="5"/>
+      <c r="MZR26" s="5"/>
+      <c r="MZT26" s="5"/>
+      <c r="MZV26" s="5"/>
+      <c r="MZX26" s="5"/>
+      <c r="MZZ26" s="5"/>
+      <c r="NAB26" s="5"/>
+      <c r="NAD26" s="5"/>
+      <c r="NAF26" s="5"/>
+      <c r="NAH26" s="5"/>
+      <c r="NAJ26" s="5"/>
+      <c r="NAL26" s="5"/>
+      <c r="NAN26" s="5"/>
+      <c r="NAP26" s="5"/>
+      <c r="NAR26" s="5"/>
+      <c r="NAT26" s="5"/>
+      <c r="NAV26" s="5"/>
+      <c r="NAX26" s="5"/>
+      <c r="NAZ26" s="5"/>
+      <c r="NBB26" s="5"/>
+      <c r="NBD26" s="5"/>
+      <c r="NBF26" s="5"/>
+      <c r="NBH26" s="5"/>
+      <c r="NBJ26" s="5"/>
+      <c r="NBL26" s="5"/>
+      <c r="NBN26" s="5"/>
+      <c r="NBP26" s="5"/>
+      <c r="NBR26" s="5"/>
+      <c r="NBT26" s="5"/>
+      <c r="NBV26" s="5"/>
+      <c r="NBX26" s="5"/>
+      <c r="NBZ26" s="5"/>
+      <c r="NCB26" s="5"/>
+      <c r="NCD26" s="5"/>
+      <c r="NCF26" s="5"/>
+      <c r="NCH26" s="5"/>
+      <c r="NCJ26" s="5"/>
+      <c r="NCL26" s="5"/>
+      <c r="NCN26" s="5"/>
+      <c r="NCP26" s="5"/>
+      <c r="NCR26" s="5"/>
+      <c r="NCT26" s="5"/>
+      <c r="NCV26" s="5"/>
+      <c r="NCX26" s="5"/>
+      <c r="NCZ26" s="5"/>
+      <c r="NDB26" s="5"/>
+      <c r="NDD26" s="5"/>
+      <c r="NDF26" s="5"/>
+      <c r="NDH26" s="5"/>
+      <c r="NDJ26" s="5"/>
+      <c r="NDL26" s="5"/>
+      <c r="NDN26" s="5"/>
+      <c r="NDP26" s="5"/>
+      <c r="NDR26" s="5"/>
+      <c r="NDT26" s="5"/>
+      <c r="NDV26" s="5"/>
+      <c r="NDX26" s="5"/>
+      <c r="NDZ26" s="5"/>
+      <c r="NEB26" s="5"/>
+      <c r="NED26" s="5"/>
+      <c r="NEF26" s="5"/>
+      <c r="NEH26" s="5"/>
+      <c r="NEJ26" s="5"/>
+      <c r="NEL26" s="5"/>
+      <c r="NEN26" s="5"/>
+      <c r="NEP26" s="5"/>
+      <c r="NER26" s="5"/>
+      <c r="NET26" s="5"/>
+      <c r="NEV26" s="5"/>
+      <c r="NEX26" s="5"/>
+      <c r="NEZ26" s="5"/>
+      <c r="NFB26" s="5"/>
+      <c r="NFD26" s="5"/>
+      <c r="NFF26" s="5"/>
+      <c r="NFH26" s="5"/>
+      <c r="NFJ26" s="5"/>
+      <c r="NFL26" s="5"/>
+      <c r="NFN26" s="5"/>
+      <c r="NFP26" s="5"/>
+      <c r="NFR26" s="5"/>
+      <c r="NFT26" s="5"/>
+      <c r="NFV26" s="5"/>
+      <c r="NFX26" s="5"/>
+      <c r="NFZ26" s="5"/>
+      <c r="NGB26" s="5"/>
+      <c r="NGD26" s="5"/>
+      <c r="NGF26" s="5"/>
+      <c r="NGH26" s="5"/>
+      <c r="NGJ26" s="5"/>
+      <c r="NGL26" s="5"/>
+      <c r="NGN26" s="5"/>
+      <c r="NGP26" s="5"/>
+      <c r="NGR26" s="5"/>
+      <c r="NGT26" s="5"/>
+      <c r="NGV26" s="5"/>
+      <c r="NGX26" s="5"/>
+      <c r="NGZ26" s="5"/>
+      <c r="NHB26" s="5"/>
+      <c r="NHD26" s="5"/>
+      <c r="NHF26" s="5"/>
+      <c r="NHH26" s="5"/>
+      <c r="NHJ26" s="5"/>
+      <c r="NHL26" s="5"/>
+      <c r="NHN26" s="5"/>
+      <c r="NHP26" s="5"/>
+      <c r="NHR26" s="5"/>
+      <c r="NHT26" s="5"/>
+      <c r="NHV26" s="5"/>
+      <c r="NHX26" s="5"/>
+      <c r="NHZ26" s="5"/>
+      <c r="NIB26" s="5"/>
+      <c r="NID26" s="5"/>
+      <c r="NIF26" s="5"/>
+      <c r="NIH26" s="5"/>
+      <c r="NIJ26" s="5"/>
+      <c r="NIL26" s="5"/>
+      <c r="NIN26" s="5"/>
+      <c r="NIP26" s="5"/>
+      <c r="NIR26" s="5"/>
+      <c r="NIT26" s="5"/>
+      <c r="NIV26" s="5"/>
+      <c r="NIX26" s="5"/>
+      <c r="NIZ26" s="5"/>
+      <c r="NJB26" s="5"/>
+      <c r="NJD26" s="5"/>
+      <c r="NJF26" s="5"/>
+      <c r="NJH26" s="5"/>
+      <c r="NJJ26" s="5"/>
+      <c r="NJL26" s="5"/>
+      <c r="NJN26" s="5"/>
+      <c r="NJP26" s="5"/>
+      <c r="NJR26" s="5"/>
+      <c r="NJT26" s="5"/>
+      <c r="NJV26" s="5"/>
+      <c r="NJX26" s="5"/>
+      <c r="NJZ26" s="5"/>
+      <c r="NKB26" s="5"/>
+      <c r="NKD26" s="5"/>
+      <c r="NKF26" s="5"/>
+      <c r="NKH26" s="5"/>
+      <c r="NKJ26" s="5"/>
+      <c r="NKL26" s="5"/>
+      <c r="NKN26" s="5"/>
+      <c r="NKP26" s="5"/>
+      <c r="NKR26" s="5"/>
+      <c r="NKT26" s="5"/>
+      <c r="NKV26" s="5"/>
+      <c r="NKX26" s="5"/>
+      <c r="NKZ26" s="5"/>
+      <c r="NLB26" s="5"/>
+      <c r="NLD26" s="5"/>
+      <c r="NLF26" s="5"/>
+      <c r="NLH26" s="5"/>
+      <c r="NLJ26" s="5"/>
+      <c r="NLL26" s="5"/>
+      <c r="NLN26" s="5"/>
+      <c r="NLP26" s="5"/>
+      <c r="NLR26" s="5"/>
+      <c r="NLT26" s="5"/>
+      <c r="NLV26" s="5"/>
+      <c r="NLX26" s="5"/>
+      <c r="NLZ26" s="5"/>
+      <c r="NMB26" s="5"/>
+      <c r="NMD26" s="5"/>
+      <c r="NMF26" s="5"/>
+      <c r="NMH26" s="5"/>
+      <c r="NMJ26" s="5"/>
+      <c r="NML26" s="5"/>
+      <c r="NMN26" s="5"/>
+      <c r="NMP26" s="5"/>
+      <c r="NMR26" s="5"/>
+      <c r="NMT26" s="5"/>
+      <c r="NMV26" s="5"/>
+      <c r="NMX26" s="5"/>
+      <c r="NMZ26" s="5"/>
+      <c r="NNB26" s="5"/>
+      <c r="NND26" s="5"/>
+      <c r="NNF26" s="5"/>
+      <c r="NNH26" s="5"/>
+      <c r="NNJ26" s="5"/>
+      <c r="NNL26" s="5"/>
+      <c r="NNN26" s="5"/>
+      <c r="NNP26" s="5"/>
+      <c r="NNR26" s="5"/>
+      <c r="NNT26" s="5"/>
+      <c r="NNV26" s="5"/>
+      <c r="NNX26" s="5"/>
+      <c r="NNZ26" s="5"/>
+      <c r="NOB26" s="5"/>
+      <c r="NOD26" s="5"/>
+      <c r="NOF26" s="5"/>
+      <c r="NOH26" s="5"/>
+      <c r="NOJ26" s="5"/>
+      <c r="NOL26" s="5"/>
+      <c r="NON26" s="5"/>
+      <c r="NOP26" s="5"/>
+      <c r="NOR26" s="5"/>
+      <c r="NOT26" s="5"/>
+      <c r="NOV26" s="5"/>
+      <c r="NOX26" s="5"/>
+      <c r="NOZ26" s="5"/>
+      <c r="NPB26" s="5"/>
+      <c r="NPD26" s="5"/>
+      <c r="NPF26" s="5"/>
+      <c r="NPH26" s="5"/>
+      <c r="NPJ26" s="5"/>
+      <c r="NPL26" s="5"/>
+      <c r="NPN26" s="5"/>
+      <c r="NPP26" s="5"/>
+      <c r="NPR26" s="5"/>
+      <c r="NPT26" s="5"/>
+      <c r="NPV26" s="5"/>
+      <c r="NPX26" s="5"/>
+      <c r="NPZ26" s="5"/>
+      <c r="NQB26" s="5"/>
+      <c r="NQD26" s="5"/>
+      <c r="NQF26" s="5"/>
+      <c r="NQH26" s="5"/>
+      <c r="NQJ26" s="5"/>
+      <c r="NQL26" s="5"/>
+      <c r="NQN26" s="5"/>
+      <c r="NQP26" s="5"/>
+      <c r="NQR26" s="5"/>
+      <c r="NQT26" s="5"/>
+      <c r="NQV26" s="5"/>
+      <c r="NQX26" s="5"/>
+      <c r="NQZ26" s="5"/>
+      <c r="NRB26" s="5"/>
+      <c r="NRD26" s="5"/>
+      <c r="NRF26" s="5"/>
+      <c r="NRH26" s="5"/>
+      <c r="NRJ26" s="5"/>
+      <c r="NRL26" s="5"/>
+      <c r="NRN26" s="5"/>
+      <c r="NRP26" s="5"/>
+      <c r="NRR26" s="5"/>
+      <c r="NRT26" s="5"/>
+      <c r="NRV26" s="5"/>
+      <c r="NRX26" s="5"/>
+      <c r="NRZ26" s="5"/>
+      <c r="NSB26" s="5"/>
+      <c r="NSD26" s="5"/>
+      <c r="NSF26" s="5"/>
+      <c r="NSH26" s="5"/>
+      <c r="NSJ26" s="5"/>
+      <c r="NSL26" s="5"/>
+      <c r="NSN26" s="5"/>
+      <c r="NSP26" s="5"/>
+      <c r="NSR26" s="5"/>
+      <c r="NST26" s="5"/>
+      <c r="NSV26" s="5"/>
+      <c r="NSX26" s="5"/>
+      <c r="NSZ26" s="5"/>
+      <c r="NTB26" s="5"/>
+      <c r="NTD26" s="5"/>
+      <c r="NTF26" s="5"/>
+      <c r="NTH26" s="5"/>
+      <c r="NTJ26" s="5"/>
+      <c r="NTL26" s="5"/>
+      <c r="NTN26" s="5"/>
+      <c r="NTP26" s="5"/>
+      <c r="NTR26" s="5"/>
+      <c r="NTT26" s="5"/>
+      <c r="NTV26" s="5"/>
+      <c r="NTX26" s="5"/>
+      <c r="NTZ26" s="5"/>
+      <c r="NUB26" s="5"/>
+      <c r="NUD26" s="5"/>
+      <c r="NUF26" s="5"/>
+      <c r="NUH26" s="5"/>
+      <c r="NUJ26" s="5"/>
+      <c r="NUL26" s="5"/>
+      <c r="NUN26" s="5"/>
+      <c r="NUP26" s="5"/>
+      <c r="NUR26" s="5"/>
+      <c r="NUT26" s="5"/>
+      <c r="NUV26" s="5"/>
+      <c r="NUX26" s="5"/>
+      <c r="NUZ26" s="5"/>
+      <c r="NVB26" s="5"/>
+      <c r="NVD26" s="5"/>
+      <c r="NVF26" s="5"/>
+      <c r="NVH26" s="5"/>
+      <c r="NVJ26" s="5"/>
+      <c r="NVL26" s="5"/>
+      <c r="NVN26" s="5"/>
+      <c r="NVP26" s="5"/>
+      <c r="NVR26" s="5"/>
+      <c r="NVT26" s="5"/>
+      <c r="NVV26" s="5"/>
+      <c r="NVX26" s="5"/>
+      <c r="NVZ26" s="5"/>
+      <c r="NWB26" s="5"/>
+      <c r="NWD26" s="5"/>
+      <c r="NWF26" s="5"/>
+      <c r="NWH26" s="5"/>
+      <c r="NWJ26" s="5"/>
+      <c r="NWL26" s="5"/>
+      <c r="NWN26" s="5"/>
+      <c r="NWP26" s="5"/>
+      <c r="NWR26" s="5"/>
+      <c r="NWT26" s="5"/>
+      <c r="NWV26" s="5"/>
+      <c r="NWX26" s="5"/>
+      <c r="NWZ26" s="5"/>
+      <c r="NXB26" s="5"/>
+      <c r="NXD26" s="5"/>
+      <c r="NXF26" s="5"/>
+      <c r="NXH26" s="5"/>
+      <c r="NXJ26" s="5"/>
+      <c r="NXL26" s="5"/>
+      <c r="NXN26" s="5"/>
+      <c r="NXP26" s="5"/>
+      <c r="NXR26" s="5"/>
+      <c r="NXT26" s="5"/>
+      <c r="NXV26" s="5"/>
+      <c r="NXX26" s="5"/>
+      <c r="NXZ26" s="5"/>
+      <c r="NYB26" s="5"/>
+      <c r="NYD26" s="5"/>
+      <c r="NYF26" s="5"/>
+      <c r="NYH26" s="5"/>
+      <c r="NYJ26" s="5"/>
+      <c r="NYL26" s="5"/>
+      <c r="NYN26" s="5"/>
+      <c r="NYP26" s="5"/>
+      <c r="NYR26" s="5"/>
+      <c r="NYT26" s="5"/>
+      <c r="NYV26" s="5"/>
+      <c r="NYX26" s="5"/>
+      <c r="NYZ26" s="5"/>
+      <c r="NZB26" s="5"/>
+      <c r="NZD26" s="5"/>
+      <c r="NZF26" s="5"/>
+      <c r="NZH26" s="5"/>
+      <c r="NZJ26" s="5"/>
+      <c r="NZL26" s="5"/>
+      <c r="NZN26" s="5"/>
+      <c r="NZP26" s="5"/>
+      <c r="NZR26" s="5"/>
+      <c r="NZT26" s="5"/>
+      <c r="NZV26" s="5"/>
+      <c r="NZX26" s="5"/>
+      <c r="NZZ26" s="5"/>
+      <c r="OAB26" s="5"/>
+      <c r="OAD26" s="5"/>
+      <c r="OAF26" s="5"/>
+      <c r="OAH26" s="5"/>
+      <c r="OAJ26" s="5"/>
+      <c r="OAL26" s="5"/>
+      <c r="OAN26" s="5"/>
+      <c r="OAP26" s="5"/>
+      <c r="OAR26" s="5"/>
+      <c r="OAT26" s="5"/>
+      <c r="OAV26" s="5"/>
+      <c r="OAX26" s="5"/>
+      <c r="OAZ26" s="5"/>
+      <c r="OBB26" s="5"/>
+      <c r="OBD26" s="5"/>
+      <c r="OBF26" s="5"/>
+      <c r="OBH26" s="5"/>
+      <c r="OBJ26" s="5"/>
+      <c r="OBL26" s="5"/>
+      <c r="OBN26" s="5"/>
+      <c r="OBP26" s="5"/>
+      <c r="OBR26" s="5"/>
+      <c r="OBT26" s="5"/>
+      <c r="OBV26" s="5"/>
+      <c r="OBX26" s="5"/>
+      <c r="OBZ26" s="5"/>
+      <c r="OCB26" s="5"/>
+      <c r="OCD26" s="5"/>
+      <c r="OCF26" s="5"/>
+      <c r="OCH26" s="5"/>
+      <c r="OCJ26" s="5"/>
+      <c r="OCL26" s="5"/>
+      <c r="OCN26" s="5"/>
+      <c r="OCP26" s="5"/>
+      <c r="OCR26" s="5"/>
+      <c r="OCT26" s="5"/>
+      <c r="OCV26" s="5"/>
+      <c r="OCX26" s="5"/>
+      <c r="OCZ26" s="5"/>
+      <c r="ODB26" s="5"/>
+      <c r="ODD26" s="5"/>
+      <c r="ODF26" s="5"/>
+      <c r="ODH26" s="5"/>
+      <c r="ODJ26" s="5"/>
+      <c r="ODL26" s="5"/>
+      <c r="ODN26" s="5"/>
+      <c r="ODP26" s="5"/>
+      <c r="ODR26" s="5"/>
+      <c r="ODT26" s="5"/>
+      <c r="ODV26" s="5"/>
+      <c r="ODX26" s="5"/>
+      <c r="ODZ26" s="5"/>
+      <c r="OEB26" s="5"/>
+      <c r="OED26" s="5"/>
+      <c r="OEF26" s="5"/>
+      <c r="OEH26" s="5"/>
+      <c r="OEJ26" s="5"/>
+      <c r="OEL26" s="5"/>
+      <c r="OEN26" s="5"/>
+      <c r="OEP26" s="5"/>
+      <c r="OER26" s="5"/>
+      <c r="OET26" s="5"/>
+      <c r="OEV26" s="5"/>
+      <c r="OEX26" s="5"/>
+      <c r="OEZ26" s="5"/>
+      <c r="OFB26" s="5"/>
+      <c r="OFD26" s="5"/>
+      <c r="OFF26" s="5"/>
+      <c r="OFH26" s="5"/>
+      <c r="OFJ26" s="5"/>
+      <c r="OFL26" s="5"/>
+      <c r="OFN26" s="5"/>
+      <c r="OFP26" s="5"/>
+      <c r="OFR26" s="5"/>
+      <c r="OFT26" s="5"/>
+      <c r="OFV26" s="5"/>
+      <c r="OFX26" s="5"/>
+      <c r="OFZ26" s="5"/>
+      <c r="OGB26" s="5"/>
+      <c r="OGD26" s="5"/>
+      <c r="OGF26" s="5"/>
+      <c r="OGH26" s="5"/>
+      <c r="OGJ26" s="5"/>
+      <c r="OGL26" s="5"/>
+      <c r="OGN26" s="5"/>
+      <c r="OGP26" s="5"/>
+      <c r="OGR26" s="5"/>
+      <c r="OGT26" s="5"/>
+      <c r="OGV26" s="5"/>
+      <c r="OGX26" s="5"/>
+      <c r="OGZ26" s="5"/>
+      <c r="OHB26" s="5"/>
+      <c r="OHD26" s="5"/>
+      <c r="OHF26" s="5"/>
+      <c r="OHH26" s="5"/>
+      <c r="OHJ26" s="5"/>
+      <c r="OHL26" s="5"/>
+      <c r="OHN26" s="5"/>
+      <c r="OHP26" s="5"/>
+      <c r="OHR26" s="5"/>
+      <c r="OHT26" s="5"/>
+      <c r="OHV26" s="5"/>
+      <c r="OHX26" s="5"/>
+      <c r="OHZ26" s="5"/>
+      <c r="OIB26" s="5"/>
+      <c r="OID26" s="5"/>
+      <c r="OIF26" s="5"/>
+      <c r="OIH26" s="5"/>
+      <c r="OIJ26" s="5"/>
+      <c r="OIL26" s="5"/>
+      <c r="OIN26" s="5"/>
+      <c r="OIP26" s="5"/>
+      <c r="OIR26" s="5"/>
+      <c r="OIT26" s="5"/>
+      <c r="OIV26" s="5"/>
+      <c r="OIX26" s="5"/>
+      <c r="OIZ26" s="5"/>
+      <c r="OJB26" s="5"/>
+      <c r="OJD26" s="5"/>
+      <c r="OJF26" s="5"/>
+      <c r="OJH26" s="5"/>
+      <c r="OJJ26" s="5"/>
+      <c r="OJL26" s="5"/>
+      <c r="OJN26" s="5"/>
+      <c r="OJP26" s="5"/>
+      <c r="OJR26" s="5"/>
+      <c r="OJT26" s="5"/>
+      <c r="OJV26" s="5"/>
+      <c r="OJX26" s="5"/>
+      <c r="OJZ26" s="5"/>
+      <c r="OKB26" s="5"/>
+      <c r="OKD26" s="5"/>
+      <c r="OKF26" s="5"/>
+      <c r="OKH26" s="5"/>
+      <c r="OKJ26" s="5"/>
+      <c r="OKL26" s="5"/>
+      <c r="OKN26" s="5"/>
+      <c r="OKP26" s="5"/>
+      <c r="OKR26" s="5"/>
+      <c r="OKT26" s="5"/>
+      <c r="OKV26" s="5"/>
+      <c r="OKX26" s="5"/>
+      <c r="OKZ26" s="5"/>
+      <c r="OLB26" s="5"/>
+      <c r="OLD26" s="5"/>
+      <c r="OLF26" s="5"/>
+      <c r="OLH26" s="5"/>
+      <c r="OLJ26" s="5"/>
+      <c r="OLL26" s="5"/>
+      <c r="OLN26" s="5"/>
+      <c r="OLP26" s="5"/>
+      <c r="OLR26" s="5"/>
+      <c r="OLT26" s="5"/>
+      <c r="OLV26" s="5"/>
+      <c r="OLX26" s="5"/>
+      <c r="OLZ26" s="5"/>
+      <c r="OMB26" s="5"/>
+      <c r="OMD26" s="5"/>
+      <c r="OMF26" s="5"/>
+      <c r="OMH26" s="5"/>
+      <c r="OMJ26" s="5"/>
+      <c r="OML26" s="5"/>
+      <c r="OMN26" s="5"/>
+      <c r="OMP26" s="5"/>
+      <c r="OMR26" s="5"/>
+      <c r="OMT26" s="5"/>
+      <c r="OMV26" s="5"/>
+      <c r="OMX26" s="5"/>
+      <c r="OMZ26" s="5"/>
+      <c r="ONB26" s="5"/>
+      <c r="OND26" s="5"/>
+      <c r="ONF26" s="5"/>
+      <c r="ONH26" s="5"/>
+      <c r="ONJ26" s="5"/>
+      <c r="ONL26" s="5"/>
+      <c r="ONN26" s="5"/>
+      <c r="ONP26" s="5"/>
+      <c r="ONR26" s="5"/>
+      <c r="ONT26" s="5"/>
+      <c r="ONV26" s="5"/>
+      <c r="ONX26" s="5"/>
+      <c r="ONZ26" s="5"/>
+      <c r="OOB26" s="5"/>
+      <c r="OOD26" s="5"/>
+      <c r="OOF26" s="5"/>
+      <c r="OOH26" s="5"/>
+      <c r="OOJ26" s="5"/>
+      <c r="OOL26" s="5"/>
+      <c r="OON26" s="5"/>
+      <c r="OOP26" s="5"/>
+      <c r="OOR26" s="5"/>
+      <c r="OOT26" s="5"/>
+      <c r="OOV26" s="5"/>
+      <c r="OOX26" s="5"/>
+      <c r="OOZ26" s="5"/>
+      <c r="OPB26" s="5"/>
+      <c r="OPD26" s="5"/>
+      <c r="OPF26" s="5"/>
+      <c r="OPH26" s="5"/>
+      <c r="OPJ26" s="5"/>
+      <c r="OPL26" s="5"/>
+      <c r="OPN26" s="5"/>
+      <c r="OPP26" s="5"/>
+      <c r="OPR26" s="5"/>
+      <c r="OPT26" s="5"/>
+      <c r="OPV26" s="5"/>
+      <c r="OPX26" s="5"/>
+      <c r="OPZ26" s="5"/>
+      <c r="OQB26" s="5"/>
+      <c r="OQD26" s="5"/>
+      <c r="OQF26" s="5"/>
+      <c r="OQH26" s="5"/>
+      <c r="OQJ26" s="5"/>
+      <c r="OQL26" s="5"/>
+      <c r="OQN26" s="5"/>
+      <c r="OQP26" s="5"/>
+      <c r="OQR26" s="5"/>
+      <c r="OQT26" s="5"/>
+      <c r="OQV26" s="5"/>
+      <c r="OQX26" s="5"/>
+      <c r="OQZ26" s="5"/>
+      <c r="ORB26" s="5"/>
+      <c r="ORD26" s="5"/>
+      <c r="ORF26" s="5"/>
+      <c r="ORH26" s="5"/>
+      <c r="ORJ26" s="5"/>
+      <c r="ORL26" s="5"/>
+      <c r="ORN26" s="5"/>
+      <c r="ORP26" s="5"/>
+      <c r="ORR26" s="5"/>
+      <c r="ORT26" s="5"/>
+      <c r="ORV26" s="5"/>
+      <c r="ORX26" s="5"/>
+      <c r="ORZ26" s="5"/>
+      <c r="OSB26" s="5"/>
+      <c r="OSD26" s="5"/>
+      <c r="OSF26" s="5"/>
+      <c r="OSH26" s="5"/>
+      <c r="OSJ26" s="5"/>
+      <c r="OSL26" s="5"/>
+      <c r="OSN26" s="5"/>
+      <c r="OSP26" s="5"/>
+      <c r="OSR26" s="5"/>
+      <c r="OST26" s="5"/>
+      <c r="OSV26" s="5"/>
+      <c r="OSX26" s="5"/>
+      <c r="OSZ26" s="5"/>
+      <c r="OTB26" s="5"/>
+      <c r="OTD26" s="5"/>
+      <c r="OTF26" s="5"/>
+      <c r="OTH26" s="5"/>
+      <c r="OTJ26" s="5"/>
+      <c r="OTL26" s="5"/>
+      <c r="OTN26" s="5"/>
+      <c r="OTP26" s="5"/>
+      <c r="OTR26" s="5"/>
+      <c r="OTT26" s="5"/>
+      <c r="OTV26" s="5"/>
+      <c r="OTX26" s="5"/>
+      <c r="OTZ26" s="5"/>
+      <c r="OUB26" s="5"/>
+      <c r="OUD26" s="5"/>
+      <c r="OUF26" s="5"/>
+      <c r="OUH26" s="5"/>
+      <c r="OUJ26" s="5"/>
+      <c r="OUL26" s="5"/>
+      <c r="OUN26" s="5"/>
+      <c r="OUP26" s="5"/>
+      <c r="OUR26" s="5"/>
+      <c r="OUT26" s="5"/>
+      <c r="OUV26" s="5"/>
+      <c r="OUX26" s="5"/>
+      <c r="OUZ26" s="5"/>
+      <c r="OVB26" s="5"/>
+      <c r="OVD26" s="5"/>
+      <c r="OVF26" s="5"/>
+      <c r="OVH26" s="5"/>
+      <c r="OVJ26" s="5"/>
+      <c r="OVL26" s="5"/>
+      <c r="OVN26" s="5"/>
+      <c r="OVP26" s="5"/>
+      <c r="OVR26" s="5"/>
+      <c r="OVT26" s="5"/>
+      <c r="OVV26" s="5"/>
+      <c r="OVX26" s="5"/>
+      <c r="OVZ26" s="5"/>
+      <c r="OWB26" s="5"/>
+      <c r="OWD26" s="5"/>
+      <c r="OWF26" s="5"/>
+      <c r="OWH26" s="5"/>
+      <c r="OWJ26" s="5"/>
+      <c r="OWL26" s="5"/>
+      <c r="OWN26" s="5"/>
+      <c r="OWP26" s="5"/>
+      <c r="OWR26" s="5"/>
+      <c r="OWT26" s="5"/>
+      <c r="OWV26" s="5"/>
+      <c r="OWX26" s="5"/>
+      <c r="OWZ26" s="5"/>
+      <c r="OXB26" s="5"/>
+      <c r="OXD26" s="5"/>
+      <c r="OXF26" s="5"/>
+      <c r="OXH26" s="5"/>
+      <c r="OXJ26" s="5"/>
+      <c r="OXL26" s="5"/>
+      <c r="OXN26" s="5"/>
+      <c r="OXP26" s="5"/>
+      <c r="OXR26" s="5"/>
+      <c r="OXT26" s="5"/>
+      <c r="OXV26" s="5"/>
+      <c r="OXX26" s="5"/>
+      <c r="OXZ26" s="5"/>
+      <c r="OYB26" s="5"/>
+      <c r="OYD26" s="5"/>
+      <c r="OYF26" s="5"/>
+      <c r="OYH26" s="5"/>
+      <c r="OYJ26" s="5"/>
+      <c r="OYL26" s="5"/>
+      <c r="OYN26" s="5"/>
+      <c r="OYP26" s="5"/>
+      <c r="OYR26" s="5"/>
+      <c r="OYT26" s="5"/>
+      <c r="OYV26" s="5"/>
+      <c r="OYX26" s="5"/>
+      <c r="OYZ26" s="5"/>
+      <c r="OZB26" s="5"/>
+      <c r="OZD26" s="5"/>
+      <c r="OZF26" s="5"/>
+      <c r="OZH26" s="5"/>
+      <c r="OZJ26" s="5"/>
+      <c r="OZL26" s="5"/>
+      <c r="OZN26" s="5"/>
+      <c r="OZP26" s="5"/>
+      <c r="OZR26" s="5"/>
+      <c r="OZT26" s="5"/>
+      <c r="OZV26" s="5"/>
+      <c r="OZX26" s="5"/>
+      <c r="OZZ26" s="5"/>
+      <c r="PAB26" s="5"/>
+      <c r="PAD26" s="5"/>
+      <c r="PAF26" s="5"/>
+      <c r="PAH26" s="5"/>
+      <c r="PAJ26" s="5"/>
+      <c r="PAL26" s="5"/>
+      <c r="PAN26" s="5"/>
+      <c r="PAP26" s="5"/>
+      <c r="PAR26" s="5"/>
+      <c r="PAT26" s="5"/>
+      <c r="PAV26" s="5"/>
+      <c r="PAX26" s="5"/>
+      <c r="PAZ26" s="5"/>
+      <c r="PBB26" s="5"/>
+      <c r="PBD26" s="5"/>
+      <c r="PBF26" s="5"/>
+      <c r="PBH26" s="5"/>
+      <c r="PBJ26" s="5"/>
+      <c r="PBL26" s="5"/>
+      <c r="PBN26" s="5"/>
+      <c r="PBP26" s="5"/>
+      <c r="PBR26" s="5"/>
+      <c r="PBT26" s="5"/>
+      <c r="PBV26" s="5"/>
+      <c r="PBX26" s="5"/>
+      <c r="PBZ26" s="5"/>
+      <c r="PCB26" s="5"/>
+      <c r="PCD26" s="5"/>
+      <c r="PCF26" s="5"/>
+      <c r="PCH26" s="5"/>
+      <c r="PCJ26" s="5"/>
+      <c r="PCL26" s="5"/>
+      <c r="PCN26" s="5"/>
+      <c r="PCP26" s="5"/>
+      <c r="PCR26" s="5"/>
+      <c r="PCT26" s="5"/>
+      <c r="PCV26" s="5"/>
+      <c r="PCX26" s="5"/>
+      <c r="PCZ26" s="5"/>
+      <c r="PDB26" s="5"/>
+      <c r="PDD26" s="5"/>
+      <c r="PDF26" s="5"/>
+      <c r="PDH26" s="5"/>
+      <c r="PDJ26" s="5"/>
+      <c r="PDL26" s="5"/>
+      <c r="PDN26" s="5"/>
+      <c r="PDP26" s="5"/>
+      <c r="PDR26" s="5"/>
+      <c r="PDT26" s="5"/>
+      <c r="PDV26" s="5"/>
+      <c r="PDX26" s="5"/>
+      <c r="PDZ26" s="5"/>
+      <c r="PEB26" s="5"/>
+      <c r="PED26" s="5"/>
+      <c r="PEF26" s="5"/>
+      <c r="PEH26" s="5"/>
+      <c r="PEJ26" s="5"/>
+      <c r="PEL26" s="5"/>
+      <c r="PEN26" s="5"/>
+      <c r="PEP26" s="5"/>
+      <c r="PER26" s="5"/>
+      <c r="PET26" s="5"/>
+      <c r="PEV26" s="5"/>
+      <c r="PEX26" s="5"/>
+      <c r="PEZ26" s="5"/>
+      <c r="PFB26" s="5"/>
+      <c r="PFD26" s="5"/>
+      <c r="PFF26" s="5"/>
+      <c r="PFH26" s="5"/>
+      <c r="PFJ26" s="5"/>
+      <c r="PFL26" s="5"/>
+      <c r="PFN26" s="5"/>
+      <c r="PFP26" s="5"/>
+      <c r="PFR26" s="5"/>
+      <c r="PFT26" s="5"/>
+      <c r="PFV26" s="5"/>
+      <c r="PFX26" s="5"/>
+      <c r="PFZ26" s="5"/>
+      <c r="PGB26" s="5"/>
+      <c r="PGD26" s="5"/>
+      <c r="PGF26" s="5"/>
+      <c r="PGH26" s="5"/>
+      <c r="PGJ26" s="5"/>
+      <c r="PGL26" s="5"/>
+      <c r="PGN26" s="5"/>
+      <c r="PGP26" s="5"/>
+      <c r="PGR26" s="5"/>
+      <c r="PGT26" s="5"/>
+      <c r="PGV26" s="5"/>
+      <c r="PGX26" s="5"/>
+      <c r="PGZ26" s="5"/>
+      <c r="PHB26" s="5"/>
+      <c r="PHD26" s="5"/>
+      <c r="PHF26" s="5"/>
+      <c r="PHH26" s="5"/>
+      <c r="PHJ26" s="5"/>
+      <c r="PHL26" s="5"/>
+      <c r="PHN26" s="5"/>
+      <c r="PHP26" s="5"/>
+      <c r="PHR26" s="5"/>
+      <c r="PHT26" s="5"/>
+      <c r="PHV26" s="5"/>
+      <c r="PHX26" s="5"/>
+      <c r="PHZ26" s="5"/>
+      <c r="PIB26" s="5"/>
+      <c r="PID26" s="5"/>
+      <c r="PIF26" s="5"/>
+      <c r="PIH26" s="5"/>
+      <c r="PIJ26" s="5"/>
+      <c r="PIL26" s="5"/>
+      <c r="PIN26" s="5"/>
+      <c r="PIP26" s="5"/>
+      <c r="PIR26" s="5"/>
+      <c r="PIT26" s="5"/>
+      <c r="PIV26" s="5"/>
+      <c r="PIX26" s="5"/>
+      <c r="PIZ26" s="5"/>
+      <c r="PJB26" s="5"/>
+      <c r="PJD26" s="5"/>
+      <c r="PJF26" s="5"/>
+      <c r="PJH26" s="5"/>
+      <c r="PJJ26" s="5"/>
+      <c r="PJL26" s="5"/>
+      <c r="PJN26" s="5"/>
+      <c r="PJP26" s="5"/>
+      <c r="PJR26" s="5"/>
+      <c r="PJT26" s="5"/>
+      <c r="PJV26" s="5"/>
+      <c r="PJX26" s="5"/>
+      <c r="PJZ26" s="5"/>
+      <c r="PKB26" s="5"/>
+      <c r="PKD26" s="5"/>
+      <c r="PKF26" s="5"/>
+      <c r="PKH26" s="5"/>
+      <c r="PKJ26" s="5"/>
+      <c r="PKL26" s="5"/>
+      <c r="PKN26" s="5"/>
+      <c r="PKP26" s="5"/>
+      <c r="PKR26" s="5"/>
+      <c r="PKT26" s="5"/>
+      <c r="PKV26" s="5"/>
+      <c r="PKX26" s="5"/>
+      <c r="PKZ26" s="5"/>
+      <c r="PLB26" s="5"/>
+      <c r="PLD26" s="5"/>
+      <c r="PLF26" s="5"/>
+      <c r="PLH26" s="5"/>
+      <c r="PLJ26" s="5"/>
+      <c r="PLL26" s="5"/>
+      <c r="PLN26" s="5"/>
+      <c r="PLP26" s="5"/>
+      <c r="PLR26" s="5"/>
+      <c r="PLT26" s="5"/>
+      <c r="PLV26" s="5"/>
+      <c r="PLX26" s="5"/>
+      <c r="PLZ26" s="5"/>
+      <c r="PMB26" s="5"/>
+      <c r="PMD26" s="5"/>
+      <c r="PMF26" s="5"/>
+      <c r="PMH26" s="5"/>
+      <c r="PMJ26" s="5"/>
+      <c r="PML26" s="5"/>
+      <c r="PMN26" s="5"/>
+      <c r="PMP26" s="5"/>
+      <c r="PMR26" s="5"/>
+      <c r="PMT26" s="5"/>
+      <c r="PMV26" s="5"/>
+      <c r="PMX26" s="5"/>
+      <c r="PMZ26" s="5"/>
+      <c r="PNB26" s="5"/>
+      <c r="PND26" s="5"/>
+      <c r="PNF26" s="5"/>
+      <c r="PNH26" s="5"/>
+      <c r="PNJ26" s="5"/>
+      <c r="PNL26" s="5"/>
+      <c r="PNN26" s="5"/>
+      <c r="PNP26" s="5"/>
+      <c r="PNR26" s="5"/>
+      <c r="PNT26" s="5"/>
+      <c r="PNV26" s="5"/>
+      <c r="PNX26" s="5"/>
+      <c r="PNZ26" s="5"/>
+      <c r="POB26" s="5"/>
+      <c r="POD26" s="5"/>
+      <c r="POF26" s="5"/>
+      <c r="POH26" s="5"/>
+      <c r="POJ26" s="5"/>
+      <c r="POL26" s="5"/>
+      <c r="PON26" s="5"/>
+      <c r="POP26" s="5"/>
+      <c r="POR26" s="5"/>
+      <c r="POT26" s="5"/>
+      <c r="POV26" s="5"/>
+      <c r="POX26" s="5"/>
+      <c r="POZ26" s="5"/>
+      <c r="PPB26" s="5"/>
+      <c r="PPD26" s="5"/>
+      <c r="PPF26" s="5"/>
+      <c r="PPH26" s="5"/>
+      <c r="PPJ26" s="5"/>
+      <c r="PPL26" s="5"/>
+      <c r="PPN26" s="5"/>
+      <c r="PPP26" s="5"/>
+      <c r="PPR26" s="5"/>
+      <c r="PPT26" s="5"/>
+      <c r="PPV26" s="5"/>
+      <c r="PPX26" s="5"/>
+      <c r="PPZ26" s="5"/>
+      <c r="PQB26" s="5"/>
+      <c r="PQD26" s="5"/>
+      <c r="PQF26" s="5"/>
+      <c r="PQH26" s="5"/>
+      <c r="PQJ26" s="5"/>
+      <c r="PQL26" s="5"/>
+      <c r="PQN26" s="5"/>
+      <c r="PQP26" s="5"/>
+      <c r="PQR26" s="5"/>
+      <c r="PQT26" s="5"/>
+      <c r="PQV26" s="5"/>
+      <c r="PQX26" s="5"/>
+      <c r="PQZ26" s="5"/>
+      <c r="PRB26" s="5"/>
+      <c r="PRD26" s="5"/>
+      <c r="PRF26" s="5"/>
+      <c r="PRH26" s="5"/>
+      <c r="PRJ26" s="5"/>
+      <c r="PRL26" s="5"/>
+      <c r="PRN26" s="5"/>
+      <c r="PRP26" s="5"/>
+      <c r="PRR26" s="5"/>
+      <c r="PRT26" s="5"/>
+      <c r="PRV26" s="5"/>
+      <c r="PRX26" s="5"/>
+      <c r="PRZ26" s="5"/>
+      <c r="PSB26" s="5"/>
+      <c r="PSD26" s="5"/>
+      <c r="PSF26" s="5"/>
+      <c r="PSH26" s="5"/>
+      <c r="PSJ26" s="5"/>
+      <c r="PSL26" s="5"/>
+      <c r="PSN26" s="5"/>
+      <c r="PSP26" s="5"/>
+      <c r="PSR26" s="5"/>
+      <c r="PST26" s="5"/>
+      <c r="PSV26" s="5"/>
+      <c r="PSX26" s="5"/>
+      <c r="PSZ26" s="5"/>
+      <c r="PTB26" s="5"/>
+      <c r="PTD26" s="5"/>
+      <c r="PTF26" s="5"/>
+      <c r="PTH26" s="5"/>
+      <c r="PTJ26" s="5"/>
+      <c r="PTL26" s="5"/>
+      <c r="PTN26" s="5"/>
+      <c r="PTP26" s="5"/>
+      <c r="PTR26" s="5"/>
+      <c r="PTT26" s="5"/>
+      <c r="PTV26" s="5"/>
+      <c r="PTX26" s="5"/>
+      <c r="PTZ26" s="5"/>
+      <c r="PUB26" s="5"/>
+      <c r="PUD26" s="5"/>
+      <c r="PUF26" s="5"/>
+      <c r="PUH26" s="5"/>
+      <c r="PUJ26" s="5"/>
+      <c r="PUL26" s="5"/>
+      <c r="PUN26" s="5"/>
+      <c r="PUP26" s="5"/>
+      <c r="PUR26" s="5"/>
+      <c r="PUT26" s="5"/>
+      <c r="PUV26" s="5"/>
+      <c r="PUX26" s="5"/>
+      <c r="PUZ26" s="5"/>
+      <c r="PVB26" s="5"/>
+      <c r="PVD26" s="5"/>
+      <c r="PVF26" s="5"/>
+      <c r="PVH26" s="5"/>
+      <c r="PVJ26" s="5"/>
+      <c r="PVL26" s="5"/>
+      <c r="PVN26" s="5"/>
+      <c r="PVP26" s="5"/>
+      <c r="PVR26" s="5"/>
+      <c r="PVT26" s="5"/>
+      <c r="PVV26" s="5"/>
+      <c r="PVX26" s="5"/>
+      <c r="PVZ26" s="5"/>
+      <c r="PWB26" s="5"/>
+      <c r="PWD26" s="5"/>
+      <c r="PWF26" s="5"/>
+      <c r="PWH26" s="5"/>
+      <c r="PWJ26" s="5"/>
+      <c r="PWL26" s="5"/>
+      <c r="PWN26" s="5"/>
+      <c r="PWP26" s="5"/>
+      <c r="PWR26" s="5"/>
+      <c r="PWT26" s="5"/>
+      <c r="PWV26" s="5"/>
+      <c r="PWX26" s="5"/>
+      <c r="PWZ26" s="5"/>
+      <c r="PXB26" s="5"/>
+      <c r="PXD26" s="5"/>
+      <c r="PXF26" s="5"/>
+      <c r="PXH26" s="5"/>
+      <c r="PXJ26" s="5"/>
+      <c r="PXL26" s="5"/>
+      <c r="PXN26" s="5"/>
+      <c r="PXP26" s="5"/>
+      <c r="PXR26" s="5"/>
+      <c r="PXT26" s="5"/>
+      <c r="PXV26" s="5"/>
+      <c r="PXX26" s="5"/>
+      <c r="PXZ26" s="5"/>
+      <c r="PYB26" s="5"/>
+      <c r="PYD26" s="5"/>
+      <c r="PYF26" s="5"/>
+      <c r="PYH26" s="5"/>
+      <c r="PYJ26" s="5"/>
+      <c r="PYL26" s="5"/>
+      <c r="PYN26" s="5"/>
+      <c r="PYP26" s="5"/>
+      <c r="PYR26" s="5"/>
+      <c r="PYT26" s="5"/>
+      <c r="PYV26" s="5"/>
+      <c r="PYX26" s="5"/>
+      <c r="PYZ26" s="5"/>
+      <c r="PZB26" s="5"/>
+      <c r="PZD26" s="5"/>
+      <c r="PZF26" s="5"/>
+      <c r="PZH26" s="5"/>
+      <c r="PZJ26" s="5"/>
+      <c r="PZL26" s="5"/>
+      <c r="PZN26" s="5"/>
+      <c r="PZP26" s="5"/>
+      <c r="PZR26" s="5"/>
+      <c r="PZT26" s="5"/>
+      <c r="PZV26" s="5"/>
+      <c r="PZX26" s="5"/>
+      <c r="PZZ26" s="5"/>
+      <c r="QAB26" s="5"/>
+      <c r="QAD26" s="5"/>
+      <c r="QAF26" s="5"/>
+      <c r="QAH26" s="5"/>
+      <c r="QAJ26" s="5"/>
+      <c r="QAL26" s="5"/>
+      <c r="QAN26" s="5"/>
+      <c r="QAP26" s="5"/>
+      <c r="QAR26" s="5"/>
+      <c r="QAT26" s="5"/>
+      <c r="QAV26" s="5"/>
+      <c r="QAX26" s="5"/>
+      <c r="QAZ26" s="5"/>
+      <c r="QBB26" s="5"/>
+      <c r="QBD26" s="5"/>
+      <c r="QBF26" s="5"/>
+      <c r="QBH26" s="5"/>
+      <c r="QBJ26" s="5"/>
+      <c r="QBL26" s="5"/>
+      <c r="QBN26" s="5"/>
+      <c r="QBP26" s="5"/>
+      <c r="QBR26" s="5"/>
+      <c r="QBT26" s="5"/>
+      <c r="QBV26" s="5"/>
+      <c r="QBX26" s="5"/>
+      <c r="QBZ26" s="5"/>
+      <c r="QCB26" s="5"/>
+      <c r="QCD26" s="5"/>
+      <c r="QCF26" s="5"/>
+      <c r="QCH26" s="5"/>
+      <c r="QCJ26" s="5"/>
+      <c r="QCL26" s="5"/>
+      <c r="QCN26" s="5"/>
+      <c r="QCP26" s="5"/>
+      <c r="QCR26" s="5"/>
+      <c r="QCT26" s="5"/>
+      <c r="QCV26" s="5"/>
+      <c r="QCX26" s="5"/>
+      <c r="QCZ26" s="5"/>
+      <c r="QDB26" s="5"/>
+      <c r="QDD26" s="5"/>
+      <c r="QDF26" s="5"/>
+      <c r="QDH26" s="5"/>
+      <c r="QDJ26" s="5"/>
+      <c r="QDL26" s="5"/>
+      <c r="QDN26" s="5"/>
+      <c r="QDP26" s="5"/>
+      <c r="QDR26" s="5"/>
+      <c r="QDT26" s="5"/>
+      <c r="QDV26" s="5"/>
+      <c r="QDX26" s="5"/>
+      <c r="QDZ26" s="5"/>
+      <c r="QEB26" s="5"/>
+      <c r="QED26" s="5"/>
+      <c r="QEF26" s="5"/>
+      <c r="QEH26" s="5"/>
+      <c r="QEJ26" s="5"/>
+      <c r="QEL26" s="5"/>
+      <c r="QEN26" s="5"/>
+      <c r="QEP26" s="5"/>
+      <c r="QER26" s="5"/>
+      <c r="QET26" s="5"/>
+      <c r="QEV26" s="5"/>
+      <c r="QEX26" s="5"/>
+      <c r="QEZ26" s="5"/>
+      <c r="QFB26" s="5"/>
+      <c r="QFD26" s="5"/>
+      <c r="QFF26" s="5"/>
+      <c r="QFH26" s="5"/>
+      <c r="QFJ26" s="5"/>
+      <c r="QFL26" s="5"/>
+      <c r="QFN26" s="5"/>
+      <c r="QFP26" s="5"/>
+      <c r="QFR26" s="5"/>
+      <c r="QFT26" s="5"/>
+      <c r="QFV26" s="5"/>
+      <c r="QFX26" s="5"/>
+      <c r="QFZ26" s="5"/>
+      <c r="QGB26" s="5"/>
+      <c r="QGD26" s="5"/>
+      <c r="QGF26" s="5"/>
+      <c r="QGH26" s="5"/>
+      <c r="QGJ26" s="5"/>
+      <c r="QGL26" s="5"/>
+      <c r="QGN26" s="5"/>
+      <c r="QGP26" s="5"/>
+      <c r="QGR26" s="5"/>
+      <c r="QGT26" s="5"/>
+      <c r="QGV26" s="5"/>
+      <c r="QGX26" s="5"/>
+      <c r="QGZ26" s="5"/>
+      <c r="QHB26" s="5"/>
+      <c r="QHD26" s="5"/>
+      <c r="QHF26" s="5"/>
+      <c r="QHH26" s="5"/>
+      <c r="QHJ26" s="5"/>
+      <c r="QHL26" s="5"/>
+      <c r="QHN26" s="5"/>
+      <c r="QHP26" s="5"/>
+      <c r="QHR26" s="5"/>
+      <c r="QHT26" s="5"/>
+      <c r="QHV26" s="5"/>
+      <c r="QHX26" s="5"/>
+      <c r="QHZ26" s="5"/>
+      <c r="QIB26" s="5"/>
+      <c r="QID26" s="5"/>
+      <c r="QIF26" s="5"/>
+      <c r="QIH26" s="5"/>
+      <c r="QIJ26" s="5"/>
+      <c r="QIL26" s="5"/>
+      <c r="QIN26" s="5"/>
+      <c r="QIP26" s="5"/>
+      <c r="QIR26" s="5"/>
+      <c r="QIT26" s="5"/>
+      <c r="QIV26" s="5"/>
+      <c r="QIX26" s="5"/>
+      <c r="QIZ26" s="5"/>
+      <c r="QJB26" s="5"/>
+      <c r="QJD26" s="5"/>
+      <c r="QJF26" s="5"/>
+      <c r="QJH26" s="5"/>
+      <c r="QJJ26" s="5"/>
+      <c r="QJL26" s="5"/>
+      <c r="QJN26" s="5"/>
+      <c r="QJP26" s="5"/>
+      <c r="QJR26" s="5"/>
+      <c r="QJT26" s="5"/>
+      <c r="QJV26" s="5"/>
+      <c r="QJX26" s="5"/>
+      <c r="QJZ26" s="5"/>
+      <c r="QKB26" s="5"/>
+      <c r="QKD26" s="5"/>
+      <c r="QKF26" s="5"/>
+      <c r="QKH26" s="5"/>
+      <c r="QKJ26" s="5"/>
+      <c r="QKL26" s="5"/>
+      <c r="QKN26" s="5"/>
+      <c r="QKP26" s="5"/>
+      <c r="QKR26" s="5"/>
+      <c r="QKT26" s="5"/>
+      <c r="QKV26" s="5"/>
+      <c r="QKX26" s="5"/>
+      <c r="QKZ26" s="5"/>
+      <c r="QLB26" s="5"/>
+      <c r="QLD26" s="5"/>
+      <c r="QLF26" s="5"/>
+      <c r="QLH26" s="5"/>
+      <c r="QLJ26" s="5"/>
+      <c r="QLL26" s="5"/>
+      <c r="QLN26" s="5"/>
+      <c r="QLP26" s="5"/>
+      <c r="QLR26" s="5"/>
+      <c r="QLT26" s="5"/>
+      <c r="QLV26" s="5"/>
+      <c r="QLX26" s="5"/>
+      <c r="QLZ26" s="5"/>
+      <c r="QMB26" s="5"/>
+      <c r="QMD26" s="5"/>
+      <c r="QMF26" s="5"/>
+      <c r="QMH26" s="5"/>
+      <c r="QMJ26" s="5"/>
+      <c r="QML26" s="5"/>
+      <c r="QMN26" s="5"/>
+      <c r="QMP26" s="5"/>
+      <c r="QMR26" s="5"/>
+      <c r="QMT26" s="5"/>
+      <c r="QMV26" s="5"/>
+      <c r="QMX26" s="5"/>
+      <c r="QMZ26" s="5"/>
+      <c r="QNB26" s="5"/>
+      <c r="QND26" s="5"/>
+      <c r="QNF26" s="5"/>
+      <c r="QNH26" s="5"/>
+      <c r="QNJ26" s="5"/>
+      <c r="QNL26" s="5"/>
+      <c r="QNN26" s="5"/>
+      <c r="QNP26" s="5"/>
+      <c r="QNR26" s="5"/>
+      <c r="QNT26" s="5"/>
+      <c r="QNV26" s="5"/>
+      <c r="QNX26" s="5"/>
+      <c r="QNZ26" s="5"/>
+      <c r="QOB26" s="5"/>
+      <c r="QOD26" s="5"/>
+      <c r="QOF26" s="5"/>
+      <c r="QOH26" s="5"/>
+      <c r="QOJ26" s="5"/>
+      <c r="QOL26" s="5"/>
+      <c r="QON26" s="5"/>
+      <c r="QOP26" s="5"/>
+      <c r="QOR26" s="5"/>
+      <c r="QOT26" s="5"/>
+      <c r="QOV26" s="5"/>
+      <c r="QOX26" s="5"/>
+      <c r="QOZ26" s="5"/>
+      <c r="QPB26" s="5"/>
+      <c r="QPD26" s="5"/>
+      <c r="QPF26" s="5"/>
+      <c r="QPH26" s="5"/>
+      <c r="QPJ26" s="5"/>
+      <c r="QPL26" s="5"/>
+      <c r="QPN26" s="5"/>
+      <c r="QPP26" s="5"/>
+      <c r="QPR26" s="5"/>
+      <c r="QPT26" s="5"/>
+      <c r="QPV26" s="5"/>
+      <c r="QPX26" s="5"/>
+      <c r="QPZ26" s="5"/>
+      <c r="QQB26" s="5"/>
+      <c r="QQD26" s="5"/>
+      <c r="QQF26" s="5"/>
+      <c r="QQH26" s="5"/>
+      <c r="QQJ26" s="5"/>
+      <c r="QQL26" s="5"/>
+      <c r="QQN26" s="5"/>
+      <c r="QQP26" s="5"/>
+      <c r="QQR26" s="5"/>
+      <c r="QQT26" s="5"/>
+      <c r="QQV26" s="5"/>
+      <c r="QQX26" s="5"/>
+      <c r="QQZ26" s="5"/>
+      <c r="QRB26" s="5"/>
+      <c r="QRD26" s="5"/>
+      <c r="QRF26" s="5"/>
+      <c r="QRH26" s="5"/>
+      <c r="QRJ26" s="5"/>
+      <c r="QRL26" s="5"/>
+      <c r="QRN26" s="5"/>
+      <c r="QRP26" s="5"/>
+      <c r="QRR26" s="5"/>
+      <c r="QRT26" s="5"/>
+      <c r="QRV26" s="5"/>
+      <c r="QRX26" s="5"/>
+      <c r="QRZ26" s="5"/>
+      <c r="QSB26" s="5"/>
+      <c r="QSD26" s="5"/>
+      <c r="QSF26" s="5"/>
+      <c r="QSH26" s="5"/>
+      <c r="QSJ26" s="5"/>
+      <c r="QSL26" s="5"/>
+      <c r="QSN26" s="5"/>
+      <c r="QSP26" s="5"/>
+      <c r="QSR26" s="5"/>
+      <c r="QST26" s="5"/>
+      <c r="QSV26" s="5"/>
+      <c r="QSX26" s="5"/>
+      <c r="QSZ26" s="5"/>
+      <c r="QTB26" s="5"/>
+      <c r="QTD26" s="5"/>
+      <c r="QTF26" s="5"/>
+      <c r="QTH26" s="5"/>
+      <c r="QTJ26" s="5"/>
+      <c r="QTL26" s="5"/>
+      <c r="QTN26" s="5"/>
+      <c r="QTP26" s="5"/>
+      <c r="QTR26" s="5"/>
+      <c r="QTT26" s="5"/>
+      <c r="QTV26" s="5"/>
+      <c r="QTX26" s="5"/>
+      <c r="QTZ26" s="5"/>
+      <c r="QUB26" s="5"/>
+      <c r="QUD26" s="5"/>
+      <c r="QUF26" s="5"/>
+      <c r="QUH26" s="5"/>
+      <c r="QUJ26" s="5"/>
+      <c r="QUL26" s="5"/>
+      <c r="QUN26" s="5"/>
+      <c r="QUP26" s="5"/>
+      <c r="QUR26" s="5"/>
+      <c r="QUT26" s="5"/>
+      <c r="QUV26" s="5"/>
+      <c r="QUX26" s="5"/>
+      <c r="QUZ26" s="5"/>
+      <c r="QVB26" s="5"/>
+      <c r="QVD26" s="5"/>
+      <c r="QVF26" s="5"/>
+      <c r="QVH26" s="5"/>
+      <c r="QVJ26" s="5"/>
+      <c r="QVL26" s="5"/>
+      <c r="QVN26" s="5"/>
+      <c r="QVP26" s="5"/>
+      <c r="QVR26" s="5"/>
+      <c r="QVT26" s="5"/>
+      <c r="QVV26" s="5"/>
+      <c r="QVX26" s="5"/>
+      <c r="QVZ26" s="5"/>
+      <c r="QWB26" s="5"/>
+      <c r="QWD26" s="5"/>
+      <c r="QWF26" s="5"/>
+      <c r="QWH26" s="5"/>
+      <c r="QWJ26" s="5"/>
+      <c r="QWL26" s="5"/>
+      <c r="QWN26" s="5"/>
+      <c r="QWP26" s="5"/>
+      <c r="QWR26" s="5"/>
+      <c r="QWT26" s="5"/>
+      <c r="QWV26" s="5"/>
+      <c r="QWX26" s="5"/>
+      <c r="QWZ26" s="5"/>
+      <c r="QXB26" s="5"/>
+      <c r="QXD26" s="5"/>
+      <c r="QXF26" s="5"/>
+      <c r="QXH26" s="5"/>
+      <c r="QXJ26" s="5"/>
+      <c r="QXL26" s="5"/>
+      <c r="QXN26" s="5"/>
+      <c r="QXP26" s="5"/>
+      <c r="QXR26" s="5"/>
+      <c r="QXT26" s="5"/>
+      <c r="QXV26" s="5"/>
+      <c r="QXX26" s="5"/>
+      <c r="QXZ26" s="5"/>
+      <c r="QYB26" s="5"/>
+      <c r="QYD26" s="5"/>
+      <c r="QYF26" s="5"/>
+      <c r="QYH26" s="5"/>
+      <c r="QYJ26" s="5"/>
+      <c r="QYL26" s="5"/>
+      <c r="QYN26" s="5"/>
+      <c r="QYP26" s="5"/>
+      <c r="QYR26" s="5"/>
+      <c r="QYT26" s="5"/>
+      <c r="QYV26" s="5"/>
+      <c r="QYX26" s="5"/>
+      <c r="QYZ26" s="5"/>
+      <c r="QZB26" s="5"/>
+      <c r="QZD26" s="5"/>
+      <c r="QZF26" s="5"/>
+      <c r="QZH26" s="5"/>
+      <c r="QZJ26" s="5"/>
+      <c r="QZL26" s="5"/>
+      <c r="QZN26" s="5"/>
+      <c r="QZP26" s="5"/>
+      <c r="QZR26" s="5"/>
+      <c r="QZT26" s="5"/>
+      <c r="QZV26" s="5"/>
+      <c r="QZX26" s="5"/>
+      <c r="QZZ26" s="5"/>
+      <c r="RAB26" s="5"/>
+      <c r="RAD26" s="5"/>
+      <c r="RAF26" s="5"/>
+      <c r="RAH26" s="5"/>
+      <c r="RAJ26" s="5"/>
+      <c r="RAL26" s="5"/>
+      <c r="RAN26" s="5"/>
+      <c r="RAP26" s="5"/>
+      <c r="RAR26" s="5"/>
+      <c r="RAT26" s="5"/>
+      <c r="RAV26" s="5"/>
+      <c r="RAX26" s="5"/>
+      <c r="RAZ26" s="5"/>
+      <c r="RBB26" s="5"/>
+      <c r="RBD26" s="5"/>
+      <c r="RBF26" s="5"/>
+      <c r="RBH26" s="5"/>
+      <c r="RBJ26" s="5"/>
+      <c r="RBL26" s="5"/>
+      <c r="RBN26" s="5"/>
+      <c r="RBP26" s="5"/>
+      <c r="RBR26" s="5"/>
+      <c r="RBT26" s="5"/>
+      <c r="RBV26" s="5"/>
+      <c r="RBX26" s="5"/>
+      <c r="RBZ26" s="5"/>
+      <c r="RCB26" s="5"/>
+      <c r="RCD26" s="5"/>
+      <c r="RCF26" s="5"/>
+      <c r="RCH26" s="5"/>
+      <c r="RCJ26" s="5"/>
+      <c r="RCL26" s="5"/>
+      <c r="RCN26" s="5"/>
+      <c r="RCP26" s="5"/>
+      <c r="RCR26" s="5"/>
+      <c r="RCT26" s="5"/>
+      <c r="RCV26" s="5"/>
+      <c r="RCX26" s="5"/>
+      <c r="RCZ26" s="5"/>
+      <c r="RDB26" s="5"/>
+      <c r="RDD26" s="5"/>
+      <c r="RDF26" s="5"/>
+      <c r="RDH26" s="5"/>
+      <c r="RDJ26" s="5"/>
+      <c r="RDL26" s="5"/>
+      <c r="RDN26" s="5"/>
+      <c r="RDP26" s="5"/>
+      <c r="RDR26" s="5"/>
+      <c r="RDT26" s="5"/>
+      <c r="RDV26" s="5"/>
+      <c r="RDX26" s="5"/>
+      <c r="RDZ26" s="5"/>
+      <c r="REB26" s="5"/>
+      <c r="RED26" s="5"/>
+      <c r="REF26" s="5"/>
+      <c r="REH26" s="5"/>
+      <c r="REJ26" s="5"/>
+      <c r="REL26" s="5"/>
+      <c r="REN26" s="5"/>
+      <c r="REP26" s="5"/>
+      <c r="RER26" s="5"/>
+      <c r="RET26" s="5"/>
+      <c r="REV26" s="5"/>
+      <c r="REX26" s="5"/>
+      <c r="REZ26" s="5"/>
+      <c r="RFB26" s="5"/>
+      <c r="RFD26" s="5"/>
+      <c r="RFF26" s="5"/>
+      <c r="RFH26" s="5"/>
+      <c r="RFJ26" s="5"/>
+      <c r="RFL26" s="5"/>
+      <c r="RFN26" s="5"/>
+      <c r="RFP26" s="5"/>
+      <c r="RFR26" s="5"/>
+      <c r="RFT26" s="5"/>
+      <c r="RFV26" s="5"/>
+      <c r="RFX26" s="5"/>
+      <c r="RFZ26" s="5"/>
+      <c r="RGB26" s="5"/>
+      <c r="RGD26" s="5"/>
+      <c r="RGF26" s="5"/>
+      <c r="RGH26" s="5"/>
+      <c r="RGJ26" s="5"/>
+      <c r="RGL26" s="5"/>
+      <c r="RGN26" s="5"/>
+      <c r="RGP26" s="5"/>
+      <c r="RGR26" s="5"/>
+      <c r="RGT26" s="5"/>
+      <c r="RGV26" s="5"/>
+      <c r="RGX26" s="5"/>
+      <c r="RGZ26" s="5"/>
+      <c r="RHB26" s="5"/>
+      <c r="RHD26" s="5"/>
+      <c r="RHF26" s="5"/>
+      <c r="RHH26" s="5"/>
+      <c r="RHJ26" s="5"/>
+      <c r="RHL26" s="5"/>
+      <c r="RHN26" s="5"/>
+      <c r="RHP26" s="5"/>
+      <c r="RHR26" s="5"/>
+      <c r="RHT26" s="5"/>
+      <c r="RHV26" s="5"/>
+      <c r="RHX26" s="5"/>
+      <c r="RHZ26" s="5"/>
+      <c r="RIB26" s="5"/>
+      <c r="RID26" s="5"/>
+      <c r="RIF26" s="5"/>
+      <c r="RIH26" s="5"/>
+      <c r="RIJ26" s="5"/>
+      <c r="RIL26" s="5"/>
+      <c r="RIN26" s="5"/>
+      <c r="RIP26" s="5"/>
+      <c r="RIR26" s="5"/>
+      <c r="RIT26" s="5"/>
+      <c r="RIV26" s="5"/>
+      <c r="RIX26" s="5"/>
+      <c r="RIZ26" s="5"/>
+      <c r="RJB26" s="5"/>
+      <c r="RJD26" s="5"/>
+      <c r="RJF26" s="5"/>
+      <c r="RJH26" s="5"/>
+      <c r="RJJ26" s="5"/>
+      <c r="RJL26" s="5"/>
+      <c r="RJN26" s="5"/>
+      <c r="RJP26" s="5"/>
+      <c r="RJR26" s="5"/>
+      <c r="RJT26" s="5"/>
+      <c r="RJV26" s="5"/>
+      <c r="RJX26" s="5"/>
+      <c r="RJZ26" s="5"/>
+      <c r="RKB26" s="5"/>
+      <c r="RKD26" s="5"/>
+      <c r="RKF26" s="5"/>
+      <c r="RKH26" s="5"/>
+      <c r="RKJ26" s="5"/>
+      <c r="RKL26" s="5"/>
+      <c r="RKN26" s="5"/>
+      <c r="RKP26" s="5"/>
+      <c r="RKR26" s="5"/>
+      <c r="RKT26" s="5"/>
+      <c r="RKV26" s="5"/>
+      <c r="RKX26" s="5"/>
+      <c r="RKZ26" s="5"/>
+      <c r="RLB26" s="5"/>
+      <c r="RLD26" s="5"/>
+      <c r="RLF26" s="5"/>
+      <c r="RLH26" s="5"/>
+      <c r="RLJ26" s="5"/>
+      <c r="RLL26" s="5"/>
+      <c r="RLN26" s="5"/>
+      <c r="RLP26" s="5"/>
+      <c r="RLR26" s="5"/>
+      <c r="RLT26" s="5"/>
+      <c r="RLV26" s="5"/>
+      <c r="RLX26" s="5"/>
+      <c r="RLZ26" s="5"/>
+      <c r="RMB26" s="5"/>
+      <c r="RMD26" s="5"/>
+      <c r="RMF26" s="5"/>
+      <c r="RMH26" s="5"/>
+      <c r="RMJ26" s="5"/>
+      <c r="RML26" s="5"/>
+      <c r="RMN26" s="5"/>
+      <c r="RMP26" s="5"/>
+      <c r="RMR26" s="5"/>
+      <c r="RMT26" s="5"/>
+      <c r="RMV26" s="5"/>
+      <c r="RMX26" s="5"/>
+      <c r="RMZ26" s="5"/>
+      <c r="RNB26" s="5"/>
+      <c r="RND26" s="5"/>
+      <c r="RNF26" s="5"/>
+      <c r="RNH26" s="5"/>
+      <c r="RNJ26" s="5"/>
+      <c r="RNL26" s="5"/>
+      <c r="RNN26" s="5"/>
+      <c r="RNP26" s="5"/>
+      <c r="RNR26" s="5"/>
+      <c r="RNT26" s="5"/>
+      <c r="RNV26" s="5"/>
+      <c r="RNX26" s="5"/>
+      <c r="RNZ26" s="5"/>
+      <c r="ROB26" s="5"/>
+      <c r="ROD26" s="5"/>
+      <c r="ROF26" s="5"/>
+      <c r="ROH26" s="5"/>
+      <c r="ROJ26" s="5"/>
+      <c r="ROL26" s="5"/>
+      <c r="RON26" s="5"/>
+      <c r="ROP26" s="5"/>
+      <c r="ROR26" s="5"/>
+      <c r="ROT26" s="5"/>
+      <c r="ROV26" s="5"/>
+      <c r="ROX26" s="5"/>
+      <c r="ROZ26" s="5"/>
+      <c r="RPB26" s="5"/>
+      <c r="RPD26" s="5"/>
+      <c r="RPF26" s="5"/>
+      <c r="RPH26" s="5"/>
+      <c r="RPJ26" s="5"/>
+      <c r="RPL26" s="5"/>
+      <c r="RPN26" s="5"/>
+      <c r="RPP26" s="5"/>
+      <c r="RPR26" s="5"/>
+      <c r="RPT26" s="5"/>
+      <c r="RPV26" s="5"/>
+      <c r="RPX26" s="5"/>
+      <c r="RPZ26" s="5"/>
+      <c r="RQB26" s="5"/>
+      <c r="RQD26" s="5"/>
+      <c r="RQF26" s="5"/>
+      <c r="RQH26" s="5"/>
+      <c r="RQJ26" s="5"/>
+      <c r="RQL26" s="5"/>
+      <c r="RQN26" s="5"/>
+      <c r="RQP26" s="5"/>
+      <c r="RQR26" s="5"/>
+      <c r="RQT26" s="5"/>
+      <c r="RQV26" s="5"/>
+      <c r="RQX26" s="5"/>
+      <c r="RQZ26" s="5"/>
+      <c r="RRB26" s="5"/>
+      <c r="RRD26" s="5"/>
+      <c r="RRF26" s="5"/>
+      <c r="RRH26" s="5"/>
+      <c r="RRJ26" s="5"/>
+      <c r="RRL26" s="5"/>
+      <c r="RRN26" s="5"/>
+      <c r="RRP26" s="5"/>
+      <c r="RRR26" s="5"/>
+      <c r="RRT26" s="5"/>
+      <c r="RRV26" s="5"/>
+      <c r="RRX26" s="5"/>
+      <c r="RRZ26" s="5"/>
+      <c r="RSB26" s="5"/>
+      <c r="RSD26" s="5"/>
+      <c r="RSF26" s="5"/>
+      <c r="RSH26" s="5"/>
+      <c r="RSJ26" s="5"/>
+      <c r="RSL26" s="5"/>
+      <c r="RSN26" s="5"/>
+      <c r="RSP26" s="5"/>
+      <c r="RSR26" s="5"/>
+      <c r="RST26" s="5"/>
+      <c r="RSV26" s="5"/>
+      <c r="RSX26" s="5"/>
+      <c r="RSZ26" s="5"/>
+      <c r="RTB26" s="5"/>
+      <c r="RTD26" s="5"/>
+      <c r="RTF26" s="5"/>
+      <c r="RTH26" s="5"/>
+      <c r="RTJ26" s="5"/>
+      <c r="RTL26" s="5"/>
+      <c r="RTN26" s="5"/>
+      <c r="RTP26" s="5"/>
+      <c r="RTR26" s="5"/>
+      <c r="RTT26" s="5"/>
+      <c r="RTV26" s="5"/>
+      <c r="RTX26" s="5"/>
+      <c r="RTZ26" s="5"/>
+      <c r="RUB26" s="5"/>
+      <c r="RUD26" s="5"/>
+      <c r="RUF26" s="5"/>
+      <c r="RUH26" s="5"/>
+      <c r="RUJ26" s="5"/>
+      <c r="RUL26" s="5"/>
+      <c r="RUN26" s="5"/>
+      <c r="RUP26" s="5"/>
+      <c r="RUR26" s="5"/>
+      <c r="RUT26" s="5"/>
+      <c r="RUV26" s="5"/>
+      <c r="RUX26" s="5"/>
+      <c r="RUZ26" s="5"/>
+      <c r="RVB26" s="5"/>
+      <c r="RVD26" s="5"/>
+      <c r="RVF26" s="5"/>
+      <c r="RVH26" s="5"/>
+      <c r="RVJ26" s="5"/>
+      <c r="RVL26" s="5"/>
+      <c r="RVN26" s="5"/>
+      <c r="RVP26" s="5"/>
+      <c r="RVR26" s="5"/>
+      <c r="RVT26" s="5"/>
+      <c r="RVV26" s="5"/>
+      <c r="RVX26" s="5"/>
+      <c r="RVZ26" s="5"/>
+      <c r="RWB26" s="5"/>
+      <c r="RWD26" s="5"/>
+      <c r="RWF26" s="5"/>
+      <c r="RWH26" s="5"/>
+      <c r="RWJ26" s="5"/>
+      <c r="RWL26" s="5"/>
+      <c r="RWN26" s="5"/>
+      <c r="RWP26" s="5"/>
+      <c r="RWR26" s="5"/>
+      <c r="RWT26" s="5"/>
+      <c r="RWV26" s="5"/>
+      <c r="RWX26" s="5"/>
+      <c r="RWZ26" s="5"/>
+      <c r="RXB26" s="5"/>
+      <c r="RXD26" s="5"/>
+      <c r="RXF26" s="5"/>
+      <c r="RXH26" s="5"/>
+      <c r="RXJ26" s="5"/>
+      <c r="RXL26" s="5"/>
+      <c r="RXN26" s="5"/>
+      <c r="RXP26" s="5"/>
+      <c r="RXR26" s="5"/>
+      <c r="RXT26" s="5"/>
+      <c r="RXV26" s="5"/>
+      <c r="RXX26" s="5"/>
+      <c r="RXZ26" s="5"/>
+      <c r="RYB26" s="5"/>
+      <c r="RYD26" s="5"/>
+      <c r="RYF26" s="5"/>
+      <c r="RYH26" s="5"/>
+      <c r="RYJ26" s="5"/>
+      <c r="RYL26" s="5"/>
+      <c r="RYN26" s="5"/>
+      <c r="RYP26" s="5"/>
+      <c r="RYR26" s="5"/>
+      <c r="RYT26" s="5"/>
+      <c r="RYV26" s="5"/>
+      <c r="RYX26" s="5"/>
+      <c r="RYZ26" s="5"/>
+      <c r="RZB26" s="5"/>
+      <c r="RZD26" s="5"/>
+      <c r="RZF26" s="5"/>
+      <c r="RZH26" s="5"/>
+      <c r="RZJ26" s="5"/>
+      <c r="RZL26" s="5"/>
+      <c r="RZN26" s="5"/>
+      <c r="RZP26" s="5"/>
+      <c r="RZR26" s="5"/>
+      <c r="RZT26" s="5"/>
+      <c r="RZV26" s="5"/>
+      <c r="RZX26" s="5"/>
+      <c r="RZZ26" s="5"/>
+      <c r="SAB26" s="5"/>
+      <c r="SAD26" s="5"/>
+      <c r="SAF26" s="5"/>
+      <c r="SAH26" s="5"/>
+      <c r="SAJ26" s="5"/>
+      <c r="SAL26" s="5"/>
+      <c r="SAN26" s="5"/>
+      <c r="SAP26" s="5"/>
+      <c r="SAR26" s="5"/>
+      <c r="SAT26" s="5"/>
+      <c r="SAV26" s="5"/>
+      <c r="SAX26" s="5"/>
+      <c r="SAZ26" s="5"/>
+      <c r="SBB26" s="5"/>
+      <c r="SBD26" s="5"/>
+      <c r="SBF26" s="5"/>
+      <c r="SBH26" s="5"/>
+      <c r="SBJ26" s="5"/>
+      <c r="SBL26" s="5"/>
+      <c r="SBN26" s="5"/>
+      <c r="SBP26" s="5"/>
+      <c r="SBR26" s="5"/>
+      <c r="SBT26" s="5"/>
+      <c r="SBV26" s="5"/>
+      <c r="SBX26" s="5"/>
+      <c r="SBZ26" s="5"/>
+      <c r="SCB26" s="5"/>
+      <c r="SCD26" s="5"/>
+      <c r="SCF26" s="5"/>
+      <c r="SCH26" s="5"/>
+      <c r="SCJ26" s="5"/>
+      <c r="SCL26" s="5"/>
+      <c r="SCN26" s="5"/>
+      <c r="SCP26" s="5"/>
+      <c r="SCR26" s="5"/>
+      <c r="SCT26" s="5"/>
+      <c r="SCV26" s="5"/>
+      <c r="SCX26" s="5"/>
+      <c r="SCZ26" s="5"/>
+      <c r="SDB26" s="5"/>
+      <c r="SDD26" s="5"/>
+      <c r="SDF26" s="5"/>
+      <c r="SDH26" s="5"/>
+      <c r="SDJ26" s="5"/>
+      <c r="SDL26" s="5"/>
+      <c r="SDN26" s="5"/>
+      <c r="SDP26" s="5"/>
+      <c r="SDR26" s="5"/>
+      <c r="SDT26" s="5"/>
+      <c r="SDV26" s="5"/>
+      <c r="SDX26" s="5"/>
+      <c r="SDZ26" s="5"/>
+      <c r="SEB26" s="5"/>
+      <c r="SED26" s="5"/>
+      <c r="SEF26" s="5"/>
+      <c r="SEH26" s="5"/>
+      <c r="SEJ26" s="5"/>
+      <c r="SEL26" s="5"/>
+      <c r="SEN26" s="5"/>
+      <c r="SEP26" s="5"/>
+      <c r="SER26" s="5"/>
+      <c r="SET26" s="5"/>
+      <c r="SEV26" s="5"/>
+      <c r="SEX26" s="5"/>
+      <c r="SEZ26" s="5"/>
+      <c r="SFB26" s="5"/>
+      <c r="SFD26" s="5"/>
+      <c r="SFF26" s="5"/>
+      <c r="SFH26" s="5"/>
+      <c r="SFJ26" s="5"/>
+      <c r="SFL26" s="5"/>
+      <c r="SFN26" s="5"/>
+      <c r="SFP26" s="5"/>
+      <c r="SFR26" s="5"/>
+      <c r="SFT26" s="5"/>
+      <c r="SFV26" s="5"/>
+      <c r="SFX26" s="5"/>
+      <c r="SFZ26" s="5"/>
+      <c r="SGB26" s="5"/>
+      <c r="SGD26" s="5"/>
+      <c r="SGF26" s="5"/>
+      <c r="SGH26" s="5"/>
+      <c r="SGJ26" s="5"/>
+      <c r="SGL26" s="5"/>
+      <c r="SGN26" s="5"/>
+      <c r="SGP26" s="5"/>
+      <c r="SGR26" s="5"/>
+      <c r="SGT26" s="5"/>
+      <c r="SGV26" s="5"/>
+      <c r="SGX26" s="5"/>
+      <c r="SGZ26" s="5"/>
+      <c r="SHB26" s="5"/>
+      <c r="SHD26" s="5"/>
+      <c r="SHF26" s="5"/>
+      <c r="SHH26" s="5"/>
+      <c r="SHJ26" s="5"/>
+      <c r="SHL26" s="5"/>
+      <c r="SHN26" s="5"/>
+      <c r="SHP26" s="5"/>
+      <c r="SHR26" s="5"/>
+      <c r="SHT26" s="5"/>
+      <c r="SHV26" s="5"/>
+      <c r="SHX26" s="5"/>
+      <c r="SHZ26" s="5"/>
+      <c r="SIB26" s="5"/>
+      <c r="SID26" s="5"/>
+      <c r="SIF26" s="5"/>
+      <c r="SIH26" s="5"/>
+      <c r="SIJ26" s="5"/>
+      <c r="SIL26" s="5"/>
+      <c r="SIN26" s="5"/>
+      <c r="SIP26" s="5"/>
+      <c r="SIR26" s="5"/>
+      <c r="SIT26" s="5"/>
+      <c r="SIV26" s="5"/>
+      <c r="SIX26" s="5"/>
+      <c r="SIZ26" s="5"/>
+      <c r="SJB26" s="5"/>
+      <c r="SJD26" s="5"/>
+      <c r="SJF26" s="5"/>
+      <c r="SJH26" s="5"/>
+      <c r="SJJ26" s="5"/>
+      <c r="SJL26" s="5"/>
+      <c r="SJN26" s="5"/>
+      <c r="SJP26" s="5"/>
+      <c r="SJR26" s="5"/>
+      <c r="SJT26" s="5"/>
+      <c r="SJV26" s="5"/>
+      <c r="SJX26" s="5"/>
+      <c r="SJZ26" s="5"/>
+      <c r="SKB26" s="5"/>
+      <c r="SKD26" s="5"/>
+      <c r="SKF26" s="5"/>
+      <c r="SKH26" s="5"/>
+      <c r="SKJ26" s="5"/>
+      <c r="SKL26" s="5"/>
+      <c r="SKN26" s="5"/>
+      <c r="SKP26" s="5"/>
+      <c r="SKR26" s="5"/>
+      <c r="SKT26" s="5"/>
+      <c r="SKV26" s="5"/>
+      <c r="SKX26" s="5"/>
+      <c r="SKZ26" s="5"/>
+      <c r="SLB26" s="5"/>
+      <c r="SLD26" s="5"/>
+      <c r="SLF26" s="5"/>
+      <c r="SLH26" s="5"/>
+      <c r="SLJ26" s="5"/>
+      <c r="SLL26" s="5"/>
+      <c r="SLN26" s="5"/>
+      <c r="SLP26" s="5"/>
+      <c r="SLR26" s="5"/>
+      <c r="SLT26" s="5"/>
+      <c r="SLV26" s="5"/>
+      <c r="SLX26" s="5"/>
+      <c r="SLZ26" s="5"/>
+      <c r="SMB26" s="5"/>
+      <c r="SMD26" s="5"/>
+      <c r="SMF26" s="5"/>
+      <c r="SMH26" s="5"/>
+      <c r="SMJ26" s="5"/>
+      <c r="SML26" s="5"/>
+      <c r="SMN26" s="5"/>
+      <c r="SMP26" s="5"/>
+      <c r="SMR26" s="5"/>
+      <c r="SMT26" s="5"/>
+      <c r="SMV26" s="5"/>
+      <c r="SMX26" s="5"/>
+      <c r="SMZ26" s="5"/>
+      <c r="SNB26" s="5"/>
+      <c r="SND26" s="5"/>
+      <c r="SNF26" s="5"/>
+      <c r="SNH26" s="5"/>
+      <c r="SNJ26" s="5"/>
+      <c r="SNL26" s="5"/>
+      <c r="SNN26" s="5"/>
+      <c r="SNP26" s="5"/>
+      <c r="SNR26" s="5"/>
+      <c r="SNT26" s="5"/>
+      <c r="SNV26" s="5"/>
+      <c r="SNX26" s="5"/>
+      <c r="SNZ26" s="5"/>
+      <c r="SOB26" s="5"/>
+      <c r="SOD26" s="5"/>
+      <c r="SOF26" s="5"/>
+      <c r="SOH26" s="5"/>
+      <c r="SOJ26" s="5"/>
+      <c r="SOL26" s="5"/>
+      <c r="SON26" s="5"/>
+      <c r="SOP26" s="5"/>
+      <c r="SOR26" s="5"/>
+      <c r="SOT26" s="5"/>
+      <c r="SOV26" s="5"/>
+      <c r="SOX26" s="5"/>
+      <c r="SOZ26" s="5"/>
+      <c r="SPB26" s="5"/>
+      <c r="SPD26" s="5"/>
+      <c r="SPF26" s="5"/>
+      <c r="SPH26" s="5"/>
+      <c r="SPJ26" s="5"/>
+      <c r="SPL26" s="5"/>
+      <c r="SPN26" s="5"/>
+      <c r="SPP26" s="5"/>
+      <c r="SPR26" s="5"/>
+      <c r="SPT26" s="5"/>
+      <c r="SPV26" s="5"/>
+      <c r="SPX26" s="5"/>
+      <c r="SPZ26" s="5"/>
+      <c r="SQB26" s="5"/>
+      <c r="SQD26" s="5"/>
+      <c r="SQF26" s="5"/>
+      <c r="SQH26" s="5"/>
+      <c r="SQJ26" s="5"/>
+      <c r="SQL26" s="5"/>
+      <c r="SQN26" s="5"/>
+      <c r="SQP26" s="5"/>
+      <c r="SQR26" s="5"/>
+      <c r="SQT26" s="5"/>
+      <c r="SQV26" s="5"/>
+      <c r="SQX26" s="5"/>
+      <c r="SQZ26" s="5"/>
+      <c r="SRB26" s="5"/>
+      <c r="SRD26" s="5"/>
+      <c r="SRF26" s="5"/>
+      <c r="SRH26" s="5"/>
+      <c r="SRJ26" s="5"/>
+      <c r="SRL26" s="5"/>
+      <c r="SRN26" s="5"/>
+      <c r="SRP26" s="5"/>
+      <c r="SRR26" s="5"/>
+      <c r="SRT26" s="5"/>
+      <c r="SRV26" s="5"/>
+      <c r="SRX26" s="5"/>
+      <c r="SRZ26" s="5"/>
+      <c r="SSB26" s="5"/>
+      <c r="SSD26" s="5"/>
+      <c r="SSF26" s="5"/>
+      <c r="SSH26" s="5"/>
+      <c r="SSJ26" s="5"/>
+      <c r="SSL26" s="5"/>
+      <c r="SSN26" s="5"/>
+      <c r="SSP26" s="5"/>
+      <c r="SSR26" s="5"/>
+      <c r="SST26" s="5"/>
+      <c r="SSV26" s="5"/>
+      <c r="SSX26" s="5"/>
+      <c r="SSZ26" s="5"/>
+      <c r="STB26" s="5"/>
+      <c r="STD26" s="5"/>
+      <c r="STF26" s="5"/>
+      <c r="STH26" s="5"/>
+      <c r="STJ26" s="5"/>
+      <c r="STL26" s="5"/>
+      <c r="STN26" s="5"/>
+      <c r="STP26" s="5"/>
+      <c r="STR26" s="5"/>
+      <c r="STT26" s="5"/>
+      <c r="STV26" s="5"/>
+      <c r="STX26" s="5"/>
+      <c r="STZ26" s="5"/>
+      <c r="SUB26" s="5"/>
+      <c r="SUD26" s="5"/>
+      <c r="SUF26" s="5"/>
+      <c r="SUH26" s="5"/>
+      <c r="SUJ26" s="5"/>
+      <c r="SUL26" s="5"/>
+      <c r="SUN26" s="5"/>
+      <c r="SUP26" s="5"/>
+      <c r="SUR26" s="5"/>
+      <c r="SUT26" s="5"/>
+      <c r="SUV26" s="5"/>
+      <c r="SUX26" s="5"/>
+      <c r="SUZ26" s="5"/>
+      <c r="SVB26" s="5"/>
+      <c r="SVD26" s="5"/>
+      <c r="SVF26" s="5"/>
+      <c r="SVH26" s="5"/>
+      <c r="SVJ26" s="5"/>
+      <c r="SVL26" s="5"/>
+      <c r="SVN26" s="5"/>
+      <c r="SVP26" s="5"/>
+      <c r="SVR26" s="5"/>
+      <c r="SVT26" s="5"/>
+      <c r="SVV26" s="5"/>
+      <c r="SVX26" s="5"/>
+      <c r="SVZ26" s="5"/>
+      <c r="SWB26" s="5"/>
+      <c r="SWD26" s="5"/>
+      <c r="SWF26" s="5"/>
+      <c r="SWH26" s="5"/>
+      <c r="SWJ26" s="5"/>
+      <c r="SWL26" s="5"/>
+      <c r="SWN26" s="5"/>
+      <c r="SWP26" s="5"/>
+      <c r="SWR26" s="5"/>
+      <c r="SWT26" s="5"/>
+      <c r="SWV26" s="5"/>
+      <c r="SWX26" s="5"/>
+      <c r="SWZ26" s="5"/>
+      <c r="SXB26" s="5"/>
+      <c r="SXD26" s="5"/>
+      <c r="SXF26" s="5"/>
+      <c r="SXH26" s="5"/>
+      <c r="SXJ26" s="5"/>
+      <c r="SXL26" s="5"/>
+      <c r="SXN26" s="5"/>
+      <c r="SXP26" s="5"/>
+      <c r="SXR26" s="5"/>
+      <c r="SXT26" s="5"/>
+      <c r="SXV26" s="5"/>
+      <c r="SXX26" s="5"/>
+      <c r="SXZ26" s="5"/>
+      <c r="SYB26" s="5"/>
+      <c r="SYD26" s="5"/>
+      <c r="SYF26" s="5"/>
+      <c r="SYH26" s="5"/>
+      <c r="SYJ26" s="5"/>
+      <c r="SYL26" s="5"/>
+      <c r="SYN26" s="5"/>
+      <c r="SYP26" s="5"/>
+      <c r="SYR26" s="5"/>
+      <c r="SYT26" s="5"/>
+      <c r="SYV26" s="5"/>
+      <c r="SYX26" s="5"/>
+      <c r="SYZ26" s="5"/>
+      <c r="SZB26" s="5"/>
+      <c r="SZD26" s="5"/>
+      <c r="SZF26" s="5"/>
+      <c r="SZH26" s="5"/>
+      <c r="SZJ26" s="5"/>
+      <c r="SZL26" s="5"/>
+      <c r="SZN26" s="5"/>
+      <c r="SZP26" s="5"/>
+      <c r="SZR26" s="5"/>
+      <c r="SZT26" s="5"/>
+      <c r="SZV26" s="5"/>
+      <c r="SZX26" s="5"/>
+      <c r="SZZ26" s="5"/>
+      <c r="TAB26" s="5"/>
+      <c r="TAD26" s="5"/>
+      <c r="TAF26" s="5"/>
+      <c r="TAH26" s="5"/>
+      <c r="TAJ26" s="5"/>
+      <c r="TAL26" s="5"/>
+      <c r="TAN26" s="5"/>
+      <c r="TAP26" s="5"/>
+      <c r="TAR26" s="5"/>
+      <c r="TAT26" s="5"/>
+      <c r="TAV26" s="5"/>
+      <c r="TAX26" s="5"/>
+      <c r="TAZ26" s="5"/>
+      <c r="TBB26" s="5"/>
+      <c r="TBD26" s="5"/>
+      <c r="TBF26" s="5"/>
+      <c r="TBH26" s="5"/>
+      <c r="TBJ26" s="5"/>
+      <c r="TBL26" s="5"/>
+      <c r="TBN26" s="5"/>
+      <c r="TBP26" s="5"/>
+      <c r="TBR26" s="5"/>
+      <c r="TBT26" s="5"/>
+      <c r="TBV26" s="5"/>
+      <c r="TBX26" s="5"/>
+      <c r="TBZ26" s="5"/>
+      <c r="TCB26" s="5"/>
+      <c r="TCD26" s="5"/>
+      <c r="TCF26" s="5"/>
+      <c r="TCH26" s="5"/>
+      <c r="TCJ26" s="5"/>
+      <c r="TCL26" s="5"/>
+      <c r="TCN26" s="5"/>
+      <c r="TCP26" s="5"/>
+      <c r="TCR26" s="5"/>
+      <c r="TCT26" s="5"/>
+      <c r="TCV26" s="5"/>
+      <c r="TCX26" s="5"/>
+      <c r="TCZ26" s="5"/>
+      <c r="TDB26" s="5"/>
+      <c r="TDD26" s="5"/>
+      <c r="TDF26" s="5"/>
+      <c r="TDH26" s="5"/>
+      <c r="TDJ26" s="5"/>
+      <c r="TDL26" s="5"/>
+      <c r="TDN26" s="5"/>
+      <c r="TDP26" s="5"/>
+      <c r="TDR26" s="5"/>
+      <c r="TDT26" s="5"/>
+      <c r="TDV26" s="5"/>
+      <c r="TDX26" s="5"/>
+      <c r="TDZ26" s="5"/>
+      <c r="TEB26" s="5"/>
+      <c r="TED26" s="5"/>
+      <c r="TEF26" s="5"/>
+      <c r="TEH26" s="5"/>
+      <c r="TEJ26" s="5"/>
+      <c r="TEL26" s="5"/>
+      <c r="TEN26" s="5"/>
+      <c r="TEP26" s="5"/>
+      <c r="TER26" s="5"/>
+      <c r="TET26" s="5"/>
+      <c r="TEV26" s="5"/>
+      <c r="TEX26" s="5"/>
+      <c r="TEZ26" s="5"/>
+      <c r="TFB26" s="5"/>
+      <c r="TFD26" s="5"/>
+      <c r="TFF26" s="5"/>
+      <c r="TFH26" s="5"/>
+      <c r="TFJ26" s="5"/>
+      <c r="TFL26" s="5"/>
+      <c r="TFN26" s="5"/>
+      <c r="TFP26" s="5"/>
+      <c r="TFR26" s="5"/>
+      <c r="TFT26" s="5"/>
+      <c r="TFV26" s="5"/>
+      <c r="TFX26" s="5"/>
+      <c r="TFZ26" s="5"/>
+      <c r="TGB26" s="5"/>
+      <c r="TGD26" s="5"/>
+      <c r="TGF26" s="5"/>
+      <c r="TGH26" s="5"/>
+      <c r="TGJ26" s="5"/>
+      <c r="TGL26" s="5"/>
+      <c r="TGN26" s="5"/>
+      <c r="TGP26" s="5"/>
+      <c r="TGR26" s="5"/>
+      <c r="TGT26" s="5"/>
+      <c r="TGV26" s="5"/>
+      <c r="TGX26" s="5"/>
+      <c r="TGZ26" s="5"/>
+      <c r="THB26" s="5"/>
+      <c r="THD26" s="5"/>
+      <c r="THF26" s="5"/>
+      <c r="THH26" s="5"/>
+      <c r="THJ26" s="5"/>
+      <c r="THL26" s="5"/>
+      <c r="THN26" s="5"/>
+      <c r="THP26" s="5"/>
+      <c r="THR26" s="5"/>
+      <c r="THT26" s="5"/>
+      <c r="THV26" s="5"/>
+      <c r="THX26" s="5"/>
+      <c r="THZ26" s="5"/>
+      <c r="TIB26" s="5"/>
+      <c r="TID26" s="5"/>
+      <c r="TIF26" s="5"/>
+      <c r="TIH26" s="5"/>
+      <c r="TIJ26" s="5"/>
+      <c r="TIL26" s="5"/>
+      <c r="TIN26" s="5"/>
+      <c r="TIP26" s="5"/>
+      <c r="TIR26" s="5"/>
+      <c r="TIT26" s="5"/>
+      <c r="TIV26" s="5"/>
+      <c r="TIX26" s="5"/>
+      <c r="TIZ26" s="5"/>
+      <c r="TJB26" s="5"/>
+      <c r="TJD26" s="5"/>
+      <c r="TJF26" s="5"/>
+      <c r="TJH26" s="5"/>
+      <c r="TJJ26" s="5"/>
+      <c r="TJL26" s="5"/>
+      <c r="TJN26" s="5"/>
+      <c r="TJP26" s="5"/>
+      <c r="TJR26" s="5"/>
+      <c r="TJT26" s="5"/>
+      <c r="TJV26" s="5"/>
+      <c r="TJX26" s="5"/>
+      <c r="TJZ26" s="5"/>
+      <c r="TKB26" s="5"/>
+      <c r="TKD26" s="5"/>
+      <c r="TKF26" s="5"/>
+      <c r="TKH26" s="5"/>
+      <c r="TKJ26" s="5"/>
+      <c r="TKL26" s="5"/>
+      <c r="TKN26" s="5"/>
+      <c r="TKP26" s="5"/>
+      <c r="TKR26" s="5"/>
+      <c r="TKT26" s="5"/>
+      <c r="TKV26" s="5"/>
+      <c r="TKX26" s="5"/>
+      <c r="TKZ26" s="5"/>
+      <c r="TLB26" s="5"/>
+      <c r="TLD26" s="5"/>
+      <c r="TLF26" s="5"/>
+      <c r="TLH26" s="5"/>
+      <c r="TLJ26" s="5"/>
+      <c r="TLL26" s="5"/>
+      <c r="TLN26" s="5"/>
+      <c r="TLP26" s="5"/>
+      <c r="TLR26" s="5"/>
+      <c r="TLT26" s="5"/>
+      <c r="TLV26" s="5"/>
+      <c r="TLX26" s="5"/>
+      <c r="TLZ26" s="5"/>
+      <c r="TMB26" s="5"/>
+      <c r="TMD26" s="5"/>
+      <c r="TMF26" s="5"/>
+      <c r="TMH26" s="5"/>
+      <c r="TMJ26" s="5"/>
+      <c r="TML26" s="5"/>
+      <c r="TMN26" s="5"/>
+      <c r="TMP26" s="5"/>
+      <c r="TMR26" s="5"/>
+      <c r="TMT26" s="5"/>
+      <c r="TMV26" s="5"/>
+      <c r="TMX26" s="5"/>
+      <c r="TMZ26" s="5"/>
+      <c r="TNB26" s="5"/>
+      <c r="TND26" s="5"/>
+      <c r="TNF26" s="5"/>
+      <c r="TNH26" s="5"/>
+      <c r="TNJ26" s="5"/>
+      <c r="TNL26" s="5"/>
+      <c r="TNN26" s="5"/>
+      <c r="TNP26" s="5"/>
+      <c r="TNR26" s="5"/>
+      <c r="TNT26" s="5"/>
+      <c r="TNV26" s="5"/>
+      <c r="TNX26" s="5"/>
+      <c r="TNZ26" s="5"/>
+      <c r="TOB26" s="5"/>
+      <c r="TOD26" s="5"/>
+      <c r="TOF26" s="5"/>
+      <c r="TOH26" s="5"/>
+      <c r="TOJ26" s="5"/>
+      <c r="TOL26" s="5"/>
+      <c r="TON26" s="5"/>
+      <c r="TOP26" s="5"/>
+      <c r="TOR26" s="5"/>
+      <c r="TOT26" s="5"/>
+      <c r="TOV26" s="5"/>
+      <c r="TOX26" s="5"/>
+      <c r="TOZ26" s="5"/>
+      <c r="TPB26" s="5"/>
+      <c r="TPD26" s="5"/>
+      <c r="TPF26" s="5"/>
+      <c r="TPH26" s="5"/>
+      <c r="TPJ26" s="5"/>
+      <c r="TPL26" s="5"/>
+      <c r="TPN26" s="5"/>
+      <c r="TPP26" s="5"/>
+      <c r="TPR26" s="5"/>
+      <c r="TPT26" s="5"/>
+      <c r="TPV26" s="5"/>
+      <c r="TPX26" s="5"/>
+      <c r="TPZ26" s="5"/>
+      <c r="TQB26" s="5"/>
+      <c r="TQD26" s="5"/>
+      <c r="TQF26" s="5"/>
+      <c r="TQH26" s="5"/>
+      <c r="TQJ26" s="5"/>
+      <c r="TQL26" s="5"/>
+      <c r="TQN26" s="5"/>
+      <c r="TQP26" s="5"/>
+      <c r="TQR26" s="5"/>
+      <c r="TQT26" s="5"/>
+      <c r="TQV26" s="5"/>
+      <c r="TQX26" s="5"/>
+      <c r="TQZ26" s="5"/>
+      <c r="TRB26" s="5"/>
+      <c r="TRD26" s="5"/>
+      <c r="TRF26" s="5"/>
+      <c r="TRH26" s="5"/>
+      <c r="TRJ26" s="5"/>
+      <c r="TRL26" s="5"/>
+      <c r="TRN26" s="5"/>
+      <c r="TRP26" s="5"/>
+      <c r="TRR26" s="5"/>
+      <c r="TRT26" s="5"/>
+      <c r="TRV26" s="5"/>
+      <c r="TRX26" s="5"/>
+      <c r="TRZ26" s="5"/>
+      <c r="TSB26" s="5"/>
+      <c r="TSD26" s="5"/>
+      <c r="TSF26" s="5"/>
+      <c r="TSH26" s="5"/>
+      <c r="TSJ26" s="5"/>
+      <c r="TSL26" s="5"/>
+      <c r="TSN26" s="5"/>
+      <c r="TSP26" s="5"/>
+      <c r="TSR26" s="5"/>
+      <c r="TST26" s="5"/>
+      <c r="TSV26" s="5"/>
+      <c r="TSX26" s="5"/>
+      <c r="TSZ26" s="5"/>
+      <c r="TTB26" s="5"/>
+      <c r="TTD26" s="5"/>
+      <c r="TTF26" s="5"/>
+      <c r="TTH26" s="5"/>
+      <c r="TTJ26" s="5"/>
+      <c r="TTL26" s="5"/>
+      <c r="TTN26" s="5"/>
+      <c r="TTP26" s="5"/>
+      <c r="TTR26" s="5"/>
+      <c r="TTT26" s="5"/>
+      <c r="TTV26" s="5"/>
+      <c r="TTX26" s="5"/>
+      <c r="TTZ26" s="5"/>
+      <c r="TUB26" s="5"/>
+      <c r="TUD26" s="5"/>
+      <c r="TUF26" s="5"/>
+      <c r="TUH26" s="5"/>
+      <c r="TUJ26" s="5"/>
+      <c r="TUL26" s="5"/>
+      <c r="TUN26" s="5"/>
+      <c r="TUP26" s="5"/>
+      <c r="TUR26" s="5"/>
+      <c r="TUT26" s="5"/>
+      <c r="TUV26" s="5"/>
+      <c r="TUX26" s="5"/>
+      <c r="TUZ26" s="5"/>
+      <c r="TVB26" s="5"/>
+      <c r="TVD26" s="5"/>
+      <c r="TVF26" s="5"/>
+      <c r="TVH26" s="5"/>
+      <c r="TVJ26" s="5"/>
+      <c r="TVL26" s="5"/>
+      <c r="TVN26" s="5"/>
+      <c r="TVP26" s="5"/>
+      <c r="TVR26" s="5"/>
+      <c r="TVT26" s="5"/>
+      <c r="TVV26" s="5"/>
+      <c r="TVX26" s="5"/>
+      <c r="TVZ26" s="5"/>
+      <c r="TWB26" s="5"/>
+      <c r="TWD26" s="5"/>
+      <c r="TWF26" s="5"/>
+      <c r="TWH26" s="5"/>
+      <c r="TWJ26" s="5"/>
+      <c r="TWL26" s="5"/>
+      <c r="TWN26" s="5"/>
+      <c r="TWP26" s="5"/>
+      <c r="TWR26" s="5"/>
+      <c r="TWT26" s="5"/>
+      <c r="TWV26" s="5"/>
+      <c r="TWX26" s="5"/>
+      <c r="TWZ26" s="5"/>
+      <c r="TXB26" s="5"/>
+      <c r="TXD26" s="5"/>
+      <c r="TXF26" s="5"/>
+      <c r="TXH26" s="5"/>
+      <c r="TXJ26" s="5"/>
+      <c r="TXL26" s="5"/>
+      <c r="TXN26" s="5"/>
+      <c r="TXP26" s="5"/>
+      <c r="TXR26" s="5"/>
+      <c r="TXT26" s="5"/>
+      <c r="TXV26" s="5"/>
+      <c r="TXX26" s="5"/>
+      <c r="TXZ26" s="5"/>
+      <c r="TYB26" s="5"/>
+      <c r="TYD26" s="5"/>
+      <c r="TYF26" s="5"/>
+      <c r="TYH26" s="5"/>
+      <c r="TYJ26" s="5"/>
+      <c r="TYL26" s="5"/>
+      <c r="TYN26" s="5"/>
+      <c r="TYP26" s="5"/>
+      <c r="TYR26" s="5"/>
+      <c r="TYT26" s="5"/>
+      <c r="TYV26" s="5"/>
+      <c r="TYX26" s="5"/>
+      <c r="TYZ26" s="5"/>
+      <c r="TZB26" s="5"/>
+      <c r="TZD26" s="5"/>
+      <c r="TZF26" s="5"/>
+      <c r="TZH26" s="5"/>
+      <c r="TZJ26" s="5"/>
+      <c r="TZL26" s="5"/>
+      <c r="TZN26" s="5"/>
+      <c r="TZP26" s="5"/>
+      <c r="TZR26" s="5"/>
+      <c r="TZT26" s="5"/>
+      <c r="TZV26" s="5"/>
+      <c r="TZX26" s="5"/>
+      <c r="TZZ26" s="5"/>
+      <c r="UAB26" s="5"/>
+      <c r="UAD26" s="5"/>
+      <c r="UAF26" s="5"/>
+      <c r="UAH26" s="5"/>
+      <c r="UAJ26" s="5"/>
+      <c r="UAL26" s="5"/>
+      <c r="UAN26" s="5"/>
+      <c r="UAP26" s="5"/>
+      <c r="UAR26" s="5"/>
+      <c r="UAT26" s="5"/>
+      <c r="UAV26" s="5"/>
+      <c r="UAX26" s="5"/>
+      <c r="UAZ26" s="5"/>
+      <c r="UBB26" s="5"/>
+      <c r="UBD26" s="5"/>
+      <c r="UBF26" s="5"/>
+      <c r="UBH26" s="5"/>
+      <c r="UBJ26" s="5"/>
+      <c r="UBL26" s="5"/>
+      <c r="UBN26" s="5"/>
+      <c r="UBP26" s="5"/>
+      <c r="UBR26" s="5"/>
+      <c r="UBT26" s="5"/>
+      <c r="UBV26" s="5"/>
+      <c r="UBX26" s="5"/>
+      <c r="UBZ26" s="5"/>
+      <c r="UCB26" s="5"/>
+      <c r="UCD26" s="5"/>
+      <c r="UCF26" s="5"/>
+      <c r="UCH26" s="5"/>
+      <c r="UCJ26" s="5"/>
+      <c r="UCL26" s="5"/>
+      <c r="UCN26" s="5"/>
+      <c r="UCP26" s="5"/>
+      <c r="UCR26" s="5"/>
+      <c r="UCT26" s="5"/>
+      <c r="UCV26" s="5"/>
+      <c r="UCX26" s="5"/>
+      <c r="UCZ26" s="5"/>
+      <c r="UDB26" s="5"/>
+      <c r="UDD26" s="5"/>
+      <c r="UDF26" s="5"/>
+      <c r="UDH26" s="5"/>
+      <c r="UDJ26" s="5"/>
+      <c r="UDL26" s="5"/>
+      <c r="UDN26" s="5"/>
+      <c r="UDP26" s="5"/>
+      <c r="UDR26" s="5"/>
+      <c r="UDT26" s="5"/>
+      <c r="UDV26" s="5"/>
+      <c r="UDX26" s="5"/>
+      <c r="UDZ26" s="5"/>
+      <c r="UEB26" s="5"/>
+      <c r="UED26" s="5"/>
+      <c r="UEF26" s="5"/>
+      <c r="UEH26" s="5"/>
+      <c r="UEJ26" s="5"/>
+      <c r="UEL26" s="5"/>
+      <c r="UEN26" s="5"/>
+      <c r="UEP26" s="5"/>
+      <c r="UER26" s="5"/>
+      <c r="UET26" s="5"/>
+      <c r="UEV26" s="5"/>
+      <c r="UEX26" s="5"/>
+      <c r="UEZ26" s="5"/>
+      <c r="UFB26" s="5"/>
+      <c r="UFD26" s="5"/>
+      <c r="UFF26" s="5"/>
+      <c r="UFH26" s="5"/>
+      <c r="UFJ26" s="5"/>
+      <c r="UFL26" s="5"/>
+      <c r="UFN26" s="5"/>
+      <c r="UFP26" s="5"/>
+      <c r="UFR26" s="5"/>
+      <c r="UFT26" s="5"/>
+      <c r="UFV26" s="5"/>
+      <c r="UFX26" s="5"/>
+      <c r="UFZ26" s="5"/>
+      <c r="UGB26" s="5"/>
+      <c r="UGD26" s="5"/>
+      <c r="UGF26" s="5"/>
+      <c r="UGH26" s="5"/>
+      <c r="UGJ26" s="5"/>
+      <c r="UGL26" s="5"/>
+      <c r="UGN26" s="5"/>
+      <c r="UGP26" s="5"/>
+      <c r="UGR26" s="5"/>
+      <c r="UGT26" s="5"/>
+      <c r="UGV26" s="5"/>
+      <c r="UGX26" s="5"/>
+      <c r="UGZ26" s="5"/>
+      <c r="UHB26" s="5"/>
+      <c r="UHD26" s="5"/>
+      <c r="UHF26" s="5"/>
+      <c r="UHH26" s="5"/>
+      <c r="UHJ26" s="5"/>
+      <c r="UHL26" s="5"/>
+      <c r="UHN26" s="5"/>
+      <c r="UHP26" s="5"/>
+      <c r="UHR26" s="5"/>
+      <c r="UHT26" s="5"/>
+      <c r="UHV26" s="5"/>
+      <c r="UHX26" s="5"/>
+      <c r="UHZ26" s="5"/>
+      <c r="UIB26" s="5"/>
+      <c r="UID26" s="5"/>
+      <c r="UIF26" s="5"/>
+      <c r="UIH26" s="5"/>
+      <c r="UIJ26" s="5"/>
+      <c r="UIL26" s="5"/>
+      <c r="UIN26" s="5"/>
+      <c r="UIP26" s="5"/>
+      <c r="UIR26" s="5"/>
+      <c r="UIT26" s="5"/>
+      <c r="UIV26" s="5"/>
+      <c r="UIX26" s="5"/>
+      <c r="UIZ26" s="5"/>
+      <c r="UJB26" s="5"/>
+      <c r="UJD26" s="5"/>
+      <c r="UJF26" s="5"/>
+      <c r="UJH26" s="5"/>
+      <c r="UJJ26" s="5"/>
+      <c r="UJL26" s="5"/>
+      <c r="UJN26" s="5"/>
+      <c r="UJP26" s="5"/>
+      <c r="UJR26" s="5"/>
+      <c r="UJT26" s="5"/>
+      <c r="UJV26" s="5"/>
+      <c r="UJX26" s="5"/>
+      <c r="UJZ26" s="5"/>
+      <c r="UKB26" s="5"/>
+      <c r="UKD26" s="5"/>
+      <c r="UKF26" s="5"/>
+      <c r="UKH26" s="5"/>
+      <c r="UKJ26" s="5"/>
+      <c r="UKL26" s="5"/>
+      <c r="UKN26" s="5"/>
+      <c r="UKP26" s="5"/>
+      <c r="UKR26" s="5"/>
+      <c r="UKT26" s="5"/>
+      <c r="UKV26" s="5"/>
+      <c r="UKX26" s="5"/>
+      <c r="UKZ26" s="5"/>
+      <c r="ULB26" s="5"/>
+      <c r="ULD26" s="5"/>
+      <c r="ULF26" s="5"/>
+      <c r="ULH26" s="5"/>
+      <c r="ULJ26" s="5"/>
+      <c r="ULL26" s="5"/>
+      <c r="ULN26" s="5"/>
+      <c r="ULP26" s="5"/>
+      <c r="ULR26" s="5"/>
+      <c r="ULT26" s="5"/>
+      <c r="ULV26" s="5"/>
+      <c r="ULX26" s="5"/>
+      <c r="ULZ26" s="5"/>
+      <c r="UMB26" s="5"/>
+      <c r="UMD26" s="5"/>
+      <c r="UMF26" s="5"/>
+      <c r="UMH26" s="5"/>
+      <c r="UMJ26" s="5"/>
+      <c r="UML26" s="5"/>
+      <c r="UMN26" s="5"/>
+      <c r="UMP26" s="5"/>
+      <c r="UMR26" s="5"/>
+      <c r="UMT26" s="5"/>
+      <c r="UMV26" s="5"/>
+      <c r="UMX26" s="5"/>
+      <c r="UMZ26" s="5"/>
+      <c r="UNB26" s="5"/>
+      <c r="UND26" s="5"/>
+      <c r="UNF26" s="5"/>
+      <c r="UNH26" s="5"/>
+      <c r="UNJ26" s="5"/>
+      <c r="UNL26" s="5"/>
+      <c r="UNN26" s="5"/>
+      <c r="UNP26" s="5"/>
+      <c r="UNR26" s="5"/>
+      <c r="UNT26" s="5"/>
+      <c r="UNV26" s="5"/>
+      <c r="UNX26" s="5"/>
+      <c r="UNZ26" s="5"/>
+      <c r="UOB26" s="5"/>
+      <c r="UOD26" s="5"/>
+      <c r="UOF26" s="5"/>
+      <c r="UOH26" s="5"/>
+      <c r="UOJ26" s="5"/>
+      <c r="UOL26" s="5"/>
+      <c r="UON26" s="5"/>
+      <c r="UOP26" s="5"/>
+      <c r="UOR26" s="5"/>
+      <c r="UOT26" s="5"/>
+      <c r="UOV26" s="5"/>
+      <c r="UOX26" s="5"/>
+      <c r="UOZ26" s="5"/>
+      <c r="UPB26" s="5"/>
+      <c r="UPD26" s="5"/>
+      <c r="UPF26" s="5"/>
+      <c r="UPH26" s="5"/>
+      <c r="UPJ26" s="5"/>
+      <c r="UPL26" s="5"/>
+      <c r="UPN26" s="5"/>
+      <c r="UPP26" s="5"/>
+      <c r="UPR26" s="5"/>
+      <c r="UPT26" s="5"/>
+      <c r="UPV26" s="5"/>
+      <c r="UPX26" s="5"/>
+      <c r="UPZ26" s="5"/>
+      <c r="UQB26" s="5"/>
+      <c r="UQD26" s="5"/>
+      <c r="UQF26" s="5"/>
+      <c r="UQH26" s="5"/>
+      <c r="UQJ26" s="5"/>
+      <c r="UQL26" s="5"/>
+      <c r="UQN26" s="5"/>
+      <c r="UQP26" s="5"/>
+      <c r="UQR26" s="5"/>
+      <c r="UQT26" s="5"/>
+      <c r="UQV26" s="5"/>
+      <c r="UQX26" s="5"/>
+      <c r="UQZ26" s="5"/>
+      <c r="URB26" s="5"/>
+      <c r="URD26" s="5"/>
+      <c r="URF26" s="5"/>
+      <c r="URH26" s="5"/>
+      <c r="URJ26" s="5"/>
+      <c r="URL26" s="5"/>
+      <c r="URN26" s="5"/>
+      <c r="URP26" s="5"/>
+      <c r="URR26" s="5"/>
+      <c r="URT26" s="5"/>
+      <c r="URV26" s="5"/>
+      <c r="URX26" s="5"/>
+      <c r="URZ26" s="5"/>
+      <c r="USB26" s="5"/>
+      <c r="USD26" s="5"/>
+      <c r="USF26" s="5"/>
+      <c r="USH26" s="5"/>
+      <c r="USJ26" s="5"/>
+      <c r="USL26" s="5"/>
+      <c r="USN26" s="5"/>
+      <c r="USP26" s="5"/>
+      <c r="USR26" s="5"/>
+      <c r="UST26" s="5"/>
+      <c r="USV26" s="5"/>
+      <c r="USX26" s="5"/>
+      <c r="USZ26" s="5"/>
+      <c r="UTB26" s="5"/>
+      <c r="UTD26" s="5"/>
+      <c r="UTF26" s="5"/>
+      <c r="UTH26" s="5"/>
+      <c r="UTJ26" s="5"/>
+      <c r="UTL26" s="5"/>
+      <c r="UTN26" s="5"/>
+      <c r="UTP26" s="5"/>
+      <c r="UTR26" s="5"/>
+      <c r="UTT26" s="5"/>
+      <c r="UTV26" s="5"/>
+      <c r="UTX26" s="5"/>
+      <c r="UTZ26" s="5"/>
+      <c r="UUB26" s="5"/>
+      <c r="UUD26" s="5"/>
+      <c r="UUF26" s="5"/>
+      <c r="UUH26" s="5"/>
+      <c r="UUJ26" s="5"/>
+      <c r="UUL26" s="5"/>
+      <c r="UUN26" s="5"/>
+      <c r="UUP26" s="5"/>
+      <c r="UUR26" s="5"/>
+      <c r="UUT26" s="5"/>
+      <c r="UUV26" s="5"/>
+      <c r="UUX26" s="5"/>
+      <c r="UUZ26" s="5"/>
+      <c r="UVB26" s="5"/>
+      <c r="UVD26" s="5"/>
+      <c r="UVF26" s="5"/>
+      <c r="UVH26" s="5"/>
+      <c r="UVJ26" s="5"/>
+      <c r="UVL26" s="5"/>
+      <c r="UVN26" s="5"/>
+      <c r="UVP26" s="5"/>
+      <c r="UVR26" s="5"/>
+      <c r="UVT26" s="5"/>
+      <c r="UVV26" s="5"/>
+      <c r="UVX26" s="5"/>
+      <c r="UVZ26" s="5"/>
+      <c r="UWB26" s="5"/>
+      <c r="UWD26" s="5"/>
+      <c r="UWF26" s="5"/>
+      <c r="UWH26" s="5"/>
+      <c r="UWJ26" s="5"/>
+      <c r="UWL26" s="5"/>
+      <c r="UWN26" s="5"/>
+      <c r="UWP26" s="5"/>
+      <c r="UWR26" s="5"/>
+      <c r="UWT26" s="5"/>
+      <c r="UWV26" s="5"/>
+      <c r="UWX26" s="5"/>
+      <c r="UWZ26" s="5"/>
+      <c r="UXB26" s="5"/>
+      <c r="UXD26" s="5"/>
+      <c r="UXF26" s="5"/>
+      <c r="UXH26" s="5"/>
+      <c r="UXJ26" s="5"/>
+      <c r="UXL26" s="5"/>
+      <c r="UXN26" s="5"/>
+      <c r="UXP26" s="5"/>
+      <c r="UXR26" s="5"/>
+      <c r="UXT26" s="5"/>
+      <c r="UXV26" s="5"/>
+      <c r="UXX26" s="5"/>
+      <c r="UXZ26" s="5"/>
+      <c r="UYB26" s="5"/>
+      <c r="UYD26" s="5"/>
+      <c r="UYF26" s="5"/>
+      <c r="UYH26" s="5"/>
+      <c r="UYJ26" s="5"/>
+      <c r="UYL26" s="5"/>
+      <c r="UYN26" s="5"/>
+      <c r="UYP26" s="5"/>
+      <c r="UYR26" s="5"/>
+      <c r="UYT26" s="5"/>
+      <c r="UYV26" s="5"/>
+      <c r="UYX26" s="5"/>
+      <c r="UYZ26" s="5"/>
+      <c r="UZB26" s="5"/>
+      <c r="UZD26" s="5"/>
+      <c r="UZF26" s="5"/>
+      <c r="UZH26" s="5"/>
+      <c r="UZJ26" s="5"/>
+      <c r="UZL26" s="5"/>
+      <c r="UZN26" s="5"/>
+      <c r="UZP26" s="5"/>
+      <c r="UZR26" s="5"/>
+      <c r="UZT26" s="5"/>
+      <c r="UZV26" s="5"/>
+      <c r="UZX26" s="5"/>
+      <c r="UZZ26" s="5"/>
+      <c r="VAB26" s="5"/>
+      <c r="VAD26" s="5"/>
+      <c r="VAF26" s="5"/>
+      <c r="VAH26" s="5"/>
+      <c r="VAJ26" s="5"/>
+      <c r="VAL26" s="5"/>
+      <c r="VAN26" s="5"/>
+      <c r="VAP26" s="5"/>
+      <c r="VAR26" s="5"/>
+      <c r="VAT26" s="5"/>
+      <c r="VAV26" s="5"/>
+      <c r="VAX26" s="5"/>
+      <c r="VAZ26" s="5"/>
+      <c r="VBB26" s="5"/>
+      <c r="VBD26" s="5"/>
+      <c r="VBF26" s="5"/>
+      <c r="VBH26" s="5"/>
+      <c r="VBJ26" s="5"/>
+      <c r="VBL26" s="5"/>
+      <c r="VBN26" s="5"/>
+      <c r="VBP26" s="5"/>
+      <c r="VBR26" s="5"/>
+      <c r="VBT26" s="5"/>
+      <c r="VBV26" s="5"/>
+      <c r="VBX26" s="5"/>
+      <c r="VBZ26" s="5"/>
+      <c r="VCB26" s="5"/>
+      <c r="VCD26" s="5"/>
+      <c r="VCF26" s="5"/>
+      <c r="VCH26" s="5"/>
+      <c r="VCJ26" s="5"/>
+      <c r="VCL26" s="5"/>
+      <c r="VCN26" s="5"/>
+      <c r="VCP26" s="5"/>
+      <c r="VCR26" s="5"/>
+      <c r="VCT26" s="5"/>
+      <c r="VCV26" s="5"/>
+      <c r="VCX26" s="5"/>
+      <c r="VCZ26" s="5"/>
+      <c r="VDB26" s="5"/>
+      <c r="VDD26" s="5"/>
+      <c r="VDF26" s="5"/>
+      <c r="VDH26" s="5"/>
+      <c r="VDJ26" s="5"/>
+      <c r="VDL26" s="5"/>
+      <c r="VDN26" s="5"/>
+      <c r="VDP26" s="5"/>
+      <c r="VDR26" s="5"/>
+      <c r="VDT26" s="5"/>
+      <c r="VDV26" s="5"/>
+      <c r="VDX26" s="5"/>
+      <c r="VDZ26" s="5"/>
+      <c r="VEB26" s="5"/>
+      <c r="VED26" s="5"/>
+      <c r="VEF26" s="5"/>
+      <c r="VEH26" s="5"/>
+      <c r="VEJ26" s="5"/>
+      <c r="VEL26" s="5"/>
+      <c r="VEN26" s="5"/>
+      <c r="VEP26" s="5"/>
+      <c r="VER26" s="5"/>
+      <c r="VET26" s="5"/>
+      <c r="VEV26" s="5"/>
+      <c r="VEX26" s="5"/>
+      <c r="VEZ26" s="5"/>
+      <c r="VFB26" s="5"/>
+      <c r="VFD26" s="5"/>
+      <c r="VFF26" s="5"/>
+      <c r="VFH26" s="5"/>
+      <c r="VFJ26" s="5"/>
+      <c r="VFL26" s="5"/>
+      <c r="VFN26" s="5"/>
+      <c r="VFP26" s="5"/>
+      <c r="VFR26" s="5"/>
+      <c r="VFT26" s="5"/>
+      <c r="VFV26" s="5"/>
+      <c r="VFX26" s="5"/>
+      <c r="VFZ26" s="5"/>
+      <c r="VGB26" s="5"/>
+      <c r="VGD26" s="5"/>
+      <c r="VGF26" s="5"/>
+      <c r="VGH26" s="5"/>
+      <c r="VGJ26" s="5"/>
+      <c r="VGL26" s="5"/>
+      <c r="VGN26" s="5"/>
+      <c r="VGP26" s="5"/>
+      <c r="VGR26" s="5"/>
+      <c r="VGT26" s="5"/>
+      <c r="VGV26" s="5"/>
+      <c r="VGX26" s="5"/>
+      <c r="VGZ26" s="5"/>
+      <c r="VHB26" s="5"/>
+      <c r="VHD26" s="5"/>
+      <c r="VHF26" s="5"/>
+      <c r="VHH26" s="5"/>
+      <c r="VHJ26" s="5"/>
+      <c r="VHL26" s="5"/>
+      <c r="VHN26" s="5"/>
+      <c r="VHP26" s="5"/>
+      <c r="VHR26" s="5"/>
+      <c r="VHT26" s="5"/>
+      <c r="VHV26" s="5"/>
+      <c r="VHX26" s="5"/>
+      <c r="VHZ26" s="5"/>
+      <c r="VIB26" s="5"/>
+      <c r="VID26" s="5"/>
+      <c r="VIF26" s="5"/>
+      <c r="VIH26" s="5"/>
+      <c r="VIJ26" s="5"/>
+      <c r="VIL26" s="5"/>
+      <c r="VIN26" s="5"/>
+      <c r="VIP26" s="5"/>
+      <c r="VIR26" s="5"/>
+      <c r="VIT26" s="5"/>
+      <c r="VIV26" s="5"/>
+      <c r="VIX26" s="5"/>
+      <c r="VIZ26" s="5"/>
+      <c r="VJB26" s="5"/>
+      <c r="VJD26" s="5"/>
+      <c r="VJF26" s="5"/>
+      <c r="VJH26" s="5"/>
+      <c r="VJJ26" s="5"/>
+      <c r="VJL26" s="5"/>
+      <c r="VJN26" s="5"/>
+      <c r="VJP26" s="5"/>
+      <c r="VJR26" s="5"/>
+      <c r="VJT26" s="5"/>
+      <c r="VJV26" s="5"/>
+      <c r="VJX26" s="5"/>
+      <c r="VJZ26" s="5"/>
+      <c r="VKB26" s="5"/>
+      <c r="VKD26" s="5"/>
+      <c r="VKF26" s="5"/>
+      <c r="VKH26" s="5"/>
+      <c r="VKJ26" s="5"/>
+      <c r="VKL26" s="5"/>
+      <c r="VKN26" s="5"/>
+      <c r="VKP26" s="5"/>
+      <c r="VKR26" s="5"/>
+      <c r="VKT26" s="5"/>
+      <c r="VKV26" s="5"/>
+      <c r="VKX26" s="5"/>
+      <c r="VKZ26" s="5"/>
+      <c r="VLB26" s="5"/>
+      <c r="VLD26" s="5"/>
+      <c r="VLF26" s="5"/>
+      <c r="VLH26" s="5"/>
+      <c r="VLJ26" s="5"/>
+      <c r="VLL26" s="5"/>
+      <c r="VLN26" s="5"/>
+      <c r="VLP26" s="5"/>
+      <c r="VLR26" s="5"/>
+      <c r="VLT26" s="5"/>
+      <c r="VLV26" s="5"/>
+      <c r="VLX26" s="5"/>
+      <c r="VLZ26" s="5"/>
+      <c r="VMB26" s="5"/>
+      <c r="VMD26" s="5"/>
+      <c r="VMF26" s="5"/>
+      <c r="VMH26" s="5"/>
+      <c r="VMJ26" s="5"/>
+      <c r="VML26" s="5"/>
+      <c r="VMN26" s="5"/>
+      <c r="VMP26" s="5"/>
+      <c r="VMR26" s="5"/>
+      <c r="VMT26" s="5"/>
+      <c r="VMV26" s="5"/>
+      <c r="VMX26" s="5"/>
+      <c r="VMZ26" s="5"/>
+      <c r="VNB26" s="5"/>
+      <c r="VND26" s="5"/>
+      <c r="VNF26" s="5"/>
+      <c r="VNH26" s="5"/>
+      <c r="VNJ26" s="5"/>
+      <c r="VNL26" s="5"/>
+      <c r="VNN26" s="5"/>
+      <c r="VNP26" s="5"/>
+      <c r="VNR26" s="5"/>
+      <c r="VNT26" s="5"/>
+      <c r="VNV26" s="5"/>
+      <c r="VNX26" s="5"/>
+      <c r="VNZ26" s="5"/>
+      <c r="VOB26" s="5"/>
+      <c r="VOD26" s="5"/>
+      <c r="VOF26" s="5"/>
+      <c r="VOH26" s="5"/>
+      <c r="VOJ26" s="5"/>
+      <c r="VOL26" s="5"/>
+      <c r="VON26" s="5"/>
+      <c r="VOP26" s="5"/>
+      <c r="VOR26" s="5"/>
+      <c r="VOT26" s="5"/>
+      <c r="VOV26" s="5"/>
+      <c r="VOX26" s="5"/>
+      <c r="VOZ26" s="5"/>
+      <c r="VPB26" s="5"/>
+      <c r="VPD26" s="5"/>
+      <c r="VPF26" s="5"/>
+      <c r="VPH26" s="5"/>
+      <c r="VPJ26" s="5"/>
+      <c r="VPL26" s="5"/>
+      <c r="VPN26" s="5"/>
+      <c r="VPP26" s="5"/>
+      <c r="VPR26" s="5"/>
+      <c r="VPT26" s="5"/>
+      <c r="VPV26" s="5"/>
+      <c r="VPX26" s="5"/>
+      <c r="VPZ26" s="5"/>
+      <c r="VQB26" s="5"/>
+      <c r="VQD26" s="5"/>
+      <c r="VQF26" s="5"/>
+      <c r="VQH26" s="5"/>
+      <c r="VQJ26" s="5"/>
+      <c r="VQL26" s="5"/>
+      <c r="VQN26" s="5"/>
+      <c r="VQP26" s="5"/>
+      <c r="VQR26" s="5"/>
+      <c r="VQT26" s="5"/>
+      <c r="VQV26" s="5"/>
+      <c r="VQX26" s="5"/>
+      <c r="VQZ26" s="5"/>
+      <c r="VRB26" s="5"/>
+      <c r="VRD26" s="5"/>
+      <c r="VRF26" s="5"/>
+      <c r="VRH26" s="5"/>
+      <c r="VRJ26" s="5"/>
+      <c r="VRL26" s="5"/>
+      <c r="VRN26" s="5"/>
+      <c r="VRP26" s="5"/>
+      <c r="VRR26" s="5"/>
+      <c r="VRT26" s="5"/>
+      <c r="VRV26" s="5"/>
+      <c r="VRX26" s="5"/>
+      <c r="VRZ26" s="5"/>
+      <c r="VSB26" s="5"/>
+      <c r="VSD26" s="5"/>
+      <c r="VSF26" s="5"/>
+      <c r="VSH26" s="5"/>
+      <c r="VSJ26" s="5"/>
+      <c r="VSL26" s="5"/>
+      <c r="VSN26" s="5"/>
+      <c r="VSP26" s="5"/>
+      <c r="VSR26" s="5"/>
+      <c r="VST26" s="5"/>
+      <c r="VSV26" s="5"/>
+      <c r="VSX26" s="5"/>
+      <c r="VSZ26" s="5"/>
+      <c r="VTB26" s="5"/>
+      <c r="VTD26" s="5"/>
+      <c r="VTF26" s="5"/>
+      <c r="VTH26" s="5"/>
+      <c r="VTJ26" s="5"/>
+      <c r="VTL26" s="5"/>
+      <c r="VTN26" s="5"/>
+      <c r="VTP26" s="5"/>
+      <c r="VTR26" s="5"/>
+      <c r="VTT26" s="5"/>
+      <c r="VTV26" s="5"/>
+      <c r="VTX26" s="5"/>
+      <c r="VTZ26" s="5"/>
+      <c r="VUB26" s="5"/>
+      <c r="VUD26" s="5"/>
+      <c r="VUF26" s="5"/>
+      <c r="VUH26" s="5"/>
+      <c r="VUJ26" s="5"/>
+      <c r="VUL26" s="5"/>
+      <c r="VUN26" s="5"/>
+      <c r="VUP26" s="5"/>
+      <c r="VUR26" s="5"/>
+      <c r="VUT26" s="5"/>
+      <c r="VUV26" s="5"/>
+      <c r="VUX26" s="5"/>
+      <c r="VUZ26" s="5"/>
+      <c r="VVB26" s="5"/>
+      <c r="VVD26" s="5"/>
+      <c r="VVF26" s="5"/>
+      <c r="VVH26" s="5"/>
+      <c r="VVJ26" s="5"/>
+      <c r="VVL26" s="5"/>
+      <c r="VVN26" s="5"/>
+      <c r="VVP26" s="5"/>
+      <c r="VVR26" s="5"/>
+      <c r="VVT26" s="5"/>
+      <c r="VVV26" s="5"/>
+      <c r="VVX26" s="5"/>
+      <c r="VVZ26" s="5"/>
+      <c r="VWB26" s="5"/>
+      <c r="VWD26" s="5"/>
+      <c r="VWF26" s="5"/>
+      <c r="VWH26" s="5"/>
+      <c r="VWJ26" s="5"/>
+      <c r="VWL26" s="5"/>
+      <c r="VWN26" s="5"/>
+      <c r="VWP26" s="5"/>
+      <c r="VWR26" s="5"/>
+      <c r="VWT26" s="5"/>
+      <c r="VWV26" s="5"/>
+      <c r="VWX26" s="5"/>
+      <c r="VWZ26" s="5"/>
+      <c r="VXB26" s="5"/>
+      <c r="VXD26" s="5"/>
+      <c r="VXF26" s="5"/>
+      <c r="VXH26" s="5"/>
+      <c r="VXJ26" s="5"/>
+      <c r="VXL26" s="5"/>
+      <c r="VXN26" s="5"/>
+      <c r="VXP26" s="5"/>
+      <c r="VXR26" s="5"/>
+      <c r="VXT26" s="5"/>
+      <c r="VXV26" s="5"/>
+      <c r="VXX26" s="5"/>
+      <c r="VXZ26" s="5"/>
+      <c r="VYB26" s="5"/>
+      <c r="VYD26" s="5"/>
+      <c r="VYF26" s="5"/>
+      <c r="VYH26" s="5"/>
+      <c r="VYJ26" s="5"/>
+      <c r="VYL26" s="5"/>
+      <c r="VYN26" s="5"/>
+      <c r="VYP26" s="5"/>
+      <c r="VYR26" s="5"/>
+      <c r="VYT26" s="5"/>
+      <c r="VYV26" s="5"/>
+      <c r="VYX26" s="5"/>
+      <c r="VYZ26" s="5"/>
+      <c r="VZB26" s="5"/>
+      <c r="VZD26" s="5"/>
+      <c r="VZF26" s="5"/>
+      <c r="VZH26" s="5"/>
+      <c r="VZJ26" s="5"/>
+      <c r="VZL26" s="5"/>
+      <c r="VZN26" s="5"/>
+      <c r="VZP26" s="5"/>
+      <c r="VZR26" s="5"/>
+      <c r="VZT26" s="5"/>
+      <c r="VZV26" s="5"/>
+      <c r="VZX26" s="5"/>
+      <c r="VZZ26" s="5"/>
+      <c r="WAB26" s="5"/>
+      <c r="WAD26" s="5"/>
+      <c r="WAF26" s="5"/>
+      <c r="WAH26" s="5"/>
+      <c r="WAJ26" s="5"/>
+      <c r="WAL26" s="5"/>
+      <c r="WAN26" s="5"/>
+      <c r="WAP26" s="5"/>
+      <c r="WAR26" s="5"/>
+      <c r="WAT26" s="5"/>
+      <c r="WAV26" s="5"/>
+      <c r="WAX26" s="5"/>
+      <c r="WAZ26" s="5"/>
+      <c r="WBB26" s="5"/>
+      <c r="WBD26" s="5"/>
+      <c r="WBF26" s="5"/>
+      <c r="WBH26" s="5"/>
+      <c r="WBJ26" s="5"/>
+      <c r="WBL26" s="5"/>
+      <c r="WBN26" s="5"/>
+      <c r="WBP26" s="5"/>
+      <c r="WBR26" s="5"/>
+      <c r="WBT26" s="5"/>
+      <c r="WBV26" s="5"/>
+      <c r="WBX26" s="5"/>
+      <c r="WBZ26" s="5"/>
+      <c r="WCB26" s="5"/>
+      <c r="WCD26" s="5"/>
+      <c r="WCF26" s="5"/>
+      <c r="WCH26" s="5"/>
+      <c r="WCJ26" s="5"/>
+      <c r="WCL26" s="5"/>
+      <c r="WCN26" s="5"/>
+      <c r="WCP26" s="5"/>
+      <c r="WCR26" s="5"/>
+      <c r="WCT26" s="5"/>
+      <c r="WCV26" s="5"/>
+      <c r="WCX26" s="5"/>
+      <c r="WCZ26" s="5"/>
+      <c r="WDB26" s="5"/>
+      <c r="WDD26" s="5"/>
+      <c r="WDF26" s="5"/>
+      <c r="WDH26" s="5"/>
+      <c r="WDJ26" s="5"/>
+      <c r="WDL26" s="5"/>
+      <c r="WDN26" s="5"/>
+      <c r="WDP26" s="5"/>
+      <c r="WDR26" s="5"/>
+      <c r="WDT26" s="5"/>
+      <c r="WDV26" s="5"/>
+      <c r="WDX26" s="5"/>
+      <c r="WDZ26" s="5"/>
+      <c r="WEB26" s="5"/>
+      <c r="WED26" s="5"/>
+      <c r="WEF26" s="5"/>
+      <c r="WEH26" s="5"/>
+      <c r="WEJ26" s="5"/>
+      <c r="WEL26" s="5"/>
+      <c r="WEN26" s="5"/>
+      <c r="WEP26" s="5"/>
+      <c r="WER26" s="5"/>
+      <c r="WET26" s="5"/>
+      <c r="WEV26" s="5"/>
+      <c r="WEX26" s="5"/>
+      <c r="WEZ26" s="5"/>
+      <c r="WFB26" s="5"/>
+      <c r="WFD26" s="5"/>
+      <c r="WFF26" s="5"/>
+      <c r="WFH26" s="5"/>
+      <c r="WFJ26" s="5"/>
+      <c r="WFL26" s="5"/>
+      <c r="WFN26" s="5"/>
+      <c r="WFP26" s="5"/>
+      <c r="WFR26" s="5"/>
+      <c r="WFT26" s="5"/>
+      <c r="WFV26" s="5"/>
+      <c r="WFX26" s="5"/>
+      <c r="WFZ26" s="5"/>
+      <c r="WGB26" s="5"/>
+      <c r="WGD26" s="5"/>
+      <c r="WGF26" s="5"/>
+      <c r="WGH26" s="5"/>
+      <c r="WGJ26" s="5"/>
+      <c r="WGL26" s="5"/>
+      <c r="WGN26" s="5"/>
+      <c r="WGP26" s="5"/>
+      <c r="WGR26" s="5"/>
+      <c r="WGT26" s="5"/>
+      <c r="WGV26" s="5"/>
+      <c r="WGX26" s="5"/>
+      <c r="WGZ26" s="5"/>
+      <c r="WHB26" s="5"/>
+      <c r="WHD26" s="5"/>
+      <c r="WHF26" s="5"/>
+      <c r="WHH26" s="5"/>
+      <c r="WHJ26" s="5"/>
+      <c r="WHL26" s="5"/>
+      <c r="WHN26" s="5"/>
+      <c r="WHP26" s="5"/>
+      <c r="WHR26" s="5"/>
+      <c r="WHT26" s="5"/>
+      <c r="WHV26" s="5"/>
+      <c r="WHX26" s="5"/>
+      <c r="WHZ26" s="5"/>
+      <c r="WIB26" s="5"/>
+      <c r="WID26" s="5"/>
+      <c r="WIF26" s="5"/>
+      <c r="WIH26" s="5"/>
+      <c r="WIJ26" s="5"/>
+      <c r="WIL26" s="5"/>
+      <c r="WIN26" s="5"/>
+      <c r="WIP26" s="5"/>
+      <c r="WIR26" s="5"/>
+      <c r="WIT26" s="5"/>
+      <c r="WIV26" s="5"/>
+      <c r="WIX26" s="5"/>
+      <c r="WIZ26" s="5"/>
+      <c r="WJB26" s="5"/>
+      <c r="WJD26" s="5"/>
+      <c r="WJF26" s="5"/>
+      <c r="WJH26" s="5"/>
+      <c r="WJJ26" s="5"/>
+      <c r="WJL26" s="5"/>
+      <c r="WJN26" s="5"/>
+      <c r="WJP26" s="5"/>
+      <c r="WJR26" s="5"/>
+      <c r="WJT26" s="5"/>
+      <c r="WJV26" s="5"/>
+      <c r="WJX26" s="5"/>
+      <c r="WJZ26" s="5"/>
+      <c r="WKB26" s="5"/>
+      <c r="WKD26" s="5"/>
+      <c r="WKF26" s="5"/>
+      <c r="WKH26" s="5"/>
+      <c r="WKJ26" s="5"/>
+      <c r="WKL26" s="5"/>
+      <c r="WKN26" s="5"/>
+      <c r="WKP26" s="5"/>
+      <c r="WKR26" s="5"/>
+      <c r="WKT26" s="5"/>
+      <c r="WKV26" s="5"/>
+      <c r="WKX26" s="5"/>
+      <c r="WKZ26" s="5"/>
+      <c r="WLB26" s="5"/>
+      <c r="WLD26" s="5"/>
+      <c r="WLF26" s="5"/>
+      <c r="WLH26" s="5"/>
+      <c r="WLJ26" s="5"/>
+      <c r="WLL26" s="5"/>
+      <c r="WLN26" s="5"/>
+      <c r="WLP26" s="5"/>
+      <c r="WLR26" s="5"/>
+      <c r="WLT26" s="5"/>
+      <c r="WLV26" s="5"/>
+      <c r="WLX26" s="5"/>
+      <c r="WLZ26" s="5"/>
+      <c r="WMB26" s="5"/>
+      <c r="WMD26" s="5"/>
+      <c r="WMF26" s="5"/>
+      <c r="WMH26" s="5"/>
+      <c r="WMJ26" s="5"/>
+      <c r="WML26" s="5"/>
+      <c r="WMN26" s="5"/>
+      <c r="WMP26" s="5"/>
+      <c r="WMR26" s="5"/>
+      <c r="WMT26" s="5"/>
+      <c r="WMV26" s="5"/>
+      <c r="WMX26" s="5"/>
+      <c r="WMZ26" s="5"/>
+      <c r="WNB26" s="5"/>
+      <c r="WND26" s="5"/>
+      <c r="WNF26" s="5"/>
+      <c r="WNH26" s="5"/>
+      <c r="WNJ26" s="5"/>
+      <c r="WNL26" s="5"/>
+      <c r="WNN26" s="5"/>
+      <c r="WNP26" s="5"/>
+      <c r="WNR26" s="5"/>
+      <c r="WNT26" s="5"/>
+      <c r="WNV26" s="5"/>
+      <c r="WNX26" s="5"/>
+      <c r="WNZ26" s="5"/>
+      <c r="WOB26" s="5"/>
+      <c r="WOD26" s="5"/>
+      <c r="WOF26" s="5"/>
+      <c r="WOH26" s="5"/>
+      <c r="WOJ26" s="5"/>
+      <c r="WOL26" s="5"/>
+      <c r="WON26" s="5"/>
+      <c r="WOP26" s="5"/>
+      <c r="WOR26" s="5"/>
+      <c r="WOT26" s="5"/>
+      <c r="WOV26" s="5"/>
+      <c r="WOX26" s="5"/>
+      <c r="WOZ26" s="5"/>
+      <c r="WPB26" s="5"/>
+      <c r="WPD26" s="5"/>
+      <c r="WPF26" s="5"/>
+      <c r="WPH26" s="5"/>
+      <c r="WPJ26" s="5"/>
+      <c r="WPL26" s="5"/>
+      <c r="WPN26" s="5"/>
+      <c r="WPP26" s="5"/>
+      <c r="WPR26" s="5"/>
+      <c r="WPT26" s="5"/>
+      <c r="WPV26" s="5"/>
+      <c r="WPX26" s="5"/>
+      <c r="WPZ26" s="5"/>
+      <c r="WQB26" s="5"/>
+      <c r="WQD26" s="5"/>
+      <c r="WQF26" s="5"/>
+      <c r="WQH26" s="5"/>
+      <c r="WQJ26" s="5"/>
+      <c r="WQL26" s="5"/>
+      <c r="WQN26" s="5"/>
+      <c r="WQP26" s="5"/>
+      <c r="WQR26" s="5"/>
+      <c r="WQT26" s="5"/>
+      <c r="WQV26" s="5"/>
+      <c r="WQX26" s="5"/>
+      <c r="WQZ26" s="5"/>
+      <c r="WRB26" s="5"/>
+      <c r="WRD26" s="5"/>
+      <c r="WRF26" s="5"/>
+      <c r="WRH26" s="5"/>
+      <c r="WRJ26" s="5"/>
+      <c r="WRL26" s="5"/>
+      <c r="WRN26" s="5"/>
+      <c r="WRP26" s="5"/>
+      <c r="WRR26" s="5"/>
+      <c r="WRT26" s="5"/>
+      <c r="WRV26" s="5"/>
+      <c r="WRX26" s="5"/>
+      <c r="WRZ26" s="5"/>
+      <c r="WSB26" s="5"/>
+      <c r="WSD26" s="5"/>
+      <c r="WSF26" s="5"/>
+      <c r="WSH26" s="5"/>
+      <c r="WSJ26" s="5"/>
+      <c r="WSL26" s="5"/>
+      <c r="WSN26" s="5"/>
+      <c r="WSP26" s="5"/>
+      <c r="WSR26" s="5"/>
+      <c r="WST26" s="5"/>
+      <c r="WSV26" s="5"/>
+      <c r="WSX26" s="5"/>
+      <c r="WSZ26" s="5"/>
+      <c r="WTB26" s="5"/>
+      <c r="WTD26" s="5"/>
+      <c r="WTF26" s="5"/>
+      <c r="WTH26" s="5"/>
+      <c r="WTJ26" s="5"/>
+      <c r="WTL26" s="5"/>
+      <c r="WTN26" s="5"/>
+      <c r="WTP26" s="5"/>
+      <c r="WTR26" s="5"/>
+      <c r="WTT26" s="5"/>
+      <c r="WTV26" s="5"/>
+      <c r="WTX26" s="5"/>
+      <c r="WTZ26" s="5"/>
+      <c r="WUB26" s="5"/>
+      <c r="WUD26" s="5"/>
+      <c r="WUF26" s="5"/>
+      <c r="WUH26" s="5"/>
+      <c r="WUJ26" s="5"/>
+      <c r="WUL26" s="5"/>
+      <c r="WUN26" s="5"/>
+      <c r="WUP26" s="5"/>
+      <c r="WUR26" s="5"/>
+      <c r="WUT26" s="5"/>
+      <c r="WUV26" s="5"/>
+      <c r="WUX26" s="5"/>
+      <c r="WUZ26" s="5"/>
+      <c r="WVB26" s="5"/>
+      <c r="WVD26" s="5"/>
+      <c r="WVF26" s="5"/>
+      <c r="WVH26" s="5"/>
+      <c r="WVJ26" s="5"/>
+      <c r="WVL26" s="5"/>
+      <c r="WVN26" s="5"/>
+      <c r="WVP26" s="5"/>
+      <c r="WVR26" s="5"/>
+      <c r="WVT26" s="5"/>
+      <c r="WVV26" s="5"/>
+      <c r="WVX26" s="5"/>
+      <c r="WVZ26" s="5"/>
+      <c r="WWB26" s="5"/>
+      <c r="WWD26" s="5"/>
+      <c r="WWF26" s="5"/>
+      <c r="WWH26" s="5"/>
+      <c r="WWJ26" s="5"/>
+      <c r="WWL26" s="5"/>
+      <c r="WWN26" s="5"/>
+      <c r="WWP26" s="5"/>
+      <c r="WWR26" s="5"/>
+      <c r="WWT26" s="5"/>
+      <c r="WWV26" s="5"/>
+      <c r="WWX26" s="5"/>
+      <c r="WWZ26" s="5"/>
+      <c r="WXB26" s="5"/>
+      <c r="WXD26" s="5"/>
+      <c r="WXF26" s="5"/>
+      <c r="WXH26" s="5"/>
+      <c r="WXJ26" s="5"/>
+      <c r="WXL26" s="5"/>
+      <c r="WXN26" s="5"/>
+      <c r="WXP26" s="5"/>
+      <c r="WXR26" s="5"/>
+      <c r="WXT26" s="5"/>
+      <c r="WXV26" s="5"/>
+      <c r="WXX26" s="5"/>
+      <c r="WXZ26" s="5"/>
+      <c r="WYB26" s="5"/>
+      <c r="WYD26" s="5"/>
+      <c r="WYF26" s="5"/>
+      <c r="WYH26" s="5"/>
+      <c r="WYJ26" s="5"/>
+      <c r="WYL26" s="5"/>
+      <c r="WYN26" s="5"/>
+      <c r="WYP26" s="5"/>
+      <c r="WYR26" s="5"/>
+      <c r="WYT26" s="5"/>
+      <c r="WYV26" s="5"/>
+      <c r="WYX26" s="5"/>
+      <c r="WYZ26" s="5"/>
+      <c r="WZB26" s="5"/>
+      <c r="WZD26" s="5"/>
+      <c r="WZF26" s="5"/>
+      <c r="WZH26" s="5"/>
+      <c r="WZJ26" s="5"/>
+      <c r="WZL26" s="5"/>
+      <c r="WZN26" s="5"/>
+      <c r="WZP26" s="5"/>
+      <c r="WZR26" s="5"/>
+      <c r="WZT26" s="5"/>
+      <c r="WZV26" s="5"/>
+      <c r="WZX26" s="5"/>
+      <c r="WZZ26" s="5"/>
+      <c r="XAB26" s="5"/>
+      <c r="XAD26" s="5"/>
+      <c r="XAF26" s="5"/>
+      <c r="XAH26" s="5"/>
+      <c r="XAJ26" s="5"/>
+      <c r="XAL26" s="5"/>
+      <c r="XAN26" s="5"/>
+      <c r="XAP26" s="5"/>
+      <c r="XAR26" s="5"/>
+      <c r="XAT26" s="5"/>
+      <c r="XAV26" s="5"/>
+      <c r="XAX26" s="5"/>
+      <c r="XAZ26" s="5"/>
+      <c r="XBB26" s="5"/>
+      <c r="XBD26" s="5"/>
+      <c r="XBF26" s="5"/>
+      <c r="XBH26" s="5"/>
+      <c r="XBJ26" s="5"/>
+      <c r="XBL26" s="5"/>
+      <c r="XBN26" s="5"/>
+      <c r="XBP26" s="5"/>
+      <c r="XBR26" s="5"/>
+      <c r="XBT26" s="5"/>
+      <c r="XBV26" s="5"/>
+      <c r="XBX26" s="5"/>
+      <c r="XBZ26" s="5"/>
+      <c r="XCB26" s="5"/>
+      <c r="XCD26" s="5"/>
+      <c r="XCF26" s="5"/>
+      <c r="XCH26" s="5"/>
+      <c r="XCJ26" s="5"/>
+      <c r="XCL26" s="5"/>
+      <c r="XCN26" s="5"/>
+      <c r="XCP26" s="5"/>
+      <c r="XCR26" s="5"/>
+      <c r="XCT26" s="5"/>
+      <c r="XCV26" s="5"/>
+      <c r="XCX26" s="5"/>
+      <c r="XCZ26" s="5"/>
+      <c r="XDB26" s="5"/>
+      <c r="XDD26" s="5"/>
+      <c r="XDF26" s="5"/>
+      <c r="XDH26" s="5"/>
+      <c r="XDJ26" s="5"/>
+      <c r="XDL26" s="5"/>
+      <c r="XDN26" s="5"/>
+      <c r="XDP26" s="5"/>
+      <c r="XDR26" s="5"/>
+      <c r="XDT26" s="5"/>
+      <c r="XDV26" s="5"/>
+      <c r="XDX26" s="5"/>
+      <c r="XDZ26" s="5"/>
+      <c r="XEB26" s="5"/>
+      <c r="XED26" s="5"/>
+      <c r="XEF26" s="5"/>
+      <c r="XEH26" s="5"/>
+      <c r="XEJ26" s="5"/>
+      <c r="XEL26" s="5"/>
+      <c r="XEN26" s="5"/>
+      <c r="XEP26" s="5"/>
+      <c r="XER26" s="5"/>
+      <c r="XET26" s="5"/>
+      <c r="XEV26" s="5"/>
+      <c r="XEX26" s="5"/>
+      <c r="XEZ26" s="5"/>
+      <c r="XFB26" s="5"/>
+    </row>
+    <row r="27" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D22" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF65E74F-A0C0-46E8-9416-D748BF035C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B22310F-B288-443A-B5D5-710A7F845B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>Season</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>`Prior_Season_Grand_Prix_Wins_Last5GP` ÷ 5</t>
+  </si>
+  <si>
+    <t>The total number of Formula 1 races started by the two drivers contracted to the team at the start of the season, regardless of any mid-season driver changes.</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience</t>
   </si>
 </sst>
 </file>
@@ -1251,12 +1257,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:XFB27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:XFB28"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" customWidth="1"/>
+    <col min="3" max="3" width="255.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1494,7 +1500,7 @@
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1516,7 +1522,7 @@
       <c r="B25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9732,6 +9738,17 @@
         <v>42</v>
       </c>
     </row>
+    <row r="28" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A28" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B22310F-B288-443A-B5D5-710A7F845B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26218E12-5353-46EF-9951-3A3CD79047C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28800" yWindow="-11370" windowWidth="16410" windowHeight="11295" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
   <si>
     <t>Season</t>
   </si>
@@ -308,6 +308,24 @@
   </si>
   <si>
     <t>Driver_Lineup_Experience</t>
+  </si>
+  <si>
+    <t>Prior_Season_Quali_Avg</t>
+  </si>
+  <si>
+    <t>Average qualifying position of both team cars across all Grands Prix in the prior season.</t>
+  </si>
+  <si>
+    <t>Total number of fastest laps recorded by the team’s drivers across all Grands Prix in the prior season.</t>
+  </si>
+  <si>
+    <t>Prior_Season_Fastest_Lap_Count</t>
+  </si>
+  <si>
+    <t>Prior_Season_Fastest_Lap_Prop</t>
+  </si>
+  <si>
+    <t>Proportion of fastest laps recorded by the team’s drivers across all Grands Prix in the prior season. (`Prior_Season_Fastest_Lap_Count` ÷ `Prior_Season_Grand_Prix_Count`)</t>
   </si>
 </sst>
 </file>
@@ -1257,12 +1275,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:XFB28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:XFB31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="255.6640625" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9739,7 +9757,7 @@
       </c>
     </row>
     <row r="28" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -9747,6 +9765,39 @@
       </c>
       <c r="C28" s="1" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A31" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26218E12-5353-46EF-9951-3A3CD79047C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E14A01-F666-49E4-9F75-33B2FE31F8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-11370" windowWidth="16410" windowHeight="11295" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -878,7 +878,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -894,7 +894,6 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -9790,7 +9789,7 @@
       </c>
     </row>
     <row r="31" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B31" s="1" t="s">

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E14A01-F666-49E4-9F75-33B2FE31F8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB56558-7787-4250-A35A-3424FB84467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>Season</t>
   </si>
@@ -119,15 +119,6 @@
     <t>Defending_Constructor_Champ</t>
   </si>
   <si>
-    <t xml:space="preserve">The number of DNF or DNS results during the previous season (this does not include sprint race results). </t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether the season included a major technical or sporting regulation change (1 = yes, 0 = no).</t>
-  </si>
-  <si>
-    <t>Numerical identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve organizational continuity (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
-  </si>
-  <si>
     <t>Year in which the constructor competed in the Formula One World Championship.</t>
   </si>
   <si>
@@ -146,98 +137,10 @@
     <t>Prior_Season_NonFinish_Rate</t>
   </si>
   <si>
-    <t>The amount of points scored by a single team in the previous season (including points earned from fastest lap or sprint races).</t>
-  </si>
-  <si>
     <t>The number of Grand Prix wins by a constructor in the previous season (this does not include sprint Race wins).</t>
   </si>
   <si>
     <t>Prior_Season_Points_Earned</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of total points scored by all teams in the previous season (`Prior_Season_Points_Earned` divided by `Prior_Season_Points_Total`). This normalizes performance across seasons with different numbers of teams or scoring systems.</t>
-  </si>
-  <si>
-    <r>
-      <t>Constructor’s proportion of races won in the previous season (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Prior_Season_Grand_Prix_Wins</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Prior_Season_Grand_Prix_Count</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Constructor’s proportion of DNF or DNS results (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Prior_Season_NonFinishes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ÷ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Prior_Season_Grand_Prix_Count</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> × 2)), accounting for 2 cars per race.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -292,31 +195,10 @@
     <t>Prior_Season_Win_Prop_Last5GP</t>
   </si>
   <si>
-    <t>The number of Grand Prix wins by a constructor in the previous season's first 5 rounds (this does not include sprint Race wins).</t>
-  </si>
-  <si>
-    <t>The number of Grand Prix wins by a constructor in the previous season's last 5 rounds (this does not include sprint Race wins).</t>
-  </si>
-  <si>
-    <t>`Prior_Season_Grand_Prix_Wins_First5GP` ÷ 5</t>
-  </si>
-  <si>
-    <t>`Prior_Season_Grand_Prix_Wins_Last5GP` ÷ 5</t>
-  </si>
-  <si>
-    <t>The total number of Formula 1 races started by the two drivers contracted to the team at the start of the season, regardless of any mid-season driver changes.</t>
-  </si>
-  <si>
     <t>Driver_Lineup_Experience</t>
   </si>
   <si>
     <t>Prior_Season_Quali_Avg</t>
-  </si>
-  <si>
-    <t>Average qualifying position of both team cars across all Grands Prix in the prior season.</t>
-  </si>
-  <si>
-    <t>Total number of fastest laps recorded by the team’s drivers across all Grands Prix in the prior season.</t>
   </si>
   <si>
     <t>Prior_Season_Fastest_Lap_Count</t>
@@ -325,7 +207,123 @@
     <t>Prior_Season_Fastest_Lap_Prop</t>
   </si>
   <si>
-    <t>Proportion of fastest laps recorded by the team’s drivers across all Grands Prix in the prior season. (`Prior_Season_Fastest_Lap_Count` ÷ `Prior_Season_Grand_Prix_Count`)</t>
+    <t>Grooved_Tyre_Era_Experience</t>
+  </si>
+  <si>
+    <t>Refueling_Ban_Aero_Era_Experience</t>
+  </si>
+  <si>
+    <t>Early_Turbo_Hybrid_Era_Experience</t>
+  </si>
+  <si>
+    <t>Mature_Turbo_Hybrid_Era_Experience</t>
+  </si>
+  <si>
+    <t>Ground_Effect_Era_Experience</t>
+  </si>
+  <si>
+    <t>Active_Aero_Era_Experience</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2026 onward regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2022 to 2025 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2017 to 2021 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2014 to 2016 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2009 to 2013 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Numerical identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve competitive and organizational continuity. (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
+  </si>
+  <si>
+    <t>Total championship points scored by the constructor in the previous season, including points awarded for fastest lap and sprint events.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of total points scored by all teams in the previous season. This metric normalizes performance across seasons with differing grid sizes or scoring systems.</t>
+  </si>
+  <si>
+    <r>
+      <t>Constructor’s proportion of DNF or DNS results (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_NonFinishes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ÷ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Prior_Season_Grand_Prix_Count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> × 2)), assuming two constructor entries per Grand Prix.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mean qualifying position across all Grand Prix qualifying sessions for both team cars in the previous season.</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the first five rounds of the previous season, excluding sprint race wins.</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the last five rounds of the previous season, excluding sprint race wins.</t>
+  </si>
+  <si>
+    <t>The number of DNF or DNS results recorded by the constructor during the previous season, excluding sprint race results.</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the season included a major technical or sporting regulation change as defined by the FIA (1 = yes, 0 = no).</t>
+  </si>
+  <si>
+    <t>Total number of fastest laps recorded by the team’s drivers across all Grand Prix in the prior season.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of Grand Prix in which one of its drivers recorded the fastest lap in the previous season.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of Grand Prix won in the previous season.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of Grand Prix wins in the first five rounds of the previous season.</t>
+  </si>
+  <si>
+    <t>Constructor’s proportion of Grand Prix wins in the last five rounds of the previous season.</t>
   </si>
 </sst>
 </file>
@@ -513,7 +511,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -717,6 +715,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -878,7 +882,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -894,6 +898,8 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1274,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:XFB31"/>
+  <dimension ref="A1:XFB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
@@ -1291,7 +1297,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -1320,7 +1326,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1331,7 +1337,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1342,7 +1348,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1386,7 +1392,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1397,7 +1403,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1408,18 +1414,18 @@
         <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1430,7 +1436,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1440,8 +1446,8 @@
       <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>40</v>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
@@ -1452,7 +1458,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
@@ -1474,7 +1480,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
@@ -1501,57 +1507,57 @@
     </row>
     <row r="22" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A22" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A24" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
-      <c r="A26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>28</v>
+      <c r="C26" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="D26" s="5"/>
       <c r="F26" s="5"/>
@@ -9745,58 +9751,124 @@
       <c r="XFB26" s="5"/>
     </row>
     <row r="27" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
-      <c r="A27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>42</v>
+      <c r="C27" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
-      <c r="A30" s="8" t="s">
-        <v>58</v>
+      <c r="A30" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16382">
+      <c r="A32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>60</v>
+      <c r="C37" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B5A420-A9A7-456E-8BC3-CA5D259D33F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F54FFB-413F-4D63-9AF8-9F350B3B191B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-10980" windowWidth="16410" windowHeight="11295" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
   <si>
     <t>Season</t>
   </si>
@@ -189,9 +189,6 @@
     <t>Prior_Season_Win_Prop_Last5GP</t>
   </si>
   <si>
-    <t>Driver_Lineup_Experience</t>
-  </si>
-  <si>
     <t>Prior_Season_Quali_Avg</t>
   </si>
   <si>
@@ -201,24 +198,6 @@
     <t>Prior_Season_Fastest_Lap_Prop</t>
   </si>
   <si>
-    <t>Grooved_Tyre_Era_Experience</t>
-  </si>
-  <si>
-    <t>Refueling_Ban_Aero_Era_Experience</t>
-  </si>
-  <si>
-    <t>Early_Turbo_Hybrid_Era_Experience</t>
-  </si>
-  <si>
-    <t>Mature_Turbo_Hybrid_Era_Experience</t>
-  </si>
-  <si>
-    <t>Ground_Effect_Era_Experience</t>
-  </si>
-  <si>
-    <t>Active_Aero_Era_Experience</t>
-  </si>
-  <si>
     <t>Total number of Formula One World Championship race starts accumulated prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
   </si>
   <si>
@@ -276,27 +255,6 @@
     <t>Constructor’s proportion of Grand Prix wins in the last five rounds of the previous season.</t>
   </si>
   <si>
-    <t>Driver_Lineup_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Active_Aero_Era_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Ground_Effect_Era_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Mature_Turbo_Hybrid_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Early_Turbo_Hybrid_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Refueling_Ban_Aero_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Grooved_Tyre_Era_Laps_Completed</t>
-  </si>
-  <si>
     <t>Total number of laps completed in Grand Prix prior to the current season within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
   </si>
   <si>
@@ -316,6 +274,90 @@
   </si>
   <si>
     <t>Total number of laps completed in Grand Prix prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Active_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Ground_Effect_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Total_Experience</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Mature_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Early_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Refueling_Ban_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Experience_Grooved_Tyre_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Total_Laps_Completed</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Active_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Ground_Effect_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Mature_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Early_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Refueling_Ban_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Laps_Grooved_Tyre_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Total_Wins</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Active_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Ground_Effect_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Mature_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Early_Turbo_Hybrid_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Refueling_Ban_Aero_Era</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Wins_Grooved_Tyre_Era</t>
+  </si>
+  <si>
+    <t>Total number of career Grand Prix wins achieved by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 2026 onward regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 2022 to 2025 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 2017 to 2021 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 2014 to 2026 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 2009 to 2013 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix won within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
   </si>
 </sst>
 </file>
@@ -1258,10 +1300,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="255.7109375" customWidth="1"/>
   </cols>
@@ -1304,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1392,7 +1434,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1403,7 +1445,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1425,7 +1467,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1458,7 +1500,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1491,7 +1533,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1502,7 +1544,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1513,7 +1555,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1524,194 +1566,271 @@
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>42</v>
+      <c r="A41" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>65</v>
+      <c r="C49" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F54FFB-413F-4D63-9AF8-9F350B3B191B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A07B725-68A4-488A-B979-848E55C677DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t>Season</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Column</t>
-  </si>
-  <si>
-    <t>Prior_Season_Points_Share</t>
   </si>
   <si>
     <t>Defending_Driver_Champ</t>
@@ -180,15 +177,9 @@
     <t>Prior_Season_Grand_Prix_Wins_First5GP</t>
   </si>
   <si>
-    <t>Prior_Season_Win_Prop_First5GP</t>
-  </si>
-  <si>
     <t>Prior_Season_Grand_Prix_Wins_Last5GP</t>
   </si>
   <si>
-    <t>Prior_Season_Win_Prop_Last5GP</t>
-  </si>
-  <si>
     <t>Prior_Season_Quali_Avg</t>
   </si>
   <si>
@@ -249,12 +240,6 @@
     <t>Constructor’s proportion of Grand Prix won in the previous season.</t>
   </si>
   <si>
-    <t>Constructor’s proportion of Grand Prix wins in the first five rounds of the previous season.</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of Grand Prix wins in the last five rounds of the previous season.</t>
-  </si>
-  <si>
     <t>Total number of laps completed in Grand Prix prior to the current season within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
   </si>
   <si>
@@ -358,6 +343,9 @@
   </si>
   <si>
     <t>Total number of Grand Prix won within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
+  </si>
+  <si>
+    <t>Prior_Season_Points_Prop</t>
   </si>
 </sst>
 </file>
@@ -905,7 +893,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -920,6 +908,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1300,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
@@ -1310,14 +1299,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -1332,21 +1321,21 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1354,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1365,21 +1354,21 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1387,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>3</v>
@@ -1395,35 +1384,35 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1431,406 +1420,384 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="B23" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>38</v>
+      <c r="A24" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>89</v>
+      <c r="A46" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A07B725-68A4-488A-B979-848E55C677DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -893,7 +893,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -908,7 +908,6 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1515,7 +1514,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1526,7 +1525,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A07B725-68A4-488A-B979-848E55C677DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB1C2AC-AE42-4B14-8A74-569148347384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
   <si>
     <t>Season</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Test|Train.csv</t>
   </si>
   <si>
     <t>Origin</t>
@@ -346,6 +343,15 @@
   </si>
   <si>
     <t>Prior_Season_Points_Prop</t>
+  </si>
+  <si>
+    <t>raw_data_2026.csv</t>
+  </si>
+  <si>
+    <t>UK_Based</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the constructor’s primary factory operations (not nationality, not engine supplier) are based in the United Kingdom (1 = factory in the United Kingdom, 0 = factory not in the United Kingdom).</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
@@ -1298,14 +1304,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -1320,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -1328,13 +1334,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,10 +1348,10 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,10 +1370,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>3</v>
@@ -1383,252 +1389,252 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>21</v>
+      <c r="B16" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
+      <c r="A17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>62</v>
@@ -1636,10 +1642,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>61</v>
@@ -1647,10 +1653,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>60</v>
@@ -1658,10 +1664,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>59</v>
@@ -1669,10 +1675,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>58</v>
@@ -1680,10 +1686,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>57</v>
@@ -1691,112 +1697,123 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="B47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB1C2AC-AE42-4B14-8A74-569148347384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0EE2C0-E536-4772-A293-4C857E44668A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>Season</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Prior_Season_Grand_Prix_Wins</t>
-  </si>
-  <si>
-    <t>Prior_Season_Grand_Prix_Count</t>
   </si>
   <si>
     <t>Description</t>
@@ -186,27 +183,6 @@
     <t>Prior_Season_Fastest_Lap_Prop</t>
   </si>
   <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2026 onward regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2022 to 2025 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2017 to 2021 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2014 to 2016 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 2009 to 2013 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Formula One World Championship race starts accumulated prior to the current season within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
     <t>Numerical identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve competitive and organizational continuity. (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
   </si>
   <si>
@@ -237,111 +213,12 @@
     <t>Constructor’s proportion of Grand Prix won in the previous season.</t>
   </si>
   <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 2009 to 2013 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 2014 to 2016 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 2017 to 2021 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 2022 to 2025 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season within the 2026 onward regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
     <t>Total number of laps completed in Grand Prix prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
   </si>
   <si>
-    <t>Driver_Lineup_Experience_Active_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Experience_Ground_Effect_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Total_Experience</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Experience_Mature_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Experience_Early_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Experience_Refueling_Ban_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Experience_Grooved_Tyre_Era</t>
-  </si>
-  <si>
     <t>Driver_Lineup_Total_Laps_Completed</t>
   </si>
   <si>
-    <t>Driver_Lineup_Laps_Active_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Laps_Ground_Effect_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Laps_Mature_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Laps_Early_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Laps_Refueling_Ban_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Laps_Grooved_Tyre_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Total_Wins</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Active_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Ground_Effect_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Mature_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Early_Turbo_Hybrid_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Refueling_Ban_Aero_Era</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Wins_Grooved_Tyre_Era</t>
-  </si>
-  <si>
-    <t>Total number of career Grand Prix wins achieved by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 2026 onward regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 2022 to 2025 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 2017 to 2021 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 2014 to 2026 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 2009 to 2013 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix won within the 1998 to 2008 regulatory era by the two drivers contracted at the start of the season.</t>
-  </si>
-  <si>
     <t>Prior_Season_Points_Prop</t>
   </si>
   <si>
@@ -352,6 +229,51 @@
   </si>
   <si>
     <t>Binary variable indicating whether the constructor’s primary factory operations (not nationality, not engine supplier) are based in the United Kingdom (1 = factory in the United Kingdom, 0 = factory not in the United Kingdom).</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_Total_Race_Starts</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_3_Season_Laps_Completed</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_3_Season_Laps_Prop</t>
+  </si>
+  <si>
+    <t>Total number of laps completed in Grand Prix by both drivers over the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Maximum possible laps for a single car across all Grand Prix in the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_3_Season_Race_Starts</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix race starts completed by both drivers over the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Maximum possible race starts for a single driver across all Grand Prix in the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Driver_Lineup_3_Season_Race_Start_Prop</t>
+  </si>
+  <si>
+    <t>Total number of Formula One Grand Prix starts accumulated prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
+  </si>
+  <si>
+    <t>Prior_Season_GP_Count</t>
+  </si>
+  <si>
+    <t>Prior_3_Season_GP_Count</t>
+  </si>
+  <si>
+    <t>Prior_3_Season_Lap_Count</t>
+  </si>
+  <si>
+    <t>Proportion of total possible laps completed by the team’s two drivers over the previous 3 seasons: Driver_Lineup_3_Season_Laps_Completed ÷ (Prior_3_Season_Lap_Count x 2)</t>
+  </si>
+  <si>
+    <t>Proportion of total possible race starts completed by the team’s two drivers over the previous 3 seasons: Driver_Lineup_3_Season_Race_Starts ÷ (Prior_3_Season_GP_Count x 2)</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
@@ -1304,14 +1226,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -1326,21 +1248,21 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1348,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1359,21 +1281,21 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1381,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>3</v>
@@ -1389,46 +1311,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1436,21 +1358,21 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1458,21 +1380,21 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1480,21 +1402,21 @@
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1502,10 +1424,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1513,307 +1435,164 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="B27" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>68</v>
+      <c r="A30" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>69</v>
+      <c r="A31" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>72</v>
+      <c r="A34" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0EE2C0-E536-4772-A293-4C857E44668A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7FBC33-6558-4E58-BE92-EF81D6043099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>Season</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>Proportion of total possible race starts completed by the team’s two drivers over the previous 3 seasons: Driver_Lineup_3_Season_Race_Starts ÷ (Prior_3_Season_GP_Count x 2)</t>
+  </si>
+  <si>
+    <t>race_starts.csv</t>
+  </si>
+  <si>
+    <t>laps_completed.csv</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1485,7 @@
         <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>63</v>
@@ -1490,7 +1496,7 @@
         <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>60</v>
@@ -1523,7 +1529,7 @@
         <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>48</v>
@@ -1534,7 +1540,7 @@
         <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>57</v>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7FBC33-6558-4E58-BE92-EF81D6043099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ED48C4-4195-4A9A-8ECA-B97EB4BCDE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28800" yWindow="-8640" windowWidth="16410" windowHeight="15480" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>Season</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Reg_Change_Year</t>
   </si>
   <si>
-    <t>Column</t>
-  </si>
-  <si>
     <t>Defending_Driver_Champ</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Origin</t>
-  </si>
-  <si>
     <t>Constructor_Lineage_ID</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
   </si>
   <si>
     <t>The number of Grand Prix held in the previous season (this does not include sprint races).</t>
-  </si>
-  <si>
-    <t>All prior season performance variables reflect results from the immediately preceding season and are used to simulate preseason championship prediction without incorporating in season outcomes.</t>
   </si>
   <si>
     <t>Engineered feature</t>
@@ -280,6 +271,27 @@
   </si>
   <si>
     <t>laps_completed.csv</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Driver_A</t>
+  </si>
+  <si>
+    <t>Driver_B</t>
+  </si>
+  <si>
+    <t>Name of one driver signed by the team for the current season.</t>
+  </si>
+  <si>
+    <t>Returning_Driver_Lineup</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a constructor's driver lineup is the same as the previous season (1 = both drivers returning from previous season, 0 = at least one new driver signed with the team).</t>
   </si>
 </sst>
 </file>
@@ -1222,389 +1234,414 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
+      <c r="A8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>3</v>
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>59</v>
+      <c r="A26" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>65</v>
+      <c r="A27" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>55</v>
+      <c r="A30" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>66</v>
+      <c r="A31" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>36</v>
+      <c r="A34" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00ED48C4-4195-4A9A-8ECA-B97EB4BCDE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F53185-C9CF-4806-9323-5F3DC1275E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-8640" windowWidth="16410" windowHeight="15480" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F53185-C9CF-4806-9323-5F3DC1275E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D168C4-0344-4848-A18E-BD9784B0B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t>Season</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Target variable indicating whether a constructor won the Formula One World Championship (1 = won championship, 0 = did not win championship).</t>
-  </si>
-  <si>
-    <t>Reg_Change_Year</t>
   </si>
   <si>
     <t>Defending_Driver_Champ</t>
@@ -190,9 +187,6 @@
   </si>
   <si>
     <t>The number of Grand Prix wins by a constructor in the last five rounds of the previous season, excluding sprint race wins.</t>
-  </si>
-  <si>
-    <t>Binary variable indicating whether the season included a major technical or sporting regulation change as defined by the FIA (1 = yes, 0 = no).</t>
   </si>
   <si>
     <t>Total number of fastest laps recorded by the team’s drivers across all Grand Prix in the prior season.</t>
@@ -1234,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1244,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1256,62 +1250,62 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>2</v>
@@ -1322,150 +1316,150 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="7" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -1476,29 +1470,29 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>71</v>
@@ -1509,134 +1503,123 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>62</v>
+        <v>15</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>63</v>
+        <v>15</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D168C4-0344-4848-A18E-BD9784B0B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD675F-7E9A-480E-934F-2DCBE9F4E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="9000" yWindow="0" windowWidth="16410" windowHeight="15480" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data_Dictionary" sheetId="1" r:id="rId1"/>
+    <sheet name="Dictionary" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
   <si>
     <t>Season</t>
   </si>
@@ -44,15 +44,9 @@
     <t>Constructor_Champion</t>
   </si>
   <si>
-    <t>Target variable indicating whether a constructor won the Formula One World Championship (1 = won championship, 0 = did not win championship).</t>
-  </si>
-  <si>
     <t>Defending_Driver_Champ</t>
   </si>
   <si>
-    <t>Prior_Season_Win_Prop</t>
-  </si>
-  <si>
     <t>Prior_Season_Points_Total</t>
   </si>
   <si>
@@ -62,27 +56,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>Constructor_Lineage_ID</t>
   </si>
   <si>
-    <t>Composite unique identifier formed by concatenating Constructor_Lineage_ID, Season, and Team_Name. Used as the primary row-level key.</t>
-  </si>
-  <si>
     <t>New_Name</t>
   </si>
   <si>
-    <t>Binary variable indicating whether the reigning Drivers’ World Champion is competing for a team in the current season (1 = one driver on the constructor’s roster won the Drivers’ Championship in the previous season, 0 = no reigning Drivers’ Champion on the team).</t>
-  </si>
-  <si>
-    <t>The number of Grand Prix held in the previous season (this does not include sprint races).</t>
-  </si>
-  <si>
-    <t>Engineered feature</t>
-  </si>
-  <si>
     <t>Engine_Branding</t>
   </si>
   <si>
@@ -92,9 +71,6 @@
     <t>New_Team</t>
   </si>
   <si>
-    <t>Binary variable indicating whether the team is the reigning Constructors World Champion (1 if the constructor won the championship the prior season, 0 otherwise).</t>
-  </si>
-  <si>
     <t>Defending_Constructor_Champ</t>
   </si>
   <si>
@@ -107,106 +83,24 @@
     <t>Binary variable indicating whether a returning constructor is competing under a new team name compared to the previous season (1 = `Team_Name` differs from the previous season, 0 = no name change).</t>
   </si>
   <si>
-    <t>Binary variable indicating whether a constructor is new to the F1 championship (1 = first ever appearance in F1 history, 0 = constructor has previously competed in Formula 1 under any name).</t>
-  </si>
-  <si>
-    <t>The number of Grand Prix wins by a constructor in the previous season (this does not include sprint Race wins).</t>
-  </si>
-  <si>
     <t>Prior_Season_Points_Earned</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <u/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Underlined</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> variables  are used solely for feature engineering and are dropped from the dataset after derived features are created.</t>
-    </r>
-  </si>
-  <si>
-    <t>Total points scored by all constructors in the previous season, including fastest lap and sprint points. This total reflects the full prior-season grid, including teams that did not compete in the current season.</t>
-  </si>
-  <si>
     <t>Prior_Season_Grand_Prix_Wins_First5GP</t>
   </si>
   <si>
     <t>Prior_Season_Grand_Prix_Wins_Last5GP</t>
   </si>
   <si>
-    <t>Prior_Season_Quali_Avg</t>
-  </si>
-  <si>
     <t>Prior_Season_Fastest_Lap_Count</t>
   </si>
   <si>
-    <t>Prior_Season_Fastest_Lap_Prop</t>
-  </si>
-  <si>
-    <t>Numerical identifier representing a constructor’s ownership lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve competitive and organizational continuity. (Ex. Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
-  </si>
-  <si>
-    <t>Total championship points scored by the constructor in the previous season, including points awarded for fastest lap and sprint events.</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of total points scored by all teams in the previous season. This metric normalizes performance across seasons with differing grid sizes or scoring systems.</t>
-  </si>
-  <si>
     <t>Mean qualifying position across all Grand Prix qualifying sessions for both team cars in the previous season.</t>
   </si>
   <si>
-    <t>The number of Grand Prix wins by a constructor in the first five rounds of the previous season, excluding sprint race wins.</t>
-  </si>
-  <si>
-    <t>The number of Grand Prix wins by a constructor in the last five rounds of the previous season, excluding sprint race wins.</t>
-  </si>
-  <si>
     <t>Total number of fastest laps recorded by the team’s drivers across all Grand Prix in the prior season.</t>
   </si>
   <si>
-    <t>Constructor’s proportion of Grand Prix in which one of its drivers recorded the fastest lap in the previous season.</t>
-  </si>
-  <si>
-    <t>Constructor’s proportion of Grand Prix won in the previous season.</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_Total_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Prior_Season_Points_Prop</t>
-  </si>
-  <si>
     <t>raw_data_2026.csv</t>
   </si>
   <si>
@@ -216,36 +110,6 @@
     <t>Binary variable indicating whether the constructor’s primary factory operations (not nationality, not engine supplier) are based in the United Kingdom (1 = factory in the United Kingdom, 0 = factory not in the United Kingdom).</t>
   </si>
   <si>
-    <t>Driver_Lineup_Total_Race_Starts</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_3_Season_Laps_Completed</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_3_Season_Laps_Prop</t>
-  </si>
-  <si>
-    <t>Total number of laps completed in Grand Prix by both drivers over the previous 3 seasons.</t>
-  </si>
-  <si>
-    <t>Maximum possible laps for a single car across all Grand Prix in the previous 3 seasons.</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_3_Season_Race_Starts</t>
-  </si>
-  <si>
-    <t>Total number of Grand Prix race starts completed by both drivers over the previous 3 seasons.</t>
-  </si>
-  <si>
-    <t>Maximum possible race starts for a single driver across all Grand Prix in the previous 3 seasons.</t>
-  </si>
-  <si>
-    <t>Driver_Lineup_3_Season_Race_Start_Prop</t>
-  </si>
-  <si>
-    <t>Total number of Formula One Grand Prix starts accumulated prior to the current season by the two drivers contracted to the constructor at the start of the season. Mid-season driver changes are not incorporated.</t>
-  </si>
-  <si>
     <t>Prior_Season_GP_Count</t>
   </si>
   <si>
@@ -255,12 +119,6 @@
     <t>Prior_3_Season_Lap_Count</t>
   </si>
   <si>
-    <t>Proportion of total possible laps completed by the team’s two drivers over the previous 3 seasons: Driver_Lineup_3_Season_Laps_Completed ÷ (Prior_3_Season_Lap_Count x 2)</t>
-  </si>
-  <si>
-    <t>Proportion of total possible race starts completed by the team’s two drivers over the previous 3 seasons: Driver_Lineup_3_Season_Race_Starts ÷ (Prior_3_Season_GP_Count x 2)</t>
-  </si>
-  <si>
     <t>race_starts.csv</t>
   </si>
   <si>
@@ -270,29 +128,101 @@
     <t>Variable</t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>Driver_A</t>
   </si>
   <si>
     <t>Driver_B</t>
   </si>
   <si>
-    <t>Name of one driver signed by the team for the current season.</t>
-  </si>
-  <si>
     <t>Returning_Driver_Lineup</t>
   </si>
   <si>
-    <t>Binary variable indicating whether a constructor's driver lineup is the same as the previous season (1 = both drivers returning from previous season, 0 = at least one new driver signed with the team).</t>
+    <t>Prior_Season_Avg_Quali_Pos</t>
+  </si>
+  <si>
+    <t>Major_Reg_Change</t>
+  </si>
+  <si>
+    <t>Data File</t>
+  </si>
+  <si>
+    <t>Target variable; indicates whether a constructor won the Formula One World Championship (1 = won championship, 0 = did not win championship).</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the previous season, excluding Sprint Race wins.</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix held in the previous season, excluding Sprint Races.</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the team is the reigning Constructors World Champion (1 = the constructor won the championship during the prior season, 0 = constructor did not win the championship during the prior season).</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the first five rounds of the previous season, excluding Sprint Race wins.</t>
+  </si>
+  <si>
+    <t>The number of Grand Prix wins by a constructor in the last five rounds of the previous season, excluding Sprint Race wins.</t>
+  </si>
+  <si>
+    <t>Total lap count for all Grand Prix in the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix held in the previous 3 seasons.</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Laps_Completed</t>
+  </si>
+  <si>
+    <t>Race_Starts</t>
+  </si>
+  <si>
+    <t>Name of one driver who competed in the Formula 1 championship.</t>
+  </si>
+  <si>
+    <t>Total laps completed by the driver throughout the given season.</t>
+  </si>
+  <si>
+    <t>Total number of Grand Prix starts completed by the driver throughout the given season.</t>
+  </si>
+  <si>
+    <t>Numerical identifier representing a constructor's organizational lineage across all seasons. This identifier remains constant across name, branding, or ownership transitions that preserve competitive and organizational continuity (e.g., Tyrrell → BAR → Honda → Brawn GP → Mercedes).</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether a constructor is making its first appearance in Formula One history (1 = first-ever appearance in Formula One, 0 = constructor has previously competed under any name).</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether major changes were made to the Formula One technical or sporting regulations (1 = major changes implemented, 0 = few or no significant changes).</t>
+  </si>
+  <si>
+    <t>Total Constructors' Championship points scored by the constructor in the previous season, including points awarded for sprint events and fastest laps where applicable.</t>
+  </si>
+  <si>
+    <t>Total Constructors' Championship points scored by all constructors in the previous season, including sprint and fastest-lap points where applicable. This total reflects the full prior-season grid, including teams that did not compete in the current season.</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the reigning Drivers' World Champion is a member of the constructor's driver lineup for the current season (1 = reigning champion drives for the constructor, 0 = reigning champion does not drive for the constructor).</t>
+  </si>
+  <si>
+    <t>Name of one driver contracted to compete for the constructor at the start of the current season (this does not account for mid-season driver changes).</t>
+  </si>
+  <si>
+    <t>Binary variable indicating whether the constructor retained the same two-driver lineup from the previous season (1 = both drivers returned from the previous season, 0 = at least one driver changed).</t>
+  </si>
+  <si>
+    <t>Year in which the driver competed in the Formula One World Championship.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,48 +357,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -646,30 +536,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -833,21 +699,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1227,406 +1081,357 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CC40D8-CCDB-4691-9AE9-BD3F7CAB3CBE}">
-  <dimension ref="A1:C36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800EEDB6-9D94-4EDC-8943-58920B932872}">
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="252.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="C25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD675F-7E9A-480E-934F-2DCBE9F4E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00DDEC1-935A-4EAA-8A8F-D8AA1669CB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="0" windowWidth="16410" windowHeight="15480" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{B38841E1-F419-4689-90BF-F91CA7B5FE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
   <si>
     <t>Season</t>
   </si>
@@ -185,9 +185,6 @@
     <t>Name of one driver who competed in the Formula 1 championship.</t>
   </si>
   <si>
-    <t>Total laps completed by the driver throughout the given season.</t>
-  </si>
-  <si>
     <t>Total number of Grand Prix starts completed by the driver throughout the given season.</t>
   </si>
   <si>
@@ -209,13 +206,19 @@
     <t>Binary variable indicating whether the reigning Drivers' World Champion is a member of the constructor's driver lineup for the current season (1 = reigning champion drives for the constructor, 0 = reigning champion does not drive for the constructor).</t>
   </si>
   <si>
-    <t>Name of one driver contracted to compete for the constructor at the start of the current season (this does not account for mid-season driver changes).</t>
-  </si>
-  <si>
     <t>Binary variable indicating whether the constructor retained the same two-driver lineup from the previous season (1 = both drivers returned from the previous season, 0 = at least one driver changed).</t>
   </si>
   <si>
     <t>Year in which the driver competed in the Formula One World Championship.</t>
+  </si>
+  <si>
+    <t>Total laps completed in a Grand Prix by the driver throughout the given season.</t>
+  </si>
+  <si>
+    <t>Name of the other primary driver contracted to compete for the constructor at the start of the current season (this does not account for mid-season driver changes).</t>
+  </si>
+  <si>
+    <t>Name of one primary driver contracted to compete for the constructor at the start of the current season (this does not account for mid-season driver changes).</t>
   </si>
 </sst>
 </file>
@@ -699,9 +702,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1085,8 +1087,8 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="252.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1109,7 +1111,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,7 +1121,7 @@
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1130,7 +1132,7 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1141,7 +1143,7 @@
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1152,7 +1154,7 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1163,7 +1165,7 @@
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1175,7 +1177,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,7 +1187,7 @@
       <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1196,7 +1198,7 @@
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1207,7 +1209,7 @@
       <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1219,7 +1221,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1230,7 +1232,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1241,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1251,7 +1253,7 @@
       <c r="B15" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1262,7 +1264,7 @@
       <c r="B16" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1274,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1284,7 +1286,7 @@
       <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1295,7 +1297,7 @@
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1306,7 +1308,7 @@
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1318,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1329,7 +1331,7 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1340,7 +1342,7 @@
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1350,7 +1352,7 @@
       <c r="B24" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1361,7 +1363,7 @@
       <c r="B25" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1372,7 +1374,7 @@
       <c r="B26" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1384,7 +1386,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1395,7 +1397,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1405,7 +1407,7 @@
       <c r="B29" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1417,7 +1419,7 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1428,10 +1430,16 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{170051ed-867f-4092-a6af-8a42e27b7e09}" enabled="1" method="Standard" siteId="{5217e0e7-539d-4563-b1bf-7c6dcf074f91}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>